--- a/output/tables/2025/tabla5_cruces_cluster.xlsx
+++ b/output/tables/2025/tabla5_cruces_cluster.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">fuente</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_ep_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_ep_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">C1</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">C5</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_barrio_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en el barrio</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Alta inseguridad en el barrio</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_casa_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en la casa</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Cree que será victima de otro tipo de delito</t>
   </si>
   <si>
-    <t xml:space="preserve">comper_pct_rec_tercil</t>
+    <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Bajas prácticas de evitación</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja disposición de medidas vivienda</t>
@@ -165,7 +165,7 @@
     <t xml:space="preserve">Alta disposición de medidas vivienda</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja adopción de medidas comunitarias</t>
@@ -724,7 +724,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="21.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="3.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="45.71" hidden="0" customWidth="1"/>

--- a/output/tables/2025/tabla5_cruces_cluster.xlsx
+++ b/output/tables/2025/tabla5_cruces_cluster.xlsx
@@ -60,19 +60,19 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja inseguridad en espacio publico</t>
+    <t xml:space="preserve">Sin inseguridad en espacio público</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">Media inseguridad en espacio publico</t>
+    <t xml:space="preserve">Inseguridad en hasta la mitad de los lugares</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">Alta inseguridad en espacio publico</t>
+    <t xml:space="preserve">Inseguridad en más de la mitad de los lugares</t>
   </si>
   <si>
     <t xml:space="preserve">C2</t>
@@ -90,25 +90,25 @@
     <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja inseguridad en el barrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media inseguridad en el barrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en el barrio</t>
+    <t xml:space="preserve">Sin inseguridad en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en el barrio, de día o de noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en el barrio, de día y de noche</t>
   </si>
   <si>
     <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja inseguridad en la casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media inseguridad en la casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en la casa</t>
+    <t xml:space="preserve">Sin inseguridad en la casa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en la casa, de día o de noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en la casa, de día y de noche</t>
   </si>
   <si>
     <t xml:space="preserve">perper_delito</t>
@@ -132,13 +132,13 @@
     <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Bajas prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medias prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altas prácticas de evitación</t>
+    <t xml:space="preserve">No modificó prácticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modificó hasta la mitad de las prácticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modificó más de la mitad de las prácticas</t>
   </si>
   <si>
     <t xml:space="preserve">comper_gasto</t>
@@ -156,25 +156,25 @@
     <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja disposición de medidas vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media disposición de medidas vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta disposición de medidas vivienda</t>
+    <t xml:space="preserve">Sin medidas en la vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una o dos medidas en la vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tres o más medidas en la vivienda</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja adopción de medidas comunitarias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media adopción de medidas comunitarias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta adopción de medidas comunitarias</t>
+    <t xml:space="preserve">Sin medidas en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una medida en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dos o más medidas en el barrio</t>
   </si>
   <si>
     <t xml:space="preserve">secundaria</t>
@@ -727,7 +727,7 @@
     <col min="2" max="2" width="21.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="3.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="45.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="46.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="7.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
   </cols>
@@ -772,10 +772,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1760658</v>
+        <v>1457071</v>
       </c>
       <c r="G2" t="n">
-        <v>75.52</v>
+        <v>58.19</v>
       </c>
     </row>
     <row r="3">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>375427</v>
+        <v>914419</v>
       </c>
       <c r="G3" t="n">
-        <v>16.1</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="4">
@@ -818,10 +818,10 @@
         <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>195316</v>
+        <v>132460</v>
       </c>
       <c r="G4" t="n">
-        <v>8.38</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="5">
@@ -841,10 +841,10 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>920372</v>
+        <v>146781</v>
       </c>
       <c r="G5" t="n">
-        <v>50.41</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="6">
@@ -864,10 +864,10 @@
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>701670</v>
+        <v>299640</v>
       </c>
       <c r="G6" t="n">
-        <v>38.43</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="7">
@@ -887,10 +887,10 @@
         <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>203735</v>
+        <v>223734</v>
       </c>
       <c r="G7" t="n">
-        <v>11.16</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="8">
@@ -910,10 +910,10 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>328805</v>
+        <v>220319</v>
       </c>
       <c r="G8" t="n">
-        <v>13.27</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="9">
@@ -933,10 +933,10 @@
         <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>1696973</v>
+        <v>3153352</v>
       </c>
       <c r="G9" t="n">
-        <v>68.5</v>
+        <v>72.79</v>
       </c>
     </row>
     <row r="10">
@@ -956,10 +956,10 @@
         <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>451649</v>
+        <v>958271</v>
       </c>
       <c r="G10" t="n">
-        <v>18.23</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="11">
@@ -979,10 +979,10 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>148771</v>
+        <v>76312</v>
       </c>
       <c r="G11" t="n">
-        <v>5.84</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="12">
@@ -1002,10 +1002,10 @@
         <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>1004702</v>
+        <v>615481</v>
       </c>
       <c r="G12" t="n">
-        <v>39.47</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="13">
@@ -1025,10 +1025,10 @@
         <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>1392042</v>
+        <v>1226039</v>
       </c>
       <c r="G13" t="n">
-        <v>54.69</v>
+        <v>63.93</v>
       </c>
     </row>
     <row r="14">
@@ -1048,10 +1048,10 @@
         <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>129375</v>
+        <v>46572</v>
       </c>
       <c r="G14" t="n">
-        <v>4.62</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="15">
@@ -1071,10 +1071,10 @@
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>555249</v>
+        <v>373748</v>
       </c>
       <c r="G15" t="n">
-        <v>19.84</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="16">
@@ -1094,10 +1094,10 @@
         <v>19</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2113640</v>
+        <v>2134186</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>75.53</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="17">
@@ -1117,10 +1117,10 @@
         <v>25</v>
       </c>
       <c r="F17" t="n">
-        <v>1623755</v>
+        <v>2186949</v>
       </c>
       <c r="G17" t="n">
-        <v>69.65</v>
+        <v>87.34</v>
       </c>
     </row>
     <row r="18">
@@ -1140,10 +1140,10 @@
         <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>537052</v>
+        <v>293735</v>
       </c>
       <c r="G18" t="n">
-        <v>23.04</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="19">
@@ -1163,10 +1163,10 @@
         <v>27</v>
       </c>
       <c r="F19" t="n">
-        <v>170595</v>
+        <v>23265</v>
       </c>
       <c r="G19" t="n">
-        <v>7.32</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="20">
@@ -1186,10 +1186,10 @@
         <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>1024906</v>
+        <v>249820</v>
       </c>
       <c r="G20" t="n">
-        <v>56.14</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="21">
@@ -1209,10 +1209,10 @@
         <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>454811</v>
+        <v>268126</v>
       </c>
       <c r="G21" t="n">
-        <v>24.91</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="22">
@@ -1232,10 +1232,10 @@
         <v>27</v>
       </c>
       <c r="F22" t="n">
-        <v>346060</v>
+        <v>152209</v>
       </c>
       <c r="G22" t="n">
-        <v>18.95</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="23">
@@ -1255,10 +1255,10 @@
         <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>437659</v>
+        <v>1042050</v>
       </c>
       <c r="G23" t="n">
-        <v>17.67</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="24">
@@ -1278,10 +1278,10 @@
         <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>1545758</v>
+        <v>2777993</v>
       </c>
       <c r="G24" t="n">
-        <v>62.39</v>
+        <v>64.13</v>
       </c>
     </row>
     <row r="25">
@@ -1301,10 +1301,10 @@
         <v>27</v>
       </c>
       <c r="F25" t="n">
-        <v>494010</v>
+        <v>511898</v>
       </c>
       <c r="G25" t="n">
-        <v>19.94</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="26">
@@ -1324,10 +1324,10 @@
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>105282</v>
+        <v>144323</v>
       </c>
       <c r="G26" t="n">
-        <v>4.14</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="27">
@@ -1347,10 +1347,10 @@
         <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>664796</v>
+        <v>1381940</v>
       </c>
       <c r="G27" t="n">
-        <v>26.12</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="28">
@@ -1370,10 +1370,10 @@
         <v>27</v>
       </c>
       <c r="F28" t="n">
-        <v>1775436</v>
+        <v>391570</v>
       </c>
       <c r="G28" t="n">
-        <v>69.75</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="29">
@@ -1393,10 +1393,10 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>162834</v>
+        <v>97530</v>
       </c>
       <c r="G29" t="n">
-        <v>5.82</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="30">
@@ -1416,10 +1416,10 @@
         <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>784877</v>
+        <v>397248</v>
       </c>
       <c r="G30" t="n">
-        <v>28.05</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="31">
@@ -1439,10 +1439,10 @@
         <v>27</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1850553</v>
+        <v>2059727</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>66.13</v>
+        <v>80.63</v>
       </c>
     </row>
     <row r="32">
@@ -1462,10 +1462,10 @@
         <v>29</v>
       </c>
       <c r="F32" t="n">
-        <v>1115383</v>
+        <v>2475735</v>
       </c>
       <c r="G32" t="n">
-        <v>47.84</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="33">
@@ -1485,10 +1485,10 @@
         <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>888837</v>
+        <v>23081</v>
       </c>
       <c r="G33" t="n">
-        <v>38.12</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="34">
@@ -1508,10 +1508,10 @@
         <v>31</v>
       </c>
       <c r="F34" t="n">
-        <v>327181</v>
+        <v>5133</v>
       </c>
       <c r="G34" t="n">
-        <v>14.03</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="F35" t="n">
-        <v>642307</v>
+        <v>538401</v>
       </c>
       <c r="G35" t="n">
-        <v>35.18</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="36">
@@ -1554,10 +1554,10 @@
         <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>960663</v>
+        <v>79442</v>
       </c>
       <c r="G36" t="n">
-        <v>52.62</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="37">
@@ -1577,10 +1577,10 @@
         <v>31</v>
       </c>
       <c r="F37" t="n">
-        <v>222806</v>
+        <v>52312</v>
       </c>
       <c r="G37" t="n">
-        <v>12.2</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="38">
@@ -1600,10 +1600,10 @@
         <v>29</v>
       </c>
       <c r="F38" t="n">
-        <v>1196271</v>
+        <v>4090442</v>
       </c>
       <c r="G38" t="n">
-        <v>48.29</v>
+        <v>94.43</v>
       </c>
     </row>
     <row r="39">
@@ -1623,10 +1623,10 @@
         <v>30</v>
       </c>
       <c r="F39" t="n">
-        <v>982610</v>
+        <v>171264</v>
       </c>
       <c r="G39" t="n">
-        <v>39.66</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="40">
@@ -1646,10 +1646,10 @@
         <v>31</v>
       </c>
       <c r="F40" t="n">
-        <v>298546</v>
+        <v>70236</v>
       </c>
       <c r="G40" t="n">
-        <v>12.05</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="41">
@@ -1669,10 +1669,10 @@
         <v>29</v>
       </c>
       <c r="F41" t="n">
-        <v>419047</v>
+        <v>715709</v>
       </c>
       <c r="G41" t="n">
-        <v>16.46</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="42">
@@ -1692,10 +1692,10 @@
         <v>30</v>
       </c>
       <c r="F42" t="n">
-        <v>520301</v>
+        <v>1190105</v>
       </c>
       <c r="G42" t="n">
-        <v>20.44</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="43">
@@ -1715,10 +1715,10 @@
         <v>31</v>
       </c>
       <c r="F43" t="n">
-        <v>1606167</v>
+        <v>12018</v>
       </c>
       <c r="G43" t="n">
-        <v>63.1</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="44">
@@ -1738,10 +1738,10 @@
         <v>29</v>
       </c>
       <c r="F44" t="n">
-        <v>764830</v>
+        <v>1459720</v>
       </c>
       <c r="G44" t="n">
-        <v>27.33</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="45">
@@ -1761,10 +1761,10 @@
         <v>30</v>
       </c>
       <c r="F45" t="n">
-        <v>691552</v>
+        <v>140238</v>
       </c>
       <c r="G45" t="n">
-        <v>24.71</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="46">
@@ -1784,10 +1784,10 @@
         <v>31</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1341882</v>
+        <v>954548</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>47.95</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="47">
@@ -1807,10 +1807,10 @@
         <v>33</v>
       </c>
       <c r="F47" t="n">
-        <v>1916293</v>
+        <v>2203991</v>
       </c>
       <c r="G47" t="n">
-        <v>82.19</v>
+        <v>88.02</v>
       </c>
     </row>
     <row r="48">
@@ -1830,10 +1830,10 @@
         <v>34</v>
       </c>
       <c r="F48" t="n">
-        <v>129655</v>
+        <v>133181</v>
       </c>
       <c r="G48" t="n">
-        <v>5.56</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="49">
@@ -1853,10 +1853,10 @@
         <v>35</v>
       </c>
       <c r="F49" t="n">
-        <v>285454</v>
+        <v>166029</v>
       </c>
       <c r="G49" t="n">
-        <v>12.24</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="50">
@@ -1867,19 +1867,19 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F50" t="n">
-        <v>1234638</v>
+        <v>748</v>
       </c>
       <c r="G50" t="n">
-        <v>67.62</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="51">
@@ -1893,16 +1893,16 @@
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F51" t="n">
-        <v>258591</v>
+        <v>347194</v>
       </c>
       <c r="G51" t="n">
-        <v>14.16</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="52">
@@ -1916,16 +1916,16 @@
         <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>332548</v>
+        <v>127915</v>
       </c>
       <c r="G52" t="n">
-        <v>18.21</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="53">
@@ -1936,19 +1936,19 @@
         <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>1119553</v>
+        <v>195047</v>
       </c>
       <c r="G53" t="n">
-        <v>45.19</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="54">
@@ -1962,16 +1962,16 @@
         <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F54" t="n">
-        <v>434883</v>
+        <v>1857321</v>
       </c>
       <c r="G54" t="n">
-        <v>17.55</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="55">
@@ -1985,16 +1985,16 @@
         <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>922991</v>
+        <v>686236</v>
       </c>
       <c r="G55" t="n">
-        <v>37.26</v>
+        <v>15.84</v>
       </c>
     </row>
     <row r="56">
@@ -2005,19 +2005,19 @@
         <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>637930</v>
+        <v>1788384</v>
       </c>
       <c r="G56" t="n">
-        <v>25.06</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="57">
@@ -2031,16 +2031,16 @@
         <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F57" t="n">
-        <v>673803</v>
+        <v>498917</v>
       </c>
       <c r="G57" t="n">
-        <v>26.47</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="58">
@@ -2054,16 +2054,16 @@
         <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>1233783</v>
+        <v>1051292</v>
       </c>
       <c r="G58" t="n">
-        <v>48.47</v>
+        <v>54.82</v>
       </c>
     </row>
     <row r="59">
@@ -2074,19 +2074,19 @@
         <v>32</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>459012</v>
+        <v>352133</v>
       </c>
       <c r="G59" t="n">
-        <v>16.4</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="60">
@@ -2097,19 +2097,19 @@
         <v>32</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E60" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>1362005</v>
+        <v>15491</v>
       </c>
       <c r="G60" t="n">
-        <v>48.67</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="61">
@@ -2123,62 +2123,62 @@
         <v>23</v>
       </c>
       <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" t="n">
+        <v>460001</v>
+      </c>
+      <c r="G61" t="n">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" t="n">
+        <v>860314</v>
+      </c>
+      <c r="G62" t="n">
+        <v>33.68</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E63" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F61" t="n">
-        <v>961008</v>
-      </c>
-      <c r="G61" t="n">
-        <v>34.34</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>16239</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" t="s">
-        <v>38</v>
-      </c>
-      <c r="C63" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" t="s">
-        <v>39</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1810170</v>
-      </c>
-      <c r="G63" t="n">
-        <v>77.64</v>
+      <c r="F63" s="2" t="n">
+        <v>1234191</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>48.31</v>
       </c>
     </row>
     <row r="64">
@@ -2192,16 +2192,16 @@
         <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>356432</v>
+        <v>1186602</v>
       </c>
       <c r="G64" t="n">
-        <v>15.29</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="65">
@@ -2215,16 +2215,16 @@
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F65" t="n">
-        <v>164799</v>
+        <v>1194065</v>
       </c>
       <c r="G65" t="n">
-        <v>7.07</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="66">
@@ -2235,19 +2235,19 @@
         <v>38</v>
       </c>
       <c r="C66" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F66" t="n">
-        <v>889125</v>
+        <v>123283</v>
       </c>
       <c r="G66" t="n">
-        <v>48.7</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="67">
@@ -2261,16 +2261,16 @@
         <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F67" t="n">
-        <v>703170</v>
+        <v>136011</v>
       </c>
       <c r="G67" t="n">
-        <v>38.51</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="68">
@@ -2284,16 +2284,16 @@
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F68" t="n">
-        <v>233482</v>
+        <v>344068</v>
       </c>
       <c r="G68" t="n">
-        <v>12.79</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="69">
@@ -2304,19 +2304,19 @@
         <v>38</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F69" t="n">
-        <v>327539</v>
+        <v>190076</v>
       </c>
       <c r="G69" t="n">
-        <v>13.22</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="70">
@@ -2330,16 +2330,16 @@
         <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F70" t="n">
-        <v>1655726</v>
+        <v>146213</v>
       </c>
       <c r="G70" t="n">
-        <v>66.83</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="71">
@@ -2353,16 +2353,16 @@
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F71" t="n">
-        <v>494162</v>
+        <v>3188657</v>
       </c>
       <c r="G71" t="n">
-        <v>19.95</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="72">
@@ -2373,19 +2373,19 @@
         <v>38</v>
       </c>
       <c r="C72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F72" t="n">
-        <v>177324</v>
+        <v>997072</v>
       </c>
       <c r="G72" t="n">
-        <v>6.97</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="73">
@@ -2399,16 +2399,16 @@
         <v>22</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>969733</v>
+        <v>52457</v>
       </c>
       <c r="G73" t="n">
-        <v>38.1</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="74">
@@ -2422,16 +2422,16 @@
         <v>22</v>
       </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F74" t="n">
-        <v>1398457</v>
+        <v>586093</v>
       </c>
       <c r="G74" t="n">
-        <v>54.94</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="75">
@@ -2442,19 +2442,19 @@
         <v>38</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F75" t="n">
-        <v>160420</v>
+        <v>1279282</v>
       </c>
       <c r="G75" t="n">
-        <v>5.73</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="76">
@@ -2468,62 +2468,62 @@
         <v>23</v>
       </c>
       <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s">
+        <v>39</v>
+      </c>
+      <c r="F76" t="n">
+        <v>65991</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" t="s">
         <v>16</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E77" t="s">
         <v>40</v>
       </c>
-      <c r="F76" t="n">
-        <v>395749</v>
-      </c>
-      <c r="G76" t="n">
-        <v>14.14</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B77" s="2" t="s">
+      <c r="F77" t="n">
+        <v>501204</v>
+      </c>
+      <c r="G77" t="n">
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F77" s="2" t="n">
-        <v>2242095</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>80.12</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" t="s">
-        <v>42</v>
-      </c>
-      <c r="C78" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" t="s">
-        <v>43</v>
-      </c>
-      <c r="E78" t="s">
-        <v>44</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1640366</v>
-      </c>
-      <c r="G78" t="n">
-        <v>70.36</v>
+      <c r="F78" s="2" t="n">
+        <v>1987310</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>77.8</v>
       </c>
     </row>
     <row r="79">
@@ -2537,16 +2537,16 @@
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F79" t="n">
-        <v>691036</v>
+        <v>1380968</v>
       </c>
       <c r="G79" t="n">
-        <v>29.64</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="80">
@@ -2557,19 +2557,19 @@
         <v>42</v>
       </c>
       <c r="C80" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F80" t="n">
-        <v>448171</v>
+        <v>1122982</v>
       </c>
       <c r="G80" t="n">
-        <v>24.55</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="81">
@@ -2583,16 +2583,16 @@
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E81" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F81" t="n">
-        <v>1377606</v>
+        <v>555959</v>
       </c>
       <c r="G81" t="n">
-        <v>75.45</v>
+        <v>82.96</v>
       </c>
     </row>
     <row r="82">
@@ -2603,19 +2603,19 @@
         <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F82" t="n">
-        <v>1716814</v>
+        <v>114197</v>
       </c>
       <c r="G82" t="n">
-        <v>69.3</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="83">
@@ -2629,16 +2629,16 @@
         <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F83" t="n">
-        <v>760613</v>
+        <v>1698685</v>
       </c>
       <c r="G83" t="n">
-        <v>30.7</v>
+        <v>39.21</v>
       </c>
     </row>
     <row r="84">
@@ -2649,19 +2649,19 @@
         <v>42</v>
       </c>
       <c r="C84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F84" t="n">
-        <v>1179664</v>
+        <v>2633256</v>
       </c>
       <c r="G84" t="n">
-        <v>46.34</v>
+        <v>60.79</v>
       </c>
     </row>
     <row r="85">
@@ -2675,16 +2675,16 @@
         <v>22</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F85" t="n">
-        <v>1365851</v>
+        <v>962913</v>
       </c>
       <c r="G85" t="n">
-        <v>53.66</v>
+        <v>50.21</v>
       </c>
     </row>
     <row r="86">
@@ -2695,65 +2695,65 @@
         <v>42</v>
       </c>
       <c r="C86" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" t="n">
+        <v>954919</v>
+      </c>
+      <c r="G86" t="n">
+        <v>49.79</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" t="s">
+        <v>42</v>
+      </c>
+      <c r="C87" t="s">
         <v>23</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D87" t="s">
         <v>43</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E87" t="s">
         <v>44</v>
       </c>
-      <c r="F86" t="n">
-        <v>753241</v>
-      </c>
-      <c r="G86" t="n">
-        <v>26.92</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B87" s="2" t="s">
+      <c r="F87" t="n">
+        <v>1139730</v>
+      </c>
+      <c r="G87" t="n">
+        <v>44.62</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="2" t="s">
+      <c r="D88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F87" s="2" t="n">
-        <v>2045024</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>73.08</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>11</v>
-      </c>
-      <c r="B88" t="s">
-        <v>46</v>
-      </c>
-      <c r="C88" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" t="s">
-        <v>14</v>
-      </c>
-      <c r="E88" t="s">
-        <v>47</v>
-      </c>
-      <c r="F88" t="n">
-        <v>893208</v>
-      </c>
-      <c r="G88" t="n">
-        <v>38.31</v>
+      <c r="F88" s="2" t="n">
+        <v>1414776</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>55.38</v>
       </c>
     </row>
     <row r="89">
@@ -2767,16 +2767,16 @@
         <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F89" t="n">
-        <v>1219173</v>
+        <v>141967</v>
       </c>
       <c r="G89" t="n">
-        <v>52.29</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="90">
@@ -2790,16 +2790,16 @@
         <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F90" t="n">
-        <v>219020</v>
+        <v>1524073</v>
       </c>
       <c r="G90" t="n">
-        <v>9.39</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="91">
@@ -2810,19 +2810,19 @@
         <v>46</v>
       </c>
       <c r="C91" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D91" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E91" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>278972</v>
+        <v>837910</v>
       </c>
       <c r="G91" t="n">
-        <v>15.28</v>
+        <v>33.46</v>
       </c>
     </row>
     <row r="92">
@@ -2836,16 +2836,16 @@
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F92" t="n">
-        <v>102081</v>
+        <v>670155</v>
       </c>
       <c r="G92" t="n">
-        <v>5.59</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -2856,19 +2856,19 @@
         <v>46</v>
       </c>
       <c r="C93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F93" t="n">
-        <v>1444724</v>
+        <v>71577</v>
       </c>
       <c r="G93" t="n">
-        <v>79.13</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="94">
@@ -2882,16 +2882,16 @@
         <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F94" t="n">
-        <v>1291034</v>
+        <v>1851898</v>
       </c>
       <c r="G94" t="n">
-        <v>52.11</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="95">
@@ -2905,16 +2905,16 @@
         <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F95" t="n">
-        <v>605018</v>
+        <v>2408466</v>
       </c>
       <c r="G95" t="n">
-        <v>24.42</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="96">
@@ -2925,19 +2925,19 @@
         <v>46</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F96" t="n">
-        <v>581375</v>
+        <v>34104</v>
       </c>
       <c r="G96" t="n">
-        <v>23.47</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="97">
@@ -2951,16 +2951,16 @@
         <v>22</v>
       </c>
       <c r="D97" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E97" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F97" t="n">
-        <v>194506</v>
+        <v>1148759</v>
       </c>
       <c r="G97" t="n">
-        <v>7.64</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="98">
@@ -2974,16 +2974,16 @@
         <v>22</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F98" t="n">
-        <v>1859384</v>
+        <v>734969</v>
       </c>
       <c r="G98" t="n">
-        <v>73.05</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="99">
@@ -2994,19 +2994,19 @@
         <v>46</v>
       </c>
       <c r="C99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F99" t="n">
-        <v>491625</v>
+        <v>63694</v>
       </c>
       <c r="G99" t="n">
-        <v>19.31</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="100">
@@ -3020,62 +3020,62 @@
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F100" t="n">
-        <v>694751</v>
+        <v>1479310</v>
       </c>
       <c r="G100" t="n">
-        <v>24.83</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
-        <v>11</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="A101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D101" t="s">
-        <v>16</v>
-      </c>
-      <c r="E101" t="s">
-        <v>48</v>
-      </c>
-      <c r="F101" t="n">
-        <v>157795</v>
-      </c>
-      <c r="G101" t="n">
-        <v>5.64</v>
+      <c r="D101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>1011502</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>39.6</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>1945718</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>69.53</v>
+      <c r="A102" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" t="s">
+        <v>50</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
+        <v>51</v>
+      </c>
+      <c r="F102" t="n">
+        <v>739963</v>
+      </c>
+      <c r="G102" t="n">
+        <v>29.55</v>
       </c>
     </row>
     <row r="103">
@@ -3089,16 +3089,16 @@
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>929131</v>
+        <v>779061</v>
       </c>
       <c r="G103" t="n">
-        <v>39.85</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="104">
@@ -3112,16 +3112,16 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F104" t="n">
-        <v>824290</v>
+        <v>984925</v>
       </c>
       <c r="G104" t="n">
-        <v>35.36</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="105">
@@ -3132,19 +3132,19 @@
         <v>50</v>
       </c>
       <c r="C105" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F105" t="n">
-        <v>577981</v>
+        <v>351974</v>
       </c>
       <c r="G105" t="n">
-        <v>24.79</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="106">
@@ -3158,16 +3158,16 @@
         <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E106" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F106" t="n">
-        <v>217881</v>
+        <v>318181</v>
       </c>
       <c r="G106" t="n">
-        <v>11.93</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="107">
@@ -3178,19 +3178,19 @@
         <v>50</v>
       </c>
       <c r="C107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E107" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F107" t="n">
-        <v>544893</v>
+        <v>867646</v>
       </c>
       <c r="G107" t="n">
-        <v>29.84</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="108">
@@ -3201,19 +3201,19 @@
         <v>50</v>
       </c>
       <c r="C108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D108" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E108" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F108" t="n">
-        <v>1063003</v>
+        <v>1049676</v>
       </c>
       <c r="G108" t="n">
-        <v>58.22</v>
+        <v>24.23</v>
       </c>
     </row>
     <row r="109">
@@ -3227,16 +3227,16 @@
         <v>21</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E109" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F109" t="n">
-        <v>899780</v>
+        <v>2414618</v>
       </c>
       <c r="G109" t="n">
-        <v>36.32</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="110">
@@ -3247,19 +3247,19 @@
         <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F110" t="n">
-        <v>839611</v>
+        <v>465684</v>
       </c>
       <c r="G110" t="n">
-        <v>33.89</v>
+        <v>24.28</v>
       </c>
     </row>
     <row r="111">
@@ -3270,19 +3270,19 @@
         <v>50</v>
       </c>
       <c r="C111" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E111" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F111" t="n">
-        <v>738036</v>
+        <v>727364</v>
       </c>
       <c r="G111" t="n">
-        <v>29.79</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="112">
@@ -3296,16 +3296,16 @@
         <v>22</v>
       </c>
       <c r="D112" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E112" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F112" t="n">
-        <v>677060</v>
+        <v>724785</v>
       </c>
       <c r="G112" t="n">
-        <v>26.6</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="113">
@@ -3316,19 +3316,19 @@
         <v>50</v>
       </c>
       <c r="C113" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F113" t="n">
-        <v>859510</v>
+        <v>600847</v>
       </c>
       <c r="G113" t="n">
-        <v>33.77</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="114">
@@ -3339,88 +3339,88 @@
         <v>50</v>
       </c>
       <c r="C114" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
+        <v>52</v>
+      </c>
+      <c r="F114" t="n">
+        <v>770260</v>
+      </c>
+      <c r="G114" t="n">
+        <v>30.15</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E115" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F114" t="n">
-        <v>1008945</v>
-      </c>
-      <c r="G114" t="n">
-        <v>39.64</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>11</v>
-      </c>
-      <c r="B115" t="s">
-        <v>50</v>
-      </c>
-      <c r="C115" t="s">
-        <v>23</v>
-      </c>
-      <c r="D115" t="s">
-        <v>14</v>
-      </c>
-      <c r="E115" t="s">
-        <v>51</v>
-      </c>
-      <c r="F115" t="n">
-        <v>463296</v>
-      </c>
-      <c r="G115" t="n">
-        <v>16.56</v>
+      <c r="F115" s="2" t="n">
+        <v>1183399</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46.33</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D116" t="s">
+        <v>14</v>
+      </c>
+      <c r="E116" t="s">
+        <v>56</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1572804</v>
+      </c>
+      <c r="G116" t="n">
+        <v>62.81</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>54</v>
+      </c>
+      <c r="B117" t="s">
+        <v>55</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
         <v>16</v>
       </c>
-      <c r="E116" t="s">
-        <v>52</v>
-      </c>
-      <c r="F116" t="n">
-        <v>876724</v>
-      </c>
-      <c r="G116" t="n">
-        <v>31.33</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>1458244</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>52.11</v>
+      <c r="E117" t="s">
+        <v>57</v>
+      </c>
+      <c r="F117" t="n">
+        <v>931146</v>
+      </c>
+      <c r="G117" t="n">
+        <v>37.19</v>
       </c>
     </row>
     <row r="118">
@@ -3431,7 +3431,7 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D118" t="s">
         <v>14</v>
@@ -3440,10 +3440,10 @@
         <v>56</v>
       </c>
       <c r="F118" t="n">
-        <v>1421400</v>
+        <v>326428</v>
       </c>
       <c r="G118" t="n">
-        <v>60.97</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="119">
@@ -3454,7 +3454,7 @@
         <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D119" t="s">
         <v>16</v>
@@ -3463,10 +3463,10 @@
         <v>57</v>
       </c>
       <c r="F119" t="n">
-        <v>910002</v>
+        <v>343728</v>
       </c>
       <c r="G119" t="n">
-        <v>39.03</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="120">
@@ -3477,7 +3477,7 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D120" t="s">
         <v>14</v>
@@ -3486,10 +3486,10 @@
         <v>56</v>
       </c>
       <c r="F120" t="n">
-        <v>1049483</v>
+        <v>2231126</v>
       </c>
       <c r="G120" t="n">
-        <v>57.48</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="121">
@@ -3500,7 +3500,7 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D121" t="s">
         <v>16</v>
@@ -3509,10 +3509,10 @@
         <v>57</v>
       </c>
       <c r="F121" t="n">
-        <v>776294</v>
+        <v>2100815</v>
       </c>
       <c r="G121" t="n">
-        <v>42.52</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="122">
@@ -3523,7 +3523,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D122" t="s">
         <v>14</v>
@@ -3532,10 +3532,10 @@
         <v>56</v>
       </c>
       <c r="F122" t="n">
-        <v>1216100</v>
+        <v>774871</v>
       </c>
       <c r="G122" t="n">
-        <v>49.09</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="123">
@@ -3546,7 +3546,7 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D123" t="s">
         <v>16</v>
@@ -3555,10 +3555,10 @@
         <v>57</v>
       </c>
       <c r="F123" t="n">
-        <v>1261327</v>
+        <v>1142962</v>
       </c>
       <c r="G123" t="n">
-        <v>50.91</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="124">
@@ -3569,7 +3569,7 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D124" t="s">
         <v>14</v>
@@ -3578,33 +3578,33 @@
         <v>56</v>
       </c>
       <c r="F124" t="n">
-        <v>1043077</v>
+        <v>975224</v>
       </c>
       <c r="G124" t="n">
-        <v>40.98</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
-        <v>54</v>
-      </c>
-      <c r="B125" t="s">
+      <c r="A125" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C125" t="s">
-        <v>22</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="C125" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D125" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F125" t="n">
-        <v>1502438</v>
-      </c>
-      <c r="G125" t="n">
-        <v>59.02</v>
+      <c r="F125" s="2" t="n">
+        <v>1579281</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>61.82</v>
       </c>
     </row>
     <row r="126">
@@ -3612,45 +3612,45 @@
         <v>54</v>
       </c>
       <c r="B126" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C126" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D126" t="s">
         <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F126" t="n">
-        <v>1150391</v>
+        <v>328389</v>
       </c>
       <c r="G126" t="n">
-        <v>41.11</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D127" s="2" t="s">
+      <c r="A127" t="s">
+        <v>54</v>
+      </c>
+      <c r="B127" t="s">
+        <v>58</v>
+      </c>
+      <c r="C127" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" t="s">
         <v>16</v>
       </c>
-      <c r="E127" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>1647873</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>58.89</v>
+      <c r="E127" t="s">
+        <v>60</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1046717</v>
+      </c>
+      <c r="G127" t="n">
+        <v>41.8</v>
       </c>
     </row>
     <row r="128">
@@ -3664,16 +3664,16 @@
         <v>13</v>
       </c>
       <c r="D128" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E128" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F128" t="n">
-        <v>361741</v>
+        <v>1118470</v>
       </c>
       <c r="G128" t="n">
-        <v>15.52</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="129">
@@ -3687,16 +3687,16 @@
         <v>13</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E129" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F129" t="n">
-        <v>1031869</v>
+        <v>6684</v>
       </c>
       <c r="G129" t="n">
-        <v>44.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="130">
@@ -3710,16 +3710,16 @@
         <v>13</v>
       </c>
       <c r="D130" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="E130" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F130" t="n">
-        <v>926790</v>
+        <v>3690</v>
       </c>
       <c r="G130" t="n">
-        <v>39.75</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="131">
@@ -3730,19 +3730,19 @@
         <v>58</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F131" t="n">
-        <v>6637</v>
+        <v>107284</v>
       </c>
       <c r="G131" t="n">
-        <v>0.28</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="132">
@@ -3753,19 +3753,19 @@
         <v>58</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E132" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F132" t="n">
-        <v>4363</v>
+        <v>293966</v>
       </c>
       <c r="G132" t="n">
-        <v>0.19</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="133">
@@ -3779,16 +3779,16 @@
         <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E133" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F133" t="n">
-        <v>141754</v>
+        <v>265195</v>
       </c>
       <c r="G133" t="n">
-        <v>7.76</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="134">
@@ -3802,16 +3802,16 @@
         <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E134" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F134" t="n">
-        <v>644571</v>
+        <v>1878</v>
       </c>
       <c r="G134" t="n">
-        <v>35.3</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="135">
@@ -3825,16 +3825,16 @@
         <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="E135" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F135" t="n">
-        <v>1034456</v>
+        <v>1832</v>
       </c>
       <c r="G135" t="n">
-        <v>56.66</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="136">
@@ -3845,19 +3845,19 @@
         <v>58</v>
       </c>
       <c r="C136" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D136" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F136" t="n">
-        <v>4003</v>
+        <v>375549</v>
       </c>
       <c r="G136" t="n">
-        <v>0.22</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="137">
@@ -3868,19 +3868,19 @@
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D137" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E137" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F137" t="n">
-        <v>993</v>
+        <v>1708369</v>
       </c>
       <c r="G137" t="n">
-        <v>0.05</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="138">
@@ -3894,16 +3894,16 @@
         <v>21</v>
       </c>
       <c r="D138" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E138" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F138" t="n">
-        <v>291453</v>
+        <v>2232762</v>
       </c>
       <c r="G138" t="n">
-        <v>11.76</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="139">
@@ -3917,16 +3917,16 @@
         <v>21</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E139" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F139" t="n">
-        <v>1110153</v>
+        <v>9661</v>
       </c>
       <c r="G139" t="n">
-        <v>44.81</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="140">
@@ -3940,16 +3940,16 @@
         <v>21</v>
       </c>
       <c r="D140" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="E140" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F140" t="n">
-        <v>1064421</v>
+        <v>5600</v>
       </c>
       <c r="G140" t="n">
-        <v>42.96</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="141">
@@ -3960,19 +3960,19 @@
         <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D141" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F141" t="n">
-        <v>6577</v>
+        <v>242122</v>
       </c>
       <c r="G141" t="n">
-        <v>0.27</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="142">
@@ -3983,19 +3983,19 @@
         <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D142" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E142" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F142" t="n">
-        <v>4822</v>
+        <v>814250</v>
       </c>
       <c r="G142" t="n">
-        <v>0.19</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="143">
@@ -4009,16 +4009,16 @@
         <v>22</v>
       </c>
       <c r="D143" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E143" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F143" t="n">
-        <v>314501</v>
+        <v>854139</v>
       </c>
       <c r="G143" t="n">
-        <v>12.36</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="144">
@@ -4032,16 +4032,16 @@
         <v>22</v>
       </c>
       <c r="D144" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E144" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F144" t="n">
-        <v>1104682</v>
+        <v>4609</v>
       </c>
       <c r="G144" t="n">
-        <v>43.4</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="145">
@@ -4055,16 +4055,16 @@
         <v>22</v>
       </c>
       <c r="D145" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="E145" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F145" t="n">
-        <v>1112990</v>
+        <v>2712</v>
       </c>
       <c r="G145" t="n">
-        <v>43.72</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="146">
@@ -4075,19 +4075,19 @@
         <v>58</v>
       </c>
       <c r="C146" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D146" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="E146" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F146" t="n">
-        <v>8204</v>
+        <v>305795</v>
       </c>
       <c r="G146" t="n">
-        <v>0.32</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="147">
@@ -4098,19 +4098,19 @@
         <v>58</v>
       </c>
       <c r="C147" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D147" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E147" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F147" t="n">
-        <v>5139</v>
+        <v>1113605</v>
       </c>
       <c r="G147" t="n">
-        <v>0.2</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="148">
@@ -4124,16 +4124,16 @@
         <v>23</v>
       </c>
       <c r="D148" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E148" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F148" t="n">
-        <v>249690</v>
+        <v>1125121</v>
       </c>
       <c r="G148" t="n">
-        <v>8.92</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="149">
@@ -4147,39 +4147,39 @@
         <v>23</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E149" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F149" t="n">
-        <v>1085632</v>
+        <v>5893</v>
       </c>
       <c r="G149" t="n">
-        <v>38.8</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s">
-        <v>54</v>
-      </c>
-      <c r="B150" t="s">
+      <c r="A150" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D150" t="s">
-        <v>18</v>
-      </c>
-      <c r="E150" t="s">
-        <v>61</v>
-      </c>
-      <c r="F150" t="n">
-        <v>1457030</v>
-      </c>
-      <c r="G150" t="n">
-        <v>52.07</v>
+      <c r="D150" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>4091</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="151">
@@ -4187,45 +4187,45 @@
         <v>54</v>
       </c>
       <c r="B151" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C151" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D151" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F151" t="n">
-        <v>3304</v>
+        <v>684107</v>
       </c>
       <c r="G151" t="n">
-        <v>0.12</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>2608</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>0.09</v>
+      <c r="A152" t="s">
+        <v>54</v>
+      </c>
+      <c r="B152" t="s">
+        <v>66</v>
+      </c>
+      <c r="C152" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" t="s">
+        <v>16</v>
+      </c>
+      <c r="E152" t="s">
+        <v>68</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1203194</v>
+      </c>
+      <c r="G152" t="n">
+        <v>48.05</v>
       </c>
     </row>
     <row r="153">
@@ -4239,16 +4239,16 @@
         <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E153" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F153" t="n">
-        <v>672110</v>
+        <v>616649</v>
       </c>
       <c r="G153" t="n">
-        <v>28.83</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="154">
@@ -4259,19 +4259,19 @@
         <v>66</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F154" t="n">
-        <v>1082754</v>
+        <v>171587</v>
       </c>
       <c r="G154" t="n">
-        <v>46.44</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="155">
@@ -4282,19 +4282,19 @@
         <v>66</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E155" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F155" t="n">
-        <v>576538</v>
+        <v>350755</v>
       </c>
       <c r="G155" t="n">
-        <v>24.73</v>
+        <v>52.34</v>
       </c>
     </row>
     <row r="156">
@@ -4308,16 +4308,16 @@
         <v>20</v>
       </c>
       <c r="D156" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E156" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F156" t="n">
-        <v>536507</v>
+        <v>147813</v>
       </c>
       <c r="G156" t="n">
-        <v>29.39</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="157">
@@ -4328,19 +4328,19 @@
         <v>66</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D157" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F157" t="n">
-        <v>948025</v>
+        <v>1315309</v>
       </c>
       <c r="G157" t="n">
-        <v>51.92</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="158">
@@ -4351,19 +4351,19 @@
         <v>66</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D158" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E158" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F158" t="n">
-        <v>341244</v>
+        <v>2247623</v>
       </c>
       <c r="G158" t="n">
-        <v>18.69</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="159">
@@ -4377,16 +4377,16 @@
         <v>21</v>
       </c>
       <c r="D159" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E159" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F159" t="n">
-        <v>743471</v>
+        <v>769009</v>
       </c>
       <c r="G159" t="n">
-        <v>30.01</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="160">
@@ -4397,19 +4397,19 @@
         <v>66</v>
       </c>
       <c r="C160" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F160" t="n">
-        <v>1221660</v>
+        <v>385897</v>
       </c>
       <c r="G160" t="n">
-        <v>49.31</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="161">
@@ -4420,19 +4420,19 @@
         <v>66</v>
       </c>
       <c r="C161" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D161" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E161" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F161" t="n">
-        <v>512297</v>
+        <v>1067480</v>
       </c>
       <c r="G161" t="n">
-        <v>20.68</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="162">
@@ -4446,16 +4446,16 @@
         <v>22</v>
       </c>
       <c r="D162" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E162" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F162" t="n">
-        <v>569993</v>
+        <v>464455</v>
       </c>
       <c r="G162" t="n">
-        <v>22.39</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="163">
@@ -4466,19 +4466,19 @@
         <v>66</v>
       </c>
       <c r="C163" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F163" t="n">
-        <v>1384802</v>
+        <v>425921</v>
       </c>
       <c r="G163" t="n">
-        <v>54.4</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="164">
@@ -4489,42 +4489,42 @@
         <v>66</v>
       </c>
       <c r="C164" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D164" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" t="s">
+        <v>68</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1509153</v>
+      </c>
+      <c r="G164" t="n">
+        <v>59.08</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E165" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F164" t="n">
-        <v>590720</v>
-      </c>
-      <c r="G164" t="n">
-        <v>23.21</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>54</v>
-      </c>
-      <c r="B165" t="s">
-        <v>66</v>
-      </c>
-      <c r="C165" t="s">
-        <v>23</v>
-      </c>
-      <c r="D165" t="s">
-        <v>14</v>
-      </c>
-      <c r="E165" t="s">
-        <v>67</v>
-      </c>
-      <c r="F165" t="n">
-        <v>460742</v>
-      </c>
-      <c r="G165" t="n">
-        <v>16.47</v>
+      <c r="F165" s="2" t="n">
+        <v>619431</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>24.25</v>
       </c>
     </row>
     <row r="166">
@@ -4532,45 +4532,45 @@
         <v>54</v>
       </c>
       <c r="B166" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C166" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D166" t="s">
+        <v>14</v>
+      </c>
+      <c r="E166" t="s">
+        <v>71</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1022724</v>
+      </c>
+      <c r="G166" t="n">
+        <v>40.84</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>54</v>
+      </c>
+      <c r="B167" t="s">
+        <v>70</v>
+      </c>
+      <c r="C167" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" t="s">
         <v>16</v>
       </c>
-      <c r="E166" t="s">
-        <v>68</v>
-      </c>
-      <c r="F166" t="n">
-        <v>1740965</v>
-      </c>
-      <c r="G166" t="n">
-        <v>62.22</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F167" s="2" t="n">
-        <v>596558</v>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>21.32</v>
+      <c r="E167" t="s">
+        <v>72</v>
+      </c>
+      <c r="F167" t="n">
+        <v>946576</v>
+      </c>
+      <c r="G167" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="168">
@@ -4584,16 +4584,16 @@
         <v>13</v>
       </c>
       <c r="D168" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E168" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F168" t="n">
-        <v>1097073</v>
+        <v>534649</v>
       </c>
       <c r="G168" t="n">
-        <v>47.06</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="169">
@@ -4604,19 +4604,19 @@
         <v>70</v>
       </c>
       <c r="C169" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F169" t="n">
-        <v>860774</v>
+        <v>323836</v>
       </c>
       <c r="G169" t="n">
-        <v>36.92</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="170">
@@ -4627,19 +4627,19 @@
         <v>70</v>
       </c>
       <c r="C170" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D170" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E170" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F170" t="n">
-        <v>373554</v>
+        <v>241856</v>
       </c>
       <c r="G170" t="n">
-        <v>16.02</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="171">
@@ -4653,16 +4653,16 @@
         <v>20</v>
       </c>
       <c r="D171" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E171" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F171" t="n">
-        <v>528191</v>
+        <v>104463</v>
       </c>
       <c r="G171" t="n">
-        <v>28.93</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="172">
@@ -4673,19 +4673,19 @@
         <v>70</v>
       </c>
       <c r="C172" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D172" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F172" t="n">
-        <v>728483</v>
+        <v>1547811</v>
       </c>
       <c r="G172" t="n">
-        <v>39.9</v>
+        <v>35.73</v>
       </c>
     </row>
     <row r="173">
@@ -4696,19 +4696,19 @@
         <v>70</v>
       </c>
       <c r="C173" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D173" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E173" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F173" t="n">
-        <v>569102</v>
+        <v>1791442</v>
       </c>
       <c r="G173" t="n">
-        <v>31.17</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="174">
@@ -4722,16 +4722,16 @@
         <v>21</v>
       </c>
       <c r="D174" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E174" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F174" t="n">
-        <v>1117253</v>
+        <v>992688</v>
       </c>
       <c r="G174" t="n">
-        <v>45.1</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="175">
@@ -4742,19 +4742,19 @@
         <v>70</v>
       </c>
       <c r="C175" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E175" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F175" t="n">
-        <v>958085</v>
+        <v>827930</v>
       </c>
       <c r="G175" t="n">
-        <v>38.67</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="176">
@@ -4765,19 +4765,19 @@
         <v>70</v>
       </c>
       <c r="C176" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D176" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E176" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F176" t="n">
-        <v>402089</v>
+        <v>772115</v>
       </c>
       <c r="G176" t="n">
-        <v>16.23</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="177">
@@ -4791,16 +4791,16 @@
         <v>22</v>
       </c>
       <c r="D177" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E177" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F177" t="n">
-        <v>1143745</v>
+        <v>317788</v>
       </c>
       <c r="G177" t="n">
-        <v>44.93</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="178">
@@ -4811,19 +4811,19 @@
         <v>70</v>
       </c>
       <c r="C178" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E178" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F178" t="n">
-        <v>1038375</v>
+        <v>1139363</v>
       </c>
       <c r="G178" t="n">
-        <v>40.79</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="179">
@@ -4834,42 +4834,42 @@
         <v>70</v>
       </c>
       <c r="C179" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D179" t="s">
+        <v>16</v>
+      </c>
+      <c r="E179" t="s">
+        <v>72</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1054088</v>
+      </c>
+      <c r="G179" t="n">
+        <v>41.26</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E180" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F179" t="n">
-        <v>363395</v>
-      </c>
-      <c r="G179" t="n">
-        <v>14.28</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>54</v>
-      </c>
-      <c r="B180" t="s">
-        <v>70</v>
-      </c>
-      <c r="C180" t="s">
-        <v>23</v>
-      </c>
-      <c r="D180" t="s">
-        <v>14</v>
-      </c>
-      <c r="E180" t="s">
-        <v>71</v>
-      </c>
-      <c r="F180" t="n">
-        <v>975404</v>
-      </c>
-      <c r="G180" t="n">
-        <v>34.86</v>
+      <c r="F180" s="2" t="n">
+        <v>361055</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>14.13</v>
       </c>
     </row>
     <row r="181">
@@ -4877,45 +4877,45 @@
         <v>54</v>
       </c>
       <c r="B181" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C181" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D181" t="s">
+        <v>14</v>
+      </c>
+      <c r="E181" t="s">
+        <v>75</v>
+      </c>
+      <c r="F181" t="n">
+        <v>330607</v>
+      </c>
+      <c r="G181" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>54</v>
+      </c>
+      <c r="B182" t="s">
+        <v>74</v>
+      </c>
+      <c r="C182" t="s">
+        <v>13</v>
+      </c>
+      <c r="D182" t="s">
         <v>16</v>
       </c>
-      <c r="E181" t="s">
-        <v>72</v>
-      </c>
-      <c r="F181" t="n">
-        <v>1220358</v>
-      </c>
-      <c r="G181" t="n">
-        <v>43.61</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F182" s="2" t="n">
-        <v>602503</v>
-      </c>
-      <c r="G182" s="2" t="n">
-        <v>21.53</v>
+      <c r="E182" t="s">
+        <v>76</v>
+      </c>
+      <c r="F182" t="n">
+        <v>890392</v>
+      </c>
+      <c r="G182" t="n">
+        <v>35.56</v>
       </c>
     </row>
     <row r="183">
@@ -4929,16 +4929,16 @@
         <v>13</v>
       </c>
       <c r="D183" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E183" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F183" t="n">
-        <v>339509</v>
+        <v>277256</v>
       </c>
       <c r="G183" t="n">
-        <v>14.56</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="184">
@@ -4952,16 +4952,16 @@
         <v>13</v>
       </c>
       <c r="D184" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E184" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F184" t="n">
-        <v>867578</v>
+        <v>1005695</v>
       </c>
       <c r="G184" t="n">
-        <v>37.21</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="185">
@@ -4972,19 +4972,19 @@
         <v>74</v>
       </c>
       <c r="C185" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D185" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E185" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F185" t="n">
-        <v>304463</v>
+        <v>132636</v>
       </c>
       <c r="G185" t="n">
-        <v>13.06</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="186">
@@ -4995,19 +4995,19 @@
         <v>74</v>
       </c>
       <c r="C186" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="E186" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F186" t="n">
-        <v>819851</v>
+        <v>224278</v>
       </c>
       <c r="G186" t="n">
-        <v>35.17</v>
+        <v>33.47</v>
       </c>
     </row>
     <row r="187">
@@ -5021,16 +5021,16 @@
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E187" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F187" t="n">
-        <v>174761</v>
+        <v>79203</v>
       </c>
       <c r="G187" t="n">
-        <v>9.57</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="188">
@@ -5044,16 +5044,16 @@
         <v>20</v>
       </c>
       <c r="D188" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E188" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F188" t="n">
-        <v>535836</v>
+        <v>234038</v>
       </c>
       <c r="G188" t="n">
-        <v>29.35</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="189">
@@ -5064,19 +5064,19 @@
         <v>74</v>
       </c>
       <c r="C189" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D189" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F189" t="n">
-        <v>94194</v>
+        <v>508786</v>
       </c>
       <c r="G189" t="n">
-        <v>5.16</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="190">
@@ -5087,19 +5087,19 @@
         <v>74</v>
       </c>
       <c r="C190" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D190" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="E190" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F190" t="n">
-        <v>1020986</v>
+        <v>1259056</v>
       </c>
       <c r="G190" t="n">
-        <v>55.92</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="191">
@@ -5113,16 +5113,16 @@
         <v>21</v>
       </c>
       <c r="D191" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E191" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F191" t="n">
-        <v>411599</v>
+        <v>218807</v>
       </c>
       <c r="G191" t="n">
-        <v>16.61</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="192">
@@ -5136,16 +5136,16 @@
         <v>21</v>
       </c>
       <c r="D192" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E192" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F192" t="n">
-        <v>741314</v>
+        <v>2345292</v>
       </c>
       <c r="G192" t="n">
-        <v>29.92</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="193">
@@ -5156,19 +5156,19 @@
         <v>74</v>
       </c>
       <c r="C193" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D193" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F193" t="n">
-        <v>171560</v>
+        <v>277225</v>
       </c>
       <c r="G193" t="n">
-        <v>6.92</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="194">
@@ -5179,19 +5179,19 @@
         <v>74</v>
       </c>
       <c r="C194" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D194" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="E194" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F194" t="n">
-        <v>1152954</v>
+        <v>667504</v>
       </c>
       <c r="G194" t="n">
-        <v>46.54</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="195">
@@ -5205,16 +5205,16 @@
         <v>22</v>
       </c>
       <c r="D195" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E195" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F195" t="n">
-        <v>325589</v>
+        <v>113209</v>
       </c>
       <c r="G195" t="n">
-        <v>12.79</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="196">
@@ -5228,16 +5228,16 @@
         <v>22</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E196" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F196" t="n">
-        <v>748204</v>
+        <v>859895</v>
       </c>
       <c r="G196" t="n">
-        <v>29.39</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="197">
@@ -5248,19 +5248,19 @@
         <v>74</v>
       </c>
       <c r="C197" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D197" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E197" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F197" t="n">
-        <v>114497</v>
+        <v>309317</v>
       </c>
       <c r="G197" t="n">
-        <v>4.5</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="198">
@@ -5271,19 +5271,19 @@
         <v>74</v>
       </c>
       <c r="C198" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D198" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="E198" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F198" t="n">
-        <v>1357224</v>
+        <v>622609</v>
       </c>
       <c r="G198" t="n">
-        <v>53.32</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="199">
@@ -5297,39 +5297,39 @@
         <v>23</v>
       </c>
       <c r="D199" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F199" t="n">
-        <v>307112</v>
+        <v>83171</v>
       </c>
       <c r="G199" t="n">
-        <v>10.98</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="s">
-        <v>54</v>
-      </c>
-      <c r="B200" t="s">
+      <c r="A200" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C200" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D200" t="s">
-        <v>16</v>
-      </c>
-      <c r="E200" t="s">
-        <v>76</v>
-      </c>
-      <c r="F200" t="n">
-        <v>770906</v>
-      </c>
-      <c r="G200" t="n">
-        <v>27.55</v>
+      <c r="D200" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>1539409</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>60.26</v>
       </c>
     </row>
     <row r="201">
@@ -5337,45 +5337,45 @@
         <v>54</v>
       </c>
       <c r="B201" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C201" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D201" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E201" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F201" t="n">
-        <v>86932</v>
+        <v>2113005</v>
       </c>
       <c r="G201" t="n">
-        <v>3.11</v>
+        <v>84.39</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F202" s="2" t="n">
-        <v>1633314</v>
-      </c>
-      <c r="G202" s="2" t="n">
-        <v>58.37</v>
+      <c r="A202" t="s">
+        <v>54</v>
+      </c>
+      <c r="B202" t="s">
+        <v>80</v>
+      </c>
+      <c r="C202" t="s">
+        <v>13</v>
+      </c>
+      <c r="D202" t="s">
+        <v>14</v>
+      </c>
+      <c r="E202" t="s">
+        <v>82</v>
+      </c>
+      <c r="F202" t="n">
+        <v>390945</v>
+      </c>
+      <c r="G202" t="n">
+        <v>15.61</v>
       </c>
     </row>
     <row r="203">
@@ -5386,7 +5386,7 @@
         <v>80</v>
       </c>
       <c r="C203" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D203" t="s">
         <v>43</v>
@@ -5395,10 +5395,10 @@
         <v>81</v>
       </c>
       <c r="F203" t="n">
-        <v>1965916</v>
+        <v>506278</v>
       </c>
       <c r="G203" t="n">
-        <v>84.32</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="204">
@@ -5409,7 +5409,7 @@
         <v>80</v>
       </c>
       <c r="C204" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D204" t="s">
         <v>14</v>
@@ -5418,10 +5418,10 @@
         <v>82</v>
       </c>
       <c r="F204" t="n">
-        <v>365485</v>
+        <v>163877</v>
       </c>
       <c r="G204" t="n">
-        <v>15.68</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="205">
@@ -5432,7 +5432,7 @@
         <v>80</v>
       </c>
       <c r="C205" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D205" t="s">
         <v>43</v>
@@ -5441,10 +5441,10 @@
         <v>81</v>
       </c>
       <c r="F205" t="n">
-        <v>1387564</v>
+        <v>3074350</v>
       </c>
       <c r="G205" t="n">
-        <v>76</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="206">
@@ -5455,7 +5455,7 @@
         <v>80</v>
       </c>
       <c r="C206" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D206" t="s">
         <v>14</v>
@@ -5464,10 +5464,10 @@
         <v>82</v>
       </c>
       <c r="F206" t="n">
-        <v>438213</v>
+        <v>1257591</v>
       </c>
       <c r="G206" t="n">
-        <v>24</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="207">
@@ -5478,7 +5478,7 @@
         <v>80</v>
       </c>
       <c r="C207" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D207" t="s">
         <v>43</v>
@@ -5487,10 +5487,10 @@
         <v>81</v>
       </c>
       <c r="F207" t="n">
-        <v>1793017</v>
+        <v>1309945</v>
       </c>
       <c r="G207" t="n">
-        <v>72.37</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="208">
@@ -5501,7 +5501,7 @@
         <v>80</v>
       </c>
       <c r="C208" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D208" t="s">
         <v>14</v>
@@ -5510,10 +5510,10 @@
         <v>82</v>
       </c>
       <c r="F208" t="n">
-        <v>684410</v>
+        <v>607887</v>
       </c>
       <c r="G208" t="n">
-        <v>27.63</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="209">
@@ -5524,7 +5524,7 @@
         <v>80</v>
       </c>
       <c r="C209" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D209" t="s">
         <v>43</v>
@@ -5533,33 +5533,33 @@
         <v>81</v>
       </c>
       <c r="F209" t="n">
-        <v>1738199</v>
+        <v>1706122</v>
       </c>
       <c r="G209" t="n">
-        <v>68.28</v>
+        <v>66.79</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="s">
-        <v>54</v>
-      </c>
-      <c r="B210" t="s">
+      <c r="A210" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B210" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C210" t="s">
-        <v>22</v>
-      </c>
-      <c r="D210" t="s">
-        <v>14</v>
-      </c>
-      <c r="E210" t="s">
+      <c r="C210" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F210" t="n">
-        <v>807316</v>
-      </c>
-      <c r="G210" t="n">
-        <v>31.72</v>
+      <c r="F210" s="2" t="n">
+        <v>848383</v>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>33.21</v>
       </c>
     </row>
     <row r="211">
@@ -5567,10 +5567,10 @@
         <v>54</v>
       </c>
       <c r="B211" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C211" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D211" t="s">
         <v>43</v>
@@ -5579,33 +5579,33 @@
         <v>81</v>
       </c>
       <c r="F211" t="n">
-        <v>1825004</v>
+        <v>2439497</v>
       </c>
       <c r="G211" t="n">
-        <v>65.22</v>
+        <v>97.43</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E212" s="2" t="s">
+      <c r="A212" t="s">
+        <v>54</v>
+      </c>
+      <c r="B212" t="s">
+        <v>83</v>
+      </c>
+      <c r="C212" t="s">
+        <v>13</v>
+      </c>
+      <c r="D212" t="s">
+        <v>14</v>
+      </c>
+      <c r="E212" t="s">
         <v>82</v>
       </c>
-      <c r="F212" s="2" t="n">
-        <v>973260</v>
-      </c>
-      <c r="G212" s="2" t="n">
-        <v>34.78</v>
+      <c r="F212" t="n">
+        <v>64453</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2.57</v>
       </c>
     </row>
     <row r="213">
@@ -5616,7 +5616,7 @@
         <v>83</v>
       </c>
       <c r="C213" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D213" t="s">
         <v>43</v>
@@ -5625,10 +5625,10 @@
         <v>81</v>
       </c>
       <c r="F213" t="n">
-        <v>2264243</v>
+        <v>629374</v>
       </c>
       <c r="G213" t="n">
-        <v>97.12</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="214">
@@ -5639,7 +5639,7 @@
         <v>83</v>
       </c>
       <c r="C214" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D214" t="s">
         <v>14</v>
@@ -5648,10 +5648,10 @@
         <v>82</v>
       </c>
       <c r="F214" t="n">
-        <v>67159</v>
+        <v>40782</v>
       </c>
       <c r="G214" t="n">
-        <v>2.88</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="215">
@@ -5662,7 +5662,7 @@
         <v>83</v>
       </c>
       <c r="C215" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D215" t="s">
         <v>43</v>
@@ -5671,10 +5671,10 @@
         <v>81</v>
       </c>
       <c r="F215" t="n">
-        <v>1762176</v>
+        <v>4098166</v>
       </c>
       <c r="G215" t="n">
-        <v>96.52</v>
+        <v>94.6</v>
       </c>
     </row>
     <row r="216">
@@ -5685,7 +5685,7 @@
         <v>83</v>
       </c>
       <c r="C216" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D216" t="s">
         <v>14</v>
@@ -5694,10 +5694,10 @@
         <v>82</v>
       </c>
       <c r="F216" t="n">
-        <v>63601</v>
+        <v>233775</v>
       </c>
       <c r="G216" t="n">
-        <v>3.48</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="217">
@@ -5708,7 +5708,7 @@
         <v>83</v>
       </c>
       <c r="C217" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D217" t="s">
         <v>43</v>
@@ -5717,10 +5717,10 @@
         <v>81</v>
       </c>
       <c r="F217" t="n">
-        <v>2339862</v>
+        <v>1800965</v>
       </c>
       <c r="G217" t="n">
-        <v>94.45</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="218">
@@ -5731,7 +5731,7 @@
         <v>83</v>
       </c>
       <c r="C218" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D218" t="s">
         <v>14</v>
@@ -5740,10 +5740,10 @@
         <v>82</v>
       </c>
       <c r="F218" t="n">
-        <v>137565</v>
+        <v>116867</v>
       </c>
       <c r="G218" t="n">
-        <v>5.55</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="219">
@@ -5754,7 +5754,7 @@
         <v>83</v>
       </c>
       <c r="C219" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D219" t="s">
         <v>43</v>
@@ -5763,33 +5763,33 @@
         <v>81</v>
       </c>
       <c r="F219" t="n">
-        <v>2379196</v>
+        <v>2368182</v>
       </c>
       <c r="G219" t="n">
-        <v>93.47</v>
+        <v>92.71</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="s">
-        <v>54</v>
-      </c>
-      <c r="B220" t="s">
+      <c r="A220" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C220" t="s">
-        <v>22</v>
-      </c>
-      <c r="D220" t="s">
-        <v>14</v>
-      </c>
-      <c r="E220" t="s">
+      <c r="C220" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F220" t="n">
-        <v>166319</v>
-      </c>
-      <c r="G220" t="n">
-        <v>6.53</v>
+      <c r="F220" s="2" t="n">
+        <v>186324</v>
+      </c>
+      <c r="G220" s="2" t="n">
+        <v>7.29</v>
       </c>
     </row>
     <row r="221">
@@ -5797,45 +5797,45 @@
         <v>54</v>
       </c>
       <c r="B221" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C221" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D221" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E221" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F221" t="n">
-        <v>2590707</v>
+        <v>1186500</v>
       </c>
       <c r="G221" t="n">
-        <v>92.58</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F222" s="2" t="n">
-        <v>207557</v>
-      </c>
-      <c r="G222" s="2" t="n">
-        <v>7.42</v>
+      <c r="A222" t="s">
+        <v>54</v>
+      </c>
+      <c r="B222" t="s">
+        <v>84</v>
+      </c>
+      <c r="C222" t="s">
+        <v>13</v>
+      </c>
+      <c r="D222" t="s">
+        <v>16</v>
+      </c>
+      <c r="E222" t="s">
+        <v>86</v>
+      </c>
+      <c r="F222" t="n">
+        <v>774822</v>
+      </c>
+      <c r="G222" t="n">
+        <v>30.94</v>
       </c>
     </row>
     <row r="223">
@@ -5849,16 +5849,16 @@
         <v>13</v>
       </c>
       <c r="D223" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E223" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F223" t="n">
-        <v>949219</v>
+        <v>540688</v>
       </c>
       <c r="G223" t="n">
-        <v>40.71</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="224">
@@ -5871,17 +5871,13 @@
       <c r="C224" t="s">
         <v>13</v>
       </c>
-      <c r="D224" t="s">
-        <v>16</v>
-      </c>
-      <c r="E224" t="s">
-        <v>86</v>
-      </c>
+      <c r="D224"/>
+      <c r="E224"/>
       <c r="F224" t="n">
-        <v>826471</v>
+        <v>1939</v>
       </c>
       <c r="G224" t="n">
-        <v>35.45</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="225">
@@ -5892,19 +5888,19 @@
         <v>84</v>
       </c>
       <c r="C225" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D225" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E225" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F225" t="n">
-        <v>555711</v>
+        <v>234120</v>
       </c>
       <c r="G225" t="n">
-        <v>23.84</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="226">
@@ -5918,16 +5914,16 @@
         <v>20</v>
       </c>
       <c r="D226" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E226" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F226" t="n">
-        <v>570166</v>
+        <v>198783</v>
       </c>
       <c r="G226" t="n">
-        <v>31.23</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="227">
@@ -5941,16 +5937,16 @@
         <v>20</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E227" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F227" t="n">
-        <v>656490</v>
+        <v>236530</v>
       </c>
       <c r="G227" t="n">
-        <v>35.96</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="228">
@@ -5963,17 +5959,13 @@
       <c r="C228" t="s">
         <v>20</v>
       </c>
-      <c r="D228" t="s">
-        <v>18</v>
-      </c>
-      <c r="E228" t="s">
-        <v>87</v>
-      </c>
+      <c r="D228"/>
+      <c r="E228"/>
       <c r="F228" t="n">
-        <v>599121</v>
+        <v>723</v>
       </c>
       <c r="G228" t="n">
-        <v>32.81</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="229">
@@ -5993,10 +5985,10 @@
         <v>85</v>
       </c>
       <c r="F229" t="n">
-        <v>574402</v>
+        <v>1138176</v>
       </c>
       <c r="G229" t="n">
-        <v>23.19</v>
+        <v>26.27</v>
       </c>
     </row>
     <row r="230">
@@ -6016,10 +6008,10 @@
         <v>86</v>
       </c>
       <c r="F230" t="n">
-        <v>849545</v>
+        <v>1441225</v>
       </c>
       <c r="G230" t="n">
-        <v>34.29</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="231">
@@ -6039,10 +6031,10 @@
         <v>87</v>
       </c>
       <c r="F231" t="n">
-        <v>1053480</v>
+        <v>1751066</v>
       </c>
       <c r="G231" t="n">
-        <v>42.52</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="232">
@@ -6053,19 +6045,15 @@
         <v>84</v>
       </c>
       <c r="C232" t="s">
-        <v>22</v>
-      </c>
-      <c r="D232" t="s">
-        <v>14</v>
-      </c>
-      <c r="E232" t="s">
-        <v>85</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D232"/>
+      <c r="E232"/>
       <c r="F232" t="n">
-        <v>384333</v>
+        <v>1474</v>
       </c>
       <c r="G232" t="n">
-        <v>15.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="233">
@@ -6079,16 +6067,16 @@
         <v>22</v>
       </c>
       <c r="D233" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F233" t="n">
-        <v>796234</v>
+        <v>429107</v>
       </c>
       <c r="G233" t="n">
-        <v>31.28</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="234">
@@ -6102,16 +6090,16 @@
         <v>22</v>
       </c>
       <c r="D234" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F234" t="n">
-        <v>1364948</v>
+        <v>573212</v>
       </c>
       <c r="G234" t="n">
-        <v>53.62</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="235">
@@ -6122,19 +6110,19 @@
         <v>84</v>
       </c>
       <c r="C235" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D235" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E235" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F235" t="n">
-        <v>416465</v>
+        <v>915216</v>
       </c>
       <c r="G235" t="n">
-        <v>14.88</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="236">
@@ -6145,42 +6133,38 @@
         <v>84</v>
       </c>
       <c r="C236" t="s">
+        <v>22</v>
+      </c>
+      <c r="D236"/>
+      <c r="E236"/>
+      <c r="F236" t="n">
+        <v>298</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>54</v>
+      </c>
+      <c r="B237" t="s">
+        <v>84</v>
+      </c>
+      <c r="C237" t="s">
         <v>23</v>
       </c>
-      <c r="D236" t="s">
-        <v>16</v>
-      </c>
-      <c r="E236" t="s">
-        <v>86</v>
-      </c>
-      <c r="F236" t="n">
-        <v>798207</v>
-      </c>
-      <c r="G236" t="n">
-        <v>28.53</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F237" s="2" t="n">
-        <v>1583591</v>
-      </c>
-      <c r="G237" s="2" t="n">
-        <v>56.59</v>
+      <c r="D237" t="s">
+        <v>14</v>
+      </c>
+      <c r="E237" t="s">
+        <v>85</v>
+      </c>
+      <c r="F237" t="n">
+        <v>371949</v>
+      </c>
+      <c r="G237" t="n">
+        <v>14.56</v>
       </c>
     </row>
     <row r="238">
@@ -6188,22 +6172,22 @@
         <v>54</v>
       </c>
       <c r="B238" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C238" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D238" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E238" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F238" t="n">
-        <v>1043619</v>
+        <v>623803</v>
       </c>
       <c r="G238" t="n">
-        <v>44.76</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="239">
@@ -6211,45 +6195,41 @@
         <v>54</v>
       </c>
       <c r="B239" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C239" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D239" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E239" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F239" t="n">
-        <v>824751</v>
+        <v>1558075</v>
       </c>
       <c r="G239" t="n">
-        <v>35.38</v>
+        <v>60.99</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="s">
-        <v>54</v>
-      </c>
-      <c r="B240" t="s">
-        <v>88</v>
-      </c>
-      <c r="C240" t="s">
-        <v>13</v>
-      </c>
-      <c r="D240" t="s">
-        <v>18</v>
-      </c>
-      <c r="E240" t="s">
-        <v>91</v>
-      </c>
-      <c r="F240" t="n">
-        <v>463031</v>
-      </c>
-      <c r="G240" t="n">
-        <v>19.86</v>
+      <c r="A240" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="G240" s="2" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="241">
@@ -6260,7 +6240,7 @@
         <v>88</v>
       </c>
       <c r="C241" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D241" t="s">
         <v>14</v>
@@ -6269,10 +6249,10 @@
         <v>89</v>
       </c>
       <c r="F241" t="n">
-        <v>574334</v>
+        <v>1164220</v>
       </c>
       <c r="G241" t="n">
-        <v>31.46</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="242">
@@ -6283,7 +6263,7 @@
         <v>88</v>
       </c>
       <c r="C242" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D242" t="s">
         <v>16</v>
@@ -6292,10 +6272,10 @@
         <v>90</v>
       </c>
       <c r="F242" t="n">
-        <v>704125</v>
+        <v>926342</v>
       </c>
       <c r="G242" t="n">
-        <v>38.57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="243">
@@ -6306,7 +6286,7 @@
         <v>88</v>
       </c>
       <c r="C243" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D243" t="s">
         <v>18</v>
@@ -6315,10 +6295,10 @@
         <v>91</v>
       </c>
       <c r="F243" t="n">
-        <v>547318</v>
+        <v>410706</v>
       </c>
       <c r="G243" t="n">
-        <v>29.98</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="244">
@@ -6329,19 +6309,15 @@
         <v>88</v>
       </c>
       <c r="C244" t="s">
-        <v>21</v>
-      </c>
-      <c r="D244" t="s">
-        <v>14</v>
-      </c>
-      <c r="E244" t="s">
-        <v>89</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D244"/>
+      <c r="E244"/>
       <c r="F244" t="n">
-        <v>592644</v>
+        <v>2682</v>
       </c>
       <c r="G244" t="n">
-        <v>23.92</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="245">
@@ -6352,19 +6328,19 @@
         <v>88</v>
       </c>
       <c r="C245" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E245" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F245" t="n">
-        <v>897818</v>
+        <v>211816</v>
       </c>
       <c r="G245" t="n">
-        <v>36.24</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="246">
@@ -6375,19 +6351,19 @@
         <v>88</v>
       </c>
       <c r="C246" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D246" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E246" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F246" t="n">
-        <v>986965</v>
+        <v>225454</v>
       </c>
       <c r="G246" t="n">
-        <v>39.84</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="247">
@@ -6398,19 +6374,19 @@
         <v>88</v>
       </c>
       <c r="C247" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D247" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E247" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F247" t="n">
-        <v>320449</v>
+        <v>232195</v>
       </c>
       <c r="G247" t="n">
-        <v>12.59</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="248">
@@ -6421,19 +6397,15 @@
         <v>88</v>
       </c>
       <c r="C248" t="s">
-        <v>22</v>
-      </c>
-      <c r="D248" t="s">
-        <v>16</v>
-      </c>
-      <c r="E248" t="s">
-        <v>90</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D248"/>
+      <c r="E248"/>
       <c r="F248" t="n">
-        <v>807979</v>
+        <v>690</v>
       </c>
       <c r="G248" t="n">
-        <v>31.74</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="249">
@@ -6444,19 +6416,19 @@
         <v>88</v>
       </c>
       <c r="C249" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D249" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E249" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F249" t="n">
-        <v>1417087</v>
+        <v>944162</v>
       </c>
       <c r="G249" t="n">
-        <v>55.67</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="250">
@@ -6467,19 +6439,19 @@
         <v>88</v>
       </c>
       <c r="C250" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D250" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E250" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F250" t="n">
-        <v>293092</v>
+        <v>1760575</v>
       </c>
       <c r="G250" t="n">
-        <v>10.47</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="251">
@@ -6490,42 +6462,38 @@
         <v>88</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D251" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E251" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F251" t="n">
-        <v>825275</v>
+        <v>1623359</v>
       </c>
       <c r="G251" t="n">
-        <v>29.49</v>
+        <v>37.47</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B252" s="2" t="s">
+      <c r="A252" t="s">
+        <v>54</v>
+      </c>
+      <c r="B252" t="s">
         <v>88</v>
       </c>
-      <c r="C252" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F252" s="2" t="n">
-        <v>1679898</v>
-      </c>
-      <c r="G252" s="2" t="n">
-        <v>60.03</v>
+      <c r="C252" t="s">
+        <v>21</v>
+      </c>
+      <c r="D252"/>
+      <c r="E252"/>
+      <c r="F252" t="n">
+        <v>3845</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="253">
@@ -6533,22 +6501,22 @@
         <v>54</v>
       </c>
       <c r="B253" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C253" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D253" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E253" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F253" t="n">
-        <v>1770319</v>
+        <v>302569</v>
       </c>
       <c r="G253" t="n">
-        <v>75.93</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="254">
@@ -6556,22 +6524,22 @@
         <v>54</v>
       </c>
       <c r="B254" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C254" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D254" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E254" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F254" t="n">
-        <v>555750</v>
+        <v>696666</v>
       </c>
       <c r="G254" t="n">
-        <v>23.84</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="255">
@@ -6579,22 +6547,22 @@
         <v>54</v>
       </c>
       <c r="B255" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C255" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D255" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="E255" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F255" t="n">
-        <v>4993</v>
+        <v>917202</v>
       </c>
       <c r="G255" t="n">
-        <v>0.21</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="256">
@@ -6602,22 +6570,18 @@
         <v>54</v>
       </c>
       <c r="B256" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C256" t="s">
-        <v>13</v>
-      </c>
-      <c r="D256" t="s">
-        <v>64</v>
-      </c>
-      <c r="E256" t="s">
-        <v>97</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D256"/>
+      <c r="E256"/>
       <c r="F256" t="n">
-        <v>339</v>
+        <v>1395</v>
       </c>
       <c r="G256" t="n">
-        <v>0.01</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="257">
@@ -6625,22 +6589,22 @@
         <v>54</v>
       </c>
       <c r="B257" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C257" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D257" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E257" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F257" t="n">
-        <v>1439810</v>
+        <v>224456</v>
       </c>
       <c r="G257" t="n">
-        <v>78.86</v>
+        <v>8.79</v>
       </c>
     </row>
     <row r="258">
@@ -6648,22 +6612,22 @@
         <v>54</v>
       </c>
       <c r="B258" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C258" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D258" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E258" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F258" t="n">
-        <v>383952</v>
+        <v>698051</v>
       </c>
       <c r="G258" t="n">
-        <v>21.03</v>
+        <v>27.33</v>
       </c>
     </row>
     <row r="259">
@@ -6671,45 +6635,41 @@
         <v>54</v>
       </c>
       <c r="B259" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C259" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D259" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="E259" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F259" t="n">
-        <v>2014</v>
+        <v>1625894</v>
       </c>
       <c r="G259" t="n">
-        <v>0.11</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="s">
-        <v>54</v>
-      </c>
-      <c r="B260" t="s">
-        <v>92</v>
-      </c>
-      <c r="C260" t="s">
-        <v>21</v>
-      </c>
-      <c r="D260" t="s">
-        <v>43</v>
-      </c>
-      <c r="E260" t="s">
-        <v>93</v>
-      </c>
-      <c r="F260" t="n">
-        <v>1907487</v>
-      </c>
-      <c r="G260" t="n">
-        <v>76.99</v>
+      <c r="A260" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2" t="n">
+        <v>6104</v>
+      </c>
+      <c r="G260" s="2" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="261">
@@ -6720,19 +6680,19 @@
         <v>92</v>
       </c>
       <c r="C261" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D261" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E261" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F261" t="n">
-        <v>568264</v>
+        <v>1919750</v>
       </c>
       <c r="G261" t="n">
-        <v>22.94</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="262">
@@ -6743,19 +6703,19 @@
         <v>92</v>
       </c>
       <c r="C262" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D262" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="E262" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F262" t="n">
-        <v>1597</v>
+        <v>580306</v>
       </c>
       <c r="G262" t="n">
-        <v>0.06</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="263">
@@ -6766,19 +6726,19 @@
         <v>92</v>
       </c>
       <c r="C263" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D263" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="E263" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F263" t="n">
-        <v>79</v>
+        <v>3570</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="264">
@@ -6789,19 +6749,19 @@
         <v>92</v>
       </c>
       <c r="C264" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D264" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E264" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F264" t="n">
-        <v>1951480</v>
+        <v>324</v>
       </c>
       <c r="G264" t="n">
-        <v>76.66</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="265">
@@ -6812,19 +6772,19 @@
         <v>92</v>
       </c>
       <c r="C265" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D265" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E265" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F265" t="n">
-        <v>593378</v>
+        <v>513700</v>
       </c>
       <c r="G265" t="n">
-        <v>23.31</v>
+        <v>76.65</v>
       </c>
     </row>
     <row r="266">
@@ -6835,19 +6795,19 @@
         <v>92</v>
       </c>
       <c r="C266" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D266" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="E266" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F266" t="n">
-        <v>657</v>
+        <v>155672</v>
       </c>
       <c r="G266" t="n">
-        <v>0.03</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="267">
@@ -6858,19 +6818,19 @@
         <v>92</v>
       </c>
       <c r="C267" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D267" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E267" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F267" t="n">
-        <v>2125831</v>
+        <v>783</v>
       </c>
       <c r="G267" t="n">
-        <v>75.97</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="268">
@@ -6881,42 +6841,42 @@
         <v>92</v>
       </c>
       <c r="C268" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D268" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E268" t="s">
+        <v>93</v>
+      </c>
+      <c r="F268" t="n">
+        <v>3394170</v>
+      </c>
+      <c r="G268" t="n">
+        <v>78.35</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>54</v>
+      </c>
+      <c r="B269" t="s">
+        <v>92</v>
+      </c>
+      <c r="C269" t="s">
+        <v>21</v>
+      </c>
+      <c r="D269" t="s">
+        <v>14</v>
+      </c>
+      <c r="E269" t="s">
         <v>94</v>
       </c>
-      <c r="F268" t="n">
-        <v>672210</v>
-      </c>
-      <c r="G268" t="n">
-        <v>24.02</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D269" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F269" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="G269" s="2" t="n">
-        <v>0.01</v>
+      <c r="F269" t="n">
+        <v>934292</v>
+      </c>
+      <c r="G269" t="n">
+        <v>21.57</v>
       </c>
     </row>
     <row r="270">
@@ -6924,22 +6884,22 @@
         <v>54</v>
       </c>
       <c r="B270" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C270" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D270" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E270" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F270" t="n">
-        <v>1001829</v>
+        <v>3400</v>
       </c>
       <c r="G270" t="n">
-        <v>42.97</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="271">
@@ -6947,22 +6907,22 @@
         <v>54</v>
       </c>
       <c r="B271" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C271" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D271" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E271" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F271" t="n">
-        <v>1324240</v>
+        <v>79</v>
       </c>
       <c r="G271" t="n">
-        <v>56.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -6970,22 +6930,22 @@
         <v>54</v>
       </c>
       <c r="B272" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C272" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D272" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E272" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F272" t="n">
-        <v>4993</v>
+        <v>1470345</v>
       </c>
       <c r="G272" t="n">
-        <v>0.21</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="273">
@@ -6993,22 +6953,22 @@
         <v>54</v>
       </c>
       <c r="B273" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C273" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D273" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="E273" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F273" t="n">
-        <v>339</v>
+        <v>446494</v>
       </c>
       <c r="G273" t="n">
-        <v>0.01</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="274">
@@ -7016,22 +6976,22 @@
         <v>54</v>
       </c>
       <c r="B274" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C274" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D274" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E274" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F274" t="n">
-        <v>827258</v>
+        <v>978</v>
       </c>
       <c r="G274" t="n">
-        <v>45.31</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="275">
@@ -7039,22 +6999,22 @@
         <v>54</v>
       </c>
       <c r="B275" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C275" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D275" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E275" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F275" t="n">
-        <v>996504</v>
+        <v>15</v>
       </c>
       <c r="G275" t="n">
-        <v>54.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -7062,22 +7022,22 @@
         <v>54</v>
       </c>
       <c r="B276" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C276" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D276" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E276" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F276" t="n">
-        <v>2014</v>
+        <v>1896963</v>
       </c>
       <c r="G276" t="n">
-        <v>0.11</v>
+        <v>74.26</v>
       </c>
     </row>
     <row r="277">
@@ -7085,45 +7045,45 @@
         <v>54</v>
       </c>
       <c r="B277" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C277" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D277" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E277" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F277" t="n">
-        <v>1036865</v>
+        <v>656790</v>
       </c>
       <c r="G277" t="n">
-        <v>41.85</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="s">
-        <v>54</v>
-      </c>
-      <c r="B278" t="s">
-        <v>98</v>
-      </c>
-      <c r="C278" t="s">
-        <v>21</v>
-      </c>
-      <c r="D278" t="s">
-        <v>14</v>
-      </c>
-      <c r="E278" t="s">
-        <v>100</v>
-      </c>
-      <c r="F278" t="n">
-        <v>1438886</v>
-      </c>
-      <c r="G278" t="n">
-        <v>58.08</v>
+      <c r="A278" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="G278" s="2" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="279">
@@ -7134,19 +7094,19 @@
         <v>98</v>
       </c>
       <c r="C279" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D279" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E279" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F279" t="n">
-        <v>1597</v>
+        <v>1106125</v>
       </c>
       <c r="G279" t="n">
-        <v>0.06</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="280">
@@ -7157,19 +7117,19 @@
         <v>98</v>
       </c>
       <c r="C280" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D280" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="E280" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F280" t="n">
-        <v>79</v>
+        <v>1393931</v>
       </c>
       <c r="G280" t="n">
-        <v>0</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="281">
@@ -7180,19 +7140,19 @@
         <v>98</v>
       </c>
       <c r="C281" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D281" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E281" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F281" t="n">
-        <v>1017057</v>
+        <v>3570</v>
       </c>
       <c r="G281" t="n">
-        <v>39.95</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="282">
@@ -7203,19 +7163,19 @@
         <v>98</v>
       </c>
       <c r="C282" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D282" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E282" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F282" t="n">
-        <v>1527801</v>
+        <v>324</v>
       </c>
       <c r="G282" t="n">
-        <v>60.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="283">
@@ -7226,19 +7186,19 @@
         <v>98</v>
       </c>
       <c r="C283" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D283" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E283" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F283" t="n">
-        <v>657</v>
+        <v>297801</v>
       </c>
       <c r="G283" t="n">
-        <v>0.03</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="284">
@@ -7249,19 +7209,19 @@
         <v>98</v>
       </c>
       <c r="C284" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D284" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E284" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F284" t="n">
-        <v>1198762</v>
+        <v>371571</v>
       </c>
       <c r="G284" t="n">
-        <v>42.84</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="285">
@@ -7272,42 +7232,42 @@
         <v>98</v>
       </c>
       <c r="C285" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D285" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="E285" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F285" t="n">
-        <v>1599280</v>
+        <v>783</v>
       </c>
       <c r="G285" t="n">
-        <v>57.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B286" s="2" t="s">
+      <c r="A286" t="s">
+        <v>54</v>
+      </c>
+      <c r="B286" t="s">
         <v>98</v>
       </c>
-      <c r="C286" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F286" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="G286" s="2" t="n">
-        <v>0.01</v>
+      <c r="C286" t="s">
+        <v>21</v>
+      </c>
+      <c r="D286" t="s">
+        <v>43</v>
+      </c>
+      <c r="E286" t="s">
+        <v>99</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1810510</v>
+      </c>
+      <c r="G286" t="n">
+        <v>41.79</v>
       </c>
     </row>
     <row r="287">
@@ -7315,22 +7275,22 @@
         <v>54</v>
       </c>
       <c r="B287" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C287" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D287" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E287" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F287" t="n">
-        <v>983626</v>
+        <v>2517953</v>
       </c>
       <c r="G287" t="n">
-        <v>42.19</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="288">
@@ -7338,22 +7298,22 @@
         <v>54</v>
       </c>
       <c r="B288" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C288" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D288" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="E288" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F288" t="n">
-        <v>1342444</v>
+        <v>3400</v>
       </c>
       <c r="G288" t="n">
-        <v>57.58</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="289">
@@ -7361,22 +7321,22 @@
         <v>54</v>
       </c>
       <c r="B289" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C289" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D289" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E289" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F289" t="n">
-        <v>4993</v>
+        <v>79</v>
       </c>
       <c r="G289" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -7384,22 +7344,22 @@
         <v>54</v>
       </c>
       <c r="B290" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C290" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D290" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E290" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F290" t="n">
-        <v>339</v>
+        <v>760636</v>
       </c>
       <c r="G290" t="n">
-        <v>0.01</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="291">
@@ -7407,22 +7367,22 @@
         <v>54</v>
       </c>
       <c r="B291" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C291" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D291" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E291" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F291" t="n">
-        <v>752286</v>
+        <v>1156203</v>
       </c>
       <c r="G291" t="n">
-        <v>41.2</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="292">
@@ -7430,22 +7390,22 @@
         <v>54</v>
       </c>
       <c r="B292" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C292" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D292" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="E292" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F292" t="n">
-        <v>1071477</v>
+        <v>978</v>
       </c>
       <c r="G292" t="n">
-        <v>58.69</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="293">
@@ -7453,22 +7413,22 @@
         <v>54</v>
       </c>
       <c r="B293" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C293" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D293" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E293" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F293" t="n">
-        <v>2014</v>
+        <v>15</v>
       </c>
       <c r="G293" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -7476,22 +7436,22 @@
         <v>54</v>
       </c>
       <c r="B294" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C294" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D294" t="s">
         <v>43</v>
       </c>
       <c r="E294" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F294" t="n">
-        <v>970830</v>
+        <v>1106700</v>
       </c>
       <c r="G294" t="n">
-        <v>39.19</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="295">
@@ -7499,45 +7459,45 @@
         <v>54</v>
       </c>
       <c r="B295" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C295" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D295" t="s">
         <v>14</v>
       </c>
       <c r="E295" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F295" t="n">
-        <v>1504921</v>
+        <v>1447053</v>
       </c>
       <c r="G295" t="n">
-        <v>60.75</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="s">
-        <v>54</v>
-      </c>
-      <c r="B296" t="s">
-        <v>101</v>
-      </c>
-      <c r="C296" t="s">
-        <v>21</v>
-      </c>
-      <c r="D296" t="s">
+      <c r="A296" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D296" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E296" t="s">
+      <c r="E296" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F296" t="n">
-        <v>1597</v>
-      </c>
-      <c r="G296" t="n">
-        <v>0.06</v>
+      <c r="F296" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="G296" s="2" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="297">
@@ -7548,19 +7508,19 @@
         <v>101</v>
       </c>
       <c r="C297" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D297" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E297" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F297" t="n">
-        <v>79</v>
+        <v>1073916</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="298">
@@ -7571,19 +7531,19 @@
         <v>101</v>
       </c>
       <c r="C298" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D298" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E298" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F298" t="n">
-        <v>1083956</v>
+        <v>1426140</v>
       </c>
       <c r="G298" t="n">
-        <v>42.58</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="299">
@@ -7594,19 +7554,19 @@
         <v>101</v>
       </c>
       <c r="C299" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D299" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="E299" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F299" t="n">
-        <v>1460903</v>
+        <v>3570</v>
       </c>
       <c r="G299" t="n">
-        <v>57.39</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="300">
@@ -7617,19 +7577,19 @@
         <v>101</v>
       </c>
       <c r="C300" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D300" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E300" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F300" t="n">
-        <v>657</v>
+        <v>324</v>
       </c>
       <c r="G300" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="301">
@@ -7640,7 +7600,7 @@
         <v>101</v>
       </c>
       <c r="C301" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D301" t="s">
         <v>43</v>
@@ -7649,10 +7609,10 @@
         <v>102</v>
       </c>
       <c r="F301" t="n">
-        <v>1202549</v>
+        <v>269921</v>
       </c>
       <c r="G301" t="n">
-        <v>42.97</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="302">
@@ -7663,7 +7623,7 @@
         <v>101</v>
       </c>
       <c r="C302" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D302" t="s">
         <v>14</v>
@@ -7672,33 +7632,33 @@
         <v>103</v>
       </c>
       <c r="F302" t="n">
-        <v>1595493</v>
+        <v>399452</v>
       </c>
       <c r="G302" t="n">
-        <v>57.02</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B303" s="2" t="s">
+      <c r="A303" t="s">
+        <v>54</v>
+      </c>
+      <c r="B303" t="s">
         <v>101</v>
       </c>
-      <c r="C303" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D303" s="2" t="s">
+      <c r="C303" t="s">
+        <v>20</v>
+      </c>
+      <c r="D303" t="s">
         <v>95</v>
       </c>
-      <c r="E303" s="2" t="s">
+      <c r="E303" t="s">
         <v>96</v>
       </c>
-      <c r="F303" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="G303" s="2" t="n">
-        <v>0.01</v>
+      <c r="F303" t="n">
+        <v>783</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="304">
@@ -7706,22 +7666,22 @@
         <v>54</v>
       </c>
       <c r="B304" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C304" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D304" t="s">
         <v>43</v>
       </c>
       <c r="E304" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F304" t="n">
-        <v>977104</v>
+        <v>1696166</v>
       </c>
       <c r="G304" t="n">
-        <v>41.91</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="305">
@@ -7729,22 +7689,22 @@
         <v>54</v>
       </c>
       <c r="B305" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C305" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D305" t="s">
         <v>14</v>
       </c>
       <c r="E305" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F305" t="n">
-        <v>1348965</v>
+        <v>2632296</v>
       </c>
       <c r="G305" t="n">
-        <v>57.86</v>
+        <v>60.76</v>
       </c>
     </row>
     <row r="306">
@@ -7752,10 +7712,10 @@
         <v>54</v>
       </c>
       <c r="B306" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C306" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D306" t="s">
         <v>95</v>
@@ -7764,10 +7724,10 @@
         <v>96</v>
       </c>
       <c r="F306" t="n">
-        <v>4993</v>
+        <v>3400</v>
       </c>
       <c r="G306" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="307">
@@ -7775,10 +7735,10 @@
         <v>54</v>
       </c>
       <c r="B307" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C307" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D307" t="s">
         <v>64</v>
@@ -7787,10 +7747,10 @@
         <v>97</v>
       </c>
       <c r="F307" t="n">
-        <v>339</v>
+        <v>79</v>
       </c>
       <c r="G307" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -7798,22 +7758,22 @@
         <v>54</v>
       </c>
       <c r="B308" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C308" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D308" t="s">
         <v>43</v>
       </c>
       <c r="E308" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F308" t="n">
-        <v>743817</v>
+        <v>806688</v>
       </c>
       <c r="G308" t="n">
-        <v>40.74</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="309">
@@ -7821,22 +7781,22 @@
         <v>54</v>
       </c>
       <c r="B309" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C309" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D309" t="s">
         <v>14</v>
       </c>
       <c r="E309" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F309" t="n">
-        <v>1079946</v>
+        <v>1110151</v>
       </c>
       <c r="G309" t="n">
-        <v>59.15</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="310">
@@ -7844,10 +7804,10 @@
         <v>54</v>
       </c>
       <c r="B310" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C310" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D310" t="s">
         <v>95</v>
@@ -7856,10 +7816,10 @@
         <v>96</v>
       </c>
       <c r="F310" t="n">
-        <v>2014</v>
+        <v>978</v>
       </c>
       <c r="G310" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="311">
@@ -7867,22 +7827,22 @@
         <v>54</v>
       </c>
       <c r="B311" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C311" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D311" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E311" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F311" t="n">
-        <v>984622</v>
+        <v>15</v>
       </c>
       <c r="G311" t="n">
-        <v>39.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -7890,22 +7850,22 @@
         <v>54</v>
       </c>
       <c r="B312" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C312" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D312" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E312" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F312" t="n">
-        <v>1491129</v>
+        <v>1146555</v>
       </c>
       <c r="G312" t="n">
-        <v>60.19</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="313">
@@ -7913,45 +7873,45 @@
         <v>54</v>
       </c>
       <c r="B313" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C313" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D313" t="s">
+        <v>14</v>
+      </c>
+      <c r="E313" t="s">
+        <v>103</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1407198</v>
+      </c>
+      <c r="G313" t="n">
+        <v>55.09</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D314" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E313" t="s">
+      <c r="E314" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F313" t="n">
-        <v>1597</v>
-      </c>
-      <c r="G313" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="s">
-        <v>54</v>
-      </c>
-      <c r="B314" t="s">
-        <v>104</v>
-      </c>
-      <c r="C314" t="s">
-        <v>21</v>
-      </c>
-      <c r="D314" t="s">
-        <v>64</v>
-      </c>
-      <c r="E314" t="s">
-        <v>97</v>
-      </c>
-      <c r="F314" t="n">
-        <v>79</v>
-      </c>
-      <c r="G314" t="n">
-        <v>0</v>
+      <c r="F314" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="G314" s="2" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="315">
@@ -7962,7 +7922,7 @@
         <v>104</v>
       </c>
       <c r="C315" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D315" t="s">
         <v>43</v>
@@ -7971,10 +7931,10 @@
         <v>105</v>
       </c>
       <c r="F315" t="n">
-        <v>964159</v>
+        <v>1042147</v>
       </c>
       <c r="G315" t="n">
-        <v>37.88</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="316">
@@ -7985,7 +7945,7 @@
         <v>104</v>
       </c>
       <c r="C316" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D316" t="s">
         <v>14</v>
@@ -7994,10 +7954,10 @@
         <v>106</v>
       </c>
       <c r="F316" t="n">
-        <v>1580699</v>
+        <v>1457909</v>
       </c>
       <c r="G316" t="n">
-        <v>62.1</v>
+        <v>58.22</v>
       </c>
     </row>
     <row r="317">
@@ -8008,7 +7968,7 @@
         <v>104</v>
       </c>
       <c r="C317" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D317" t="s">
         <v>95</v>
@@ -8017,10 +7977,10 @@
         <v>96</v>
       </c>
       <c r="F317" t="n">
-        <v>657</v>
+        <v>3570</v>
       </c>
       <c r="G317" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="318">
@@ -8031,19 +7991,19 @@
         <v>104</v>
       </c>
       <c r="C318" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D318" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E318" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F318" t="n">
-        <v>1029653</v>
+        <v>324</v>
       </c>
       <c r="G318" t="n">
-        <v>36.8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="319">
@@ -8054,42 +8014,42 @@
         <v>104</v>
       </c>
       <c r="C319" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D319" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E319" t="s">
+        <v>105</v>
+      </c>
+      <c r="F319" t="n">
+        <v>268614</v>
+      </c>
+      <c r="G319" t="n">
+        <v>40.08</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>54</v>
+      </c>
+      <c r="B320" t="s">
+        <v>104</v>
+      </c>
+      <c r="C320" t="s">
+        <v>20</v>
+      </c>
+      <c r="D320" t="s">
+        <v>14</v>
+      </c>
+      <c r="E320" t="s">
         <v>106</v>
       </c>
-      <c r="F319" t="n">
-        <v>1768389</v>
-      </c>
-      <c r="G319" t="n">
-        <v>63.2</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D320" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F320" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="G320" s="2" t="n">
-        <v>0.01</v>
+      <c r="F320" t="n">
+        <v>400758</v>
+      </c>
+      <c r="G320" t="n">
+        <v>59.8</v>
       </c>
     </row>
     <row r="321">
@@ -8097,22 +8057,22 @@
         <v>54</v>
       </c>
       <c r="B321" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C321" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D321" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E321" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F321" t="n">
-        <v>1252547</v>
+        <v>783</v>
       </c>
       <c r="G321" t="n">
-        <v>53.73</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="322">
@@ -8120,22 +8080,22 @@
         <v>54</v>
       </c>
       <c r="B322" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C322" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D322" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E322" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F322" t="n">
-        <v>1073522</v>
+        <v>1729012</v>
       </c>
       <c r="G322" t="n">
-        <v>46.05</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="323">
@@ -8143,22 +8103,22 @@
         <v>54</v>
       </c>
       <c r="B323" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C323" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D323" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="E323" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F323" t="n">
-        <v>4993</v>
+        <v>2599450</v>
       </c>
       <c r="G323" t="n">
-        <v>0.21</v>
+        <v>60.01</v>
       </c>
     </row>
     <row r="324">
@@ -8166,22 +8126,22 @@
         <v>54</v>
       </c>
       <c r="B324" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C324" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D324" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="E324" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F324" t="n">
-        <v>339</v>
+        <v>3400</v>
       </c>
       <c r="G324" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="325">
@@ -8189,22 +8149,22 @@
         <v>54</v>
       </c>
       <c r="B325" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C325" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D325" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E325" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F325" t="n">
-        <v>1006932</v>
+        <v>79</v>
       </c>
       <c r="G325" t="n">
-        <v>55.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -8212,22 +8172,22 @@
         <v>54</v>
       </c>
       <c r="B326" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C326" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D326" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E326" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F326" t="n">
-        <v>816830</v>
+        <v>700215</v>
       </c>
       <c r="G326" t="n">
-        <v>44.74</v>
+        <v>36.51</v>
       </c>
     </row>
     <row r="327">
@@ -8235,22 +8195,22 @@
         <v>54</v>
       </c>
       <c r="B327" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C327" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D327" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="E327" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F327" t="n">
-        <v>2014</v>
+        <v>1216625</v>
       </c>
       <c r="G327" t="n">
-        <v>0.11</v>
+        <v>63.44</v>
       </c>
     </row>
     <row r="328">
@@ -8258,22 +8218,22 @@
         <v>54</v>
       </c>
       <c r="B328" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C328" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D328" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E328" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F328" t="n">
-        <v>1264191</v>
+        <v>978</v>
       </c>
       <c r="G328" t="n">
-        <v>51.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="329">
@@ -8281,22 +8241,22 @@
         <v>54</v>
       </c>
       <c r="B329" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C329" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D329" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E329" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F329" t="n">
-        <v>1211560</v>
+        <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>48.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -8304,22 +8264,22 @@
         <v>54</v>
       </c>
       <c r="B330" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C330" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D330" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E330" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F330" t="n">
-        <v>1597</v>
+        <v>959368</v>
       </c>
       <c r="G330" t="n">
-        <v>0.06</v>
+        <v>37.56</v>
       </c>
     </row>
     <row r="331">
@@ -8327,45 +8287,45 @@
         <v>54</v>
       </c>
       <c r="B331" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C331" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D331" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="E331" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F331" t="n">
-        <v>79</v>
+        <v>1594385</v>
       </c>
       <c r="G331" t="n">
-        <v>0</v>
+        <v>62.41</v>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="s">
-        <v>54</v>
-      </c>
-      <c r="B332" t="s">
-        <v>107</v>
-      </c>
-      <c r="C332" t="s">
-        <v>22</v>
-      </c>
-      <c r="D332" t="s">
-        <v>43</v>
-      </c>
-      <c r="E332" t="s">
-        <v>108</v>
-      </c>
-      <c r="F332" t="n">
-        <v>1222058</v>
-      </c>
-      <c r="G332" t="n">
-        <v>48.01</v>
+      <c r="A332" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="G332" s="2" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="333">
@@ -8376,19 +8336,19 @@
         <v>107</v>
       </c>
       <c r="C333" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D333" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E333" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F333" t="n">
-        <v>1322800</v>
+        <v>1369885</v>
       </c>
       <c r="G333" t="n">
-        <v>51.97</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="334">
@@ -8399,19 +8359,19 @@
         <v>107</v>
       </c>
       <c r="C334" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D334" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="E334" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F334" t="n">
-        <v>657</v>
+        <v>1130171</v>
       </c>
       <c r="G334" t="n">
-        <v>0.03</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="335">
@@ -8422,19 +8382,19 @@
         <v>107</v>
       </c>
       <c r="C335" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D335" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E335" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F335" t="n">
-        <v>1347818</v>
+        <v>3570</v>
       </c>
       <c r="G335" t="n">
-        <v>48.17</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="336">
@@ -8445,19 +8405,19 @@
         <v>107</v>
       </c>
       <c r="C336" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D336" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E336" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F336" t="n">
-        <v>1450223</v>
+        <v>324</v>
       </c>
       <c r="G336" t="n">
-        <v>51.83</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="337">
@@ -8468,19 +8428,318 @@
         <v>107</v>
       </c>
       <c r="C337" t="s">
+        <v>20</v>
+      </c>
+      <c r="D337" t="s">
+        <v>43</v>
+      </c>
+      <c r="E337" t="s">
+        <v>108</v>
+      </c>
+      <c r="F337" t="n">
+        <v>336013</v>
+      </c>
+      <c r="G337" t="n">
+        <v>50.14</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>54</v>
+      </c>
+      <c r="B338" t="s">
+        <v>107</v>
+      </c>
+      <c r="C338" t="s">
+        <v>20</v>
+      </c>
+      <c r="D338" t="s">
+        <v>14</v>
+      </c>
+      <c r="E338" t="s">
+        <v>109</v>
+      </c>
+      <c r="F338" t="n">
+        <v>333359</v>
+      </c>
+      <c r="G338" t="n">
+        <v>49.74</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>54</v>
+      </c>
+      <c r="B339" t="s">
+        <v>107</v>
+      </c>
+      <c r="C339" t="s">
+        <v>20</v>
+      </c>
+      <c r="D339" t="s">
+        <v>95</v>
+      </c>
+      <c r="E339" t="s">
+        <v>96</v>
+      </c>
+      <c r="F339" t="n">
+        <v>783</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>54</v>
+      </c>
+      <c r="B340" t="s">
+        <v>107</v>
+      </c>
+      <c r="C340" t="s">
+        <v>21</v>
+      </c>
+      <c r="D340" t="s">
+        <v>43</v>
+      </c>
+      <c r="E340" t="s">
+        <v>108</v>
+      </c>
+      <c r="F340" t="n">
+        <v>2255476</v>
+      </c>
+      <c r="G340" t="n">
+        <v>52.07</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>54</v>
+      </c>
+      <c r="B341" t="s">
+        <v>107</v>
+      </c>
+      <c r="C341" t="s">
+        <v>21</v>
+      </c>
+      <c r="D341" t="s">
+        <v>14</v>
+      </c>
+      <c r="E341" t="s">
+        <v>109</v>
+      </c>
+      <c r="F341" t="n">
+        <v>2072987</v>
+      </c>
+      <c r="G341" t="n">
+        <v>47.85</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>54</v>
+      </c>
+      <c r="B342" t="s">
+        <v>107</v>
+      </c>
+      <c r="C342" t="s">
+        <v>21</v>
+      </c>
+      <c r="D342" t="s">
+        <v>95</v>
+      </c>
+      <c r="E342" t="s">
+        <v>96</v>
+      </c>
+      <c r="F342" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G342" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>54</v>
+      </c>
+      <c r="B343" t="s">
+        <v>107</v>
+      </c>
+      <c r="C343" t="s">
+        <v>21</v>
+      </c>
+      <c r="D343" t="s">
+        <v>64</v>
+      </c>
+      <c r="E343" t="s">
+        <v>97</v>
+      </c>
+      <c r="F343" t="n">
+        <v>79</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>54</v>
+      </c>
+      <c r="B344" t="s">
+        <v>107</v>
+      </c>
+      <c r="C344" t="s">
+        <v>22</v>
+      </c>
+      <c r="D344" t="s">
+        <v>43</v>
+      </c>
+      <c r="E344" t="s">
+        <v>108</v>
+      </c>
+      <c r="F344" t="n">
+        <v>909108</v>
+      </c>
+      <c r="G344" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>54</v>
+      </c>
+      <c r="B345" t="s">
+        <v>107</v>
+      </c>
+      <c r="C345" t="s">
+        <v>22</v>
+      </c>
+      <c r="D345" t="s">
+        <v>14</v>
+      </c>
+      <c r="E345" t="s">
+        <v>109</v>
+      </c>
+      <c r="F345" t="n">
+        <v>1007732</v>
+      </c>
+      <c r="G345" t="n">
+        <v>52.55</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>54</v>
+      </c>
+      <c r="B346" t="s">
+        <v>107</v>
+      </c>
+      <c r="C346" t="s">
+        <v>22</v>
+      </c>
+      <c r="D346" t="s">
+        <v>95</v>
+      </c>
+      <c r="E346" t="s">
+        <v>96</v>
+      </c>
+      <c r="F346" t="n">
+        <v>978</v>
+      </c>
+      <c r="G346" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>54</v>
+      </c>
+      <c r="B347" t="s">
+        <v>107</v>
+      </c>
+      <c r="C347" t="s">
+        <v>22</v>
+      </c>
+      <c r="D347" t="s">
+        <v>64</v>
+      </c>
+      <c r="E347" t="s">
+        <v>97</v>
+      </c>
+      <c r="F347" t="n">
+        <v>15</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>54</v>
+      </c>
+      <c r="B348" t="s">
+        <v>107</v>
+      </c>
+      <c r="C348" t="s">
         <v>23</v>
       </c>
-      <c r="D337" t="s">
+      <c r="D348" t="s">
+        <v>43</v>
+      </c>
+      <c r="E348" t="s">
+        <v>108</v>
+      </c>
+      <c r="F348" t="n">
+        <v>1223065</v>
+      </c>
+      <c r="G348" t="n">
+        <v>47.88</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>54</v>
+      </c>
+      <c r="B349" t="s">
+        <v>107</v>
+      </c>
+      <c r="C349" t="s">
+        <v>23</v>
+      </c>
+      <c r="D349" t="s">
+        <v>14</v>
+      </c>
+      <c r="E349" t="s">
+        <v>109</v>
+      </c>
+      <c r="F349" t="n">
+        <v>1330688</v>
+      </c>
+      <c r="G349" t="n">
+        <v>52.09</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>54</v>
+      </c>
+      <c r="B350" t="s">
+        <v>107</v>
+      </c>
+      <c r="C350" t="s">
+        <v>23</v>
+      </c>
+      <c r="D350" t="s">
         <v>95</v>
       </c>
-      <c r="E337" t="s">
+      <c r="E350" t="s">
         <v>96</v>
       </c>
-      <c r="F337" t="n">
-        <v>222</v>
-      </c>
-      <c r="G337" t="n">
-        <v>0.01</v>
+      <c r="F350" t="n">
+        <v>753</v>
+      </c>
+      <c r="G350" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/2025/tabla5_cruces_cluster.xlsx
+++ b/output/tables/2025/tabla5_cruces_cluster.xlsx
@@ -6,26 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cruces_cluster" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cruces_cluster" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
-  <si>
-    <t xml:space="preserve">aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVISIONAL - no citar como número final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 (categorización/clusters) y D5 (índices secundarios) abiertas (PLAN.md): el perfil de cada cluster puede cambiar en ambas partes.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t xml:space="preserve">grupo_variable</t>
   </si>
@@ -695,33 +682,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="21.71" hidden="0" customWidth="1"/>
@@ -734,42 +694,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>1457071</v>
@@ -780,19 +740,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
       </c>
       <c r="F3" t="n">
         <v>914419</v>
@@ -803,19 +763,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>132460</v>
@@ -826,19 +786,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>146781</v>
@@ -849,19 +809,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
         <v>299640</v>
@@ -872,19 +832,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
         <v>223734</v>
@@ -895,19 +855,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>220319</v>
@@ -918,19 +878,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
         <v>3153352</v>
@@ -941,19 +901,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>958271</v>
@@ -964,19 +924,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>76312</v>
@@ -987,19 +947,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
         <v>615481</v>
@@ -1010,19 +970,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>1226039</v>
@@ -1033,19 +993,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>46572</v>
@@ -1056,19 +1016,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
         <v>373748</v>
@@ -1079,19 +1039,19 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>2134186</v>
@@ -1102,19 +1062,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F17" t="n">
         <v>2186949</v>
@@ -1125,19 +1085,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
         <v>293735</v>
@@ -1148,19 +1108,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>23265</v>
@@ -1171,19 +1131,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
         <v>249820</v>
@@ -1194,19 +1154,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
         <v>268126</v>
@@ -1217,19 +1177,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>152209</v>
@@ -1240,19 +1200,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
         <v>21</v>
-      </c>
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s">
-        <v>25</v>
       </c>
       <c r="F23" t="n">
         <v>1042050</v>
@@ -1263,19 +1223,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
         <v>2777993</v>
@@ -1286,19 +1246,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
         <v>511898</v>
@@ -1309,19 +1269,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
         <v>144323</v>
@@ -1332,19 +1292,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
         <v>22</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>26</v>
       </c>
       <c r="F27" t="n">
         <v>1381940</v>
@@ -1355,19 +1315,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>391570</v>
@@ -1378,19 +1338,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F29" t="n">
         <v>97530</v>
@@ -1401,19 +1361,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
         <v>397248</v>
@@ -1424,19 +1384,19 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>2059727</v>
@@ -1447,19 +1407,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F32" t="n">
         <v>2475735</v>
@@ -1470,19 +1430,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F33" t="n">
         <v>23081</v>
@@ -1493,19 +1453,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F34" t="n">
         <v>5133</v>
@@ -1516,19 +1476,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
         <v>538401</v>
@@ -1539,19 +1499,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
         <v>79442</v>
@@ -1562,19 +1522,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F37" t="n">
         <v>52312</v>
@@ -1585,19 +1545,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
         <v>4090442</v>
@@ -1608,19 +1568,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
         <v>171264</v>
@@ -1631,19 +1591,19 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F40" t="n">
         <v>70236</v>
@@ -1654,19 +1614,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F41" t="n">
         <v>715709</v>
@@ -1677,19 +1637,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F42" t="n">
         <v>1190105</v>
@@ -1700,19 +1660,19 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F43" t="n">
         <v>12018</v>
@@ -1723,19 +1683,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F44" t="n">
         <v>1459720</v>
@@ -1746,19 +1706,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
         <v>140238</v>
@@ -1769,19 +1729,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>954548</v>
@@ -1792,19 +1752,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F47" t="n">
         <v>2203991</v>
@@ -1815,19 +1775,19 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F48" t="n">
         <v>133181</v>
@@ -1838,19 +1798,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F49" t="n">
         <v>166029</v>
@@ -1861,19 +1821,19 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
         <v>32</v>
       </c>
-      <c r="C50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" t="s">
-        <v>36</v>
-      </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F50" t="n">
         <v>748</v>
@@ -1884,19 +1844,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F51" t="n">
         <v>347194</v>
@@ -1907,19 +1867,19 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F52" t="n">
         <v>127915</v>
@@ -1930,19 +1890,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F53" t="n">
         <v>195047</v>
@@ -1953,19 +1913,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F54" t="n">
         <v>1857321</v>
@@ -1976,19 +1936,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n">
         <v>686236</v>
@@ -1999,19 +1959,19 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F56" t="n">
         <v>1788384</v>
@@ -2022,19 +1982,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F57" t="n">
         <v>498917</v>
@@ -2045,19 +2005,19 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F58" t="n">
         <v>1051292</v>
@@ -2068,19 +2028,19 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F59" t="n">
         <v>352133</v>
@@ -2091,19 +2051,19 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" t="s">
         <v>32</v>
       </c>
-      <c r="C60" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" t="s">
-        <v>36</v>
-      </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F60" t="n">
         <v>15491</v>
@@ -2114,19 +2074,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F61" t="n">
         <v>460001</v>
@@ -2137,19 +2097,19 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F62" t="n">
         <v>860314</v>
@@ -2160,19 +2120,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>1234191</v>
@@ -2183,19 +2143,19 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
         <v>1186602</v>
@@ -2206,19 +2166,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F65" t="n">
         <v>1194065</v>
@@ -2229,19 +2189,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F66" t="n">
         <v>123283</v>
@@ -2252,19 +2212,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F67" t="n">
         <v>136011</v>
@@ -2275,19 +2235,19 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F68" t="n">
         <v>344068</v>
@@ -2298,19 +2258,19 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C69" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F69" t="n">
         <v>190076</v>
@@ -2321,19 +2281,19 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F70" t="n">
         <v>146213</v>
@@ -2344,19 +2304,19 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
         <v>3188657</v>
@@ -2367,19 +2327,19 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E72" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F72" t="n">
         <v>997072</v>
@@ -2390,19 +2350,19 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C73" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>52457</v>
@@ -2413,19 +2373,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
         <v>586093</v>
@@ -2436,19 +2396,19 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F75" t="n">
         <v>1279282</v>
@@ -2459,19 +2419,19 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F76" t="n">
         <v>65991</v>
@@ -2482,19 +2442,19 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F77" t="n">
         <v>501204</v>
@@ -2505,19 +2465,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>1987310</v>
@@ -2528,19 +2488,19 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E79" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F79" t="n">
         <v>1380968</v>
@@ -2551,19 +2511,19 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F80" t="n">
         <v>1122982</v>
@@ -2574,19 +2534,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C81" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D81" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F81" t="n">
         <v>555959</v>
@@ -2597,19 +2557,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C82" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F82" t="n">
         <v>114197</v>
@@ -2620,19 +2580,19 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F83" t="n">
         <v>1698685</v>
@@ -2643,19 +2603,19 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C84" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F84" t="n">
         <v>2633256</v>
@@ -2666,19 +2626,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C85" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F85" t="n">
         <v>962913</v>
@@ -2689,19 +2649,19 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C86" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F86" t="n">
         <v>954919</v>
@@ -2712,19 +2672,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D87" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E87" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F87" t="n">
         <v>1139730</v>
@@ -2735,19 +2695,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>1414776</v>
@@ -2758,19 +2718,19 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F89" t="n">
         <v>141967</v>
@@ -2781,19 +2741,19 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F90" t="n">
         <v>1524073</v>
@@ -2804,19 +2764,19 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F91" t="n">
         <v>837910</v>
@@ -2827,19 +2787,19 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F92" t="n">
         <v>670155</v>
@@ -2850,19 +2810,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E93" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F93" t="n">
         <v>71577</v>
@@ -2873,19 +2833,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C94" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F94" t="n">
         <v>1851898</v>
@@ -2896,19 +2856,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F95" t="n">
         <v>2408466</v>
@@ -2919,19 +2879,19 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C96" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F96" t="n">
         <v>34104</v>
@@ -2942,19 +2902,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F97" t="n">
         <v>1148759</v>
@@ -2965,19 +2925,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C98" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F98" t="n">
         <v>734969</v>
@@ -2988,19 +2948,19 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F99" t="n">
         <v>63694</v>
@@ -3011,19 +2971,19 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C100" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F100" t="n">
         <v>1479310</v>
@@ -3034,19 +2994,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>1011502</v>
@@ -3057,19 +3017,19 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F102" t="n">
         <v>739963</v>
@@ -3080,19 +3040,19 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F103" t="n">
         <v>779061</v>
@@ -3103,19 +3063,19 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F104" t="n">
         <v>984925</v>
@@ -3126,19 +3086,19 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F105" t="n">
         <v>351974</v>
@@ -3149,19 +3109,19 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C106" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F106" t="n">
         <v>318181</v>
@@ -3172,19 +3132,19 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F107" t="n">
         <v>867646</v>
@@ -3195,19 +3155,19 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C108" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F108" t="n">
         <v>1049676</v>
@@ -3218,19 +3178,19 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F109" t="n">
         <v>2414618</v>
@@ -3241,19 +3201,19 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C110" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E110" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F110" t="n">
         <v>465684</v>
@@ -3264,19 +3224,19 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C111" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F111" t="n">
         <v>727364</v>
@@ -3287,19 +3247,19 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C112" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F112" t="n">
         <v>724785</v>
@@ -3310,19 +3270,19 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D113" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F113" t="n">
         <v>600847</v>
@@ -3333,19 +3293,19 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D114" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F114" t="n">
         <v>770260</v>
@@ -3356,19 +3316,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>1183399</v>
@@ -3379,19 +3339,19 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B116" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F116" t="n">
         <v>1572804</v>
@@ -3402,19 +3362,19 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B117" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F117" t="n">
         <v>931146</v>
@@ -3425,19 +3385,19 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B118" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E118" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F118" t="n">
         <v>326428</v>
@@ -3448,19 +3408,19 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B119" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F119" t="n">
         <v>343728</v>
@@ -3471,19 +3431,19 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B120" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C120" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D120" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F120" t="n">
         <v>2231126</v>
@@ -3494,19 +3454,19 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B121" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C121" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E121" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F121" t="n">
         <v>2100815</v>
@@ -3517,19 +3477,19 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B122" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C122" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F122" t="n">
         <v>774871</v>
@@ -3540,19 +3500,19 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B123" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C123" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E123" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F123" t="n">
         <v>1142962</v>
@@ -3563,19 +3523,19 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B124" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C124" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D124" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E124" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F124" t="n">
         <v>975224</v>
@@ -3586,19 +3546,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>1579281</v>
@@ -3609,19 +3569,19 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" t="s">
         <v>54</v>
       </c>
-      <c r="B126" t="s">
-        <v>58</v>
-      </c>
       <c r="C126" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D126" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E126" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F126" t="n">
         <v>328389</v>
@@ -3632,19 +3592,19 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
+        <v>50</v>
+      </c>
+      <c r="B127" t="s">
         <v>54</v>
       </c>
-      <c r="B127" t="s">
-        <v>58</v>
-      </c>
       <c r="C127" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E127" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F127" t="n">
         <v>1046717</v>
@@ -3655,19 +3615,19 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>50</v>
+      </c>
+      <c r="B128" t="s">
         <v>54</v>
       </c>
-      <c r="B128" t="s">
-        <v>58</v>
-      </c>
       <c r="C128" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D128" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E128" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F128" t="n">
         <v>1118470</v>
@@ -3678,19 +3638,19 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>50</v>
+      </c>
+      <c r="B129" t="s">
         <v>54</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" t="s">
         <v>58</v>
       </c>
-      <c r="C129" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" t="s">
-        <v>62</v>
-      </c>
       <c r="E129" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F129" t="n">
         <v>6684</v>
@@ -3701,19 +3661,19 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>50</v>
+      </c>
+      <c r="B130" t="s">
         <v>54</v>
       </c>
-      <c r="B130" t="s">
-        <v>58</v>
-      </c>
       <c r="C130" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D130" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E130" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F130" t="n">
         <v>3690</v>
@@ -3724,19 +3684,19 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
+        <v>50</v>
+      </c>
+      <c r="B131" t="s">
         <v>54</v>
       </c>
-      <c r="B131" t="s">
-        <v>58</v>
-      </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E131" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F131" t="n">
         <v>107284</v>
@@ -3747,19 +3707,19 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>50</v>
+      </c>
+      <c r="B132" t="s">
         <v>54</v>
       </c>
-      <c r="B132" t="s">
-        <v>58</v>
-      </c>
       <c r="C132" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E132" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F132" t="n">
         <v>293966</v>
@@ -3770,19 +3730,19 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
+        <v>50</v>
+      </c>
+      <c r="B133" t="s">
         <v>54</v>
       </c>
-      <c r="B133" t="s">
-        <v>58</v>
-      </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D133" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F133" t="n">
         <v>265195</v>
@@ -3793,19 +3753,19 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
+        <v>50</v>
+      </c>
+      <c r="B134" t="s">
         <v>54</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" t="s">
         <v>58</v>
       </c>
-      <c r="C134" t="s">
-        <v>20</v>
-      </c>
-      <c r="D134" t="s">
-        <v>62</v>
-      </c>
       <c r="E134" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F134" t="n">
         <v>1878</v>
@@ -3816,19 +3776,19 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
+        <v>50</v>
+      </c>
+      <c r="B135" t="s">
         <v>54</v>
       </c>
-      <c r="B135" t="s">
-        <v>58</v>
-      </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D135" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E135" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F135" t="n">
         <v>1832</v>
@@ -3839,19 +3799,19 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>50</v>
+      </c>
+      <c r="B136" t="s">
         <v>54</v>
       </c>
-      <c r="B136" t="s">
-        <v>58</v>
-      </c>
       <c r="C136" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F136" t="n">
         <v>375549</v>
@@ -3862,19 +3822,19 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>50</v>
+      </c>
+      <c r="B137" t="s">
         <v>54</v>
       </c>
-      <c r="B137" t="s">
-        <v>58</v>
-      </c>
       <c r="C137" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E137" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F137" t="n">
         <v>1708369</v>
@@ -3885,19 +3845,19 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>50</v>
+      </c>
+      <c r="B138" t="s">
         <v>54</v>
       </c>
-      <c r="B138" t="s">
-        <v>58</v>
-      </c>
       <c r="C138" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F138" t="n">
         <v>2232762</v>
@@ -3908,19 +3868,19 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>50</v>
+      </c>
+      <c r="B139" t="s">
         <v>54</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" t="s">
         <v>58</v>
       </c>
-      <c r="C139" t="s">
-        <v>21</v>
-      </c>
-      <c r="D139" t="s">
-        <v>62</v>
-      </c>
       <c r="E139" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F139" t="n">
         <v>9661</v>
@@ -3931,19 +3891,19 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
+        <v>50</v>
+      </c>
+      <c r="B140" t="s">
         <v>54</v>
       </c>
-      <c r="B140" t="s">
-        <v>58</v>
-      </c>
       <c r="C140" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E140" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F140" t="n">
         <v>5600</v>
@@ -3954,19 +3914,19 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
+        <v>50</v>
+      </c>
+      <c r="B141" t="s">
         <v>54</v>
       </c>
-      <c r="B141" t="s">
-        <v>58</v>
-      </c>
       <c r="C141" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E141" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F141" t="n">
         <v>242122</v>
@@ -3977,19 +3937,19 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" t="s">
         <v>54</v>
       </c>
-      <c r="B142" t="s">
-        <v>58</v>
-      </c>
       <c r="C142" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E142" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F142" t="n">
         <v>814250</v>
@@ -4000,19 +3960,19 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
+        <v>50</v>
+      </c>
+      <c r="B143" t="s">
         <v>54</v>
       </c>
-      <c r="B143" t="s">
-        <v>58</v>
-      </c>
       <c r="C143" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F143" t="n">
         <v>854139</v>
@@ -4023,19 +3983,19 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
+        <v>50</v>
+      </c>
+      <c r="B144" t="s">
         <v>54</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
+        <v>18</v>
+      </c>
+      <c r="D144" t="s">
         <v>58</v>
       </c>
-      <c r="C144" t="s">
-        <v>22</v>
-      </c>
-      <c r="D144" t="s">
-        <v>62</v>
-      </c>
       <c r="E144" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F144" t="n">
         <v>4609</v>
@@ -4046,19 +4006,19 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
+        <v>50</v>
+      </c>
+      <c r="B145" t="s">
         <v>54</v>
       </c>
-      <c r="B145" t="s">
-        <v>58</v>
-      </c>
       <c r="C145" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E145" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F145" t="n">
         <v>2712</v>
@@ -4069,19 +4029,19 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>50</v>
+      </c>
+      <c r="B146" t="s">
         <v>54</v>
       </c>
-      <c r="B146" t="s">
-        <v>58</v>
-      </c>
       <c r="C146" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D146" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E146" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F146" t="n">
         <v>305795</v>
@@ -4092,19 +4052,19 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
+        <v>50</v>
+      </c>
+      <c r="B147" t="s">
         <v>54</v>
       </c>
-      <c r="B147" t="s">
-        <v>58</v>
-      </c>
       <c r="C147" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E147" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F147" t="n">
         <v>1113605</v>
@@ -4115,19 +4075,19 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>50</v>
+      </c>
+      <c r="B148" t="s">
         <v>54</v>
       </c>
-      <c r="B148" t="s">
-        <v>58</v>
-      </c>
       <c r="C148" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D148" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E148" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F148" t="n">
         <v>1125121</v>
@@ -4138,19 +4098,19 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
+        <v>50</v>
+      </c>
+      <c r="B149" t="s">
         <v>54</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D149" t="s">
         <v>58</v>
       </c>
-      <c r="C149" t="s">
-        <v>23</v>
-      </c>
-      <c r="D149" t="s">
-        <v>62</v>
-      </c>
       <c r="E149" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F149" t="n">
         <v>5893</v>
@@ -4161,19 +4121,19 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C150" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F150" s="2" t="n">
         <v>4091</v>
@@ -4184,19 +4144,19 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B151" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E151" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F151" t="n">
         <v>684107</v>
@@ -4207,19 +4167,19 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B152" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E152" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F152" t="n">
         <v>1203194</v>
@@ -4230,19 +4190,19 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B153" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F153" t="n">
         <v>616649</v>
@@ -4253,19 +4213,19 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B154" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D154" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F154" t="n">
         <v>171587</v>
@@ -4276,19 +4236,19 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B155" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D155" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E155" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F155" t="n">
         <v>350755</v>
@@ -4299,19 +4259,19 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B156" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C156" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D156" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F156" t="n">
         <v>147813</v>
@@ -4322,19 +4282,19 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B157" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C157" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E157" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F157" t="n">
         <v>1315309</v>
@@ -4345,19 +4305,19 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B158" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C158" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F158" t="n">
         <v>2247623</v>
@@ -4368,19 +4328,19 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B159" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F159" t="n">
         <v>769009</v>
@@ -4391,19 +4351,19 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B160" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C160" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E160" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F160" t="n">
         <v>385897</v>
@@ -4414,19 +4374,19 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B161" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C161" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E161" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F161" t="n">
         <v>1067480</v>
@@ -4437,19 +4397,19 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B162" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C162" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F162" t="n">
         <v>464455</v>
@@ -4460,19 +4420,19 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B163" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C163" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D163" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E163" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F163" t="n">
         <v>425921</v>
@@ -4483,19 +4443,19 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B164" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C164" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E164" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F164" t="n">
         <v>1509153</v>
@@ -4506,19 +4466,19 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F165" s="2" t="n">
         <v>619431</v>
@@ -4529,19 +4489,19 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B166" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C166" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D166" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F166" t="n">
         <v>1022724</v>
@@ -4552,19 +4512,19 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B167" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C167" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E167" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F167" t="n">
         <v>946576</v>
@@ -4575,19 +4535,19 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B168" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C168" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D168" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F168" t="n">
         <v>534649</v>
@@ -4598,19 +4558,19 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B169" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C169" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D169" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E169" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F169" t="n">
         <v>323836</v>
@@ -4621,19 +4581,19 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B170" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C170" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E170" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F170" t="n">
         <v>241856</v>
@@ -4644,19 +4604,19 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B171" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C171" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D171" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E171" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F171" t="n">
         <v>104463</v>
@@ -4667,19 +4627,19 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B172" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C172" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D172" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E172" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F172" t="n">
         <v>1547811</v>
@@ -4690,19 +4650,19 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B173" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C173" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D173" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E173" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F173" t="n">
         <v>1791442</v>
@@ -4713,19 +4673,19 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B174" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C174" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D174" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E174" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F174" t="n">
         <v>992688</v>
@@ -4736,19 +4696,19 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B175" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C175" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D175" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E175" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F175" t="n">
         <v>827930</v>
@@ -4759,19 +4719,19 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B176" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C176" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E176" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F176" t="n">
         <v>772115</v>
@@ -4782,19 +4742,19 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B177" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C177" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D177" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E177" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F177" t="n">
         <v>317788</v>
@@ -4805,19 +4765,19 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B178" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C178" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D178" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E178" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F178" t="n">
         <v>1139363</v>
@@ -4828,19 +4788,19 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B179" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D179" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E179" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F179" t="n">
         <v>1054088</v>
@@ -4851,19 +4811,19 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F180" s="2" t="n">
         <v>361055</v>
@@ -4874,19 +4834,19 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B181" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C181" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E181" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F181" t="n">
         <v>330607</v>
@@ -4897,19 +4857,19 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B182" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C182" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F182" t="n">
         <v>890392</v>
@@ -4920,19 +4880,19 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B183" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C183" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F183" t="n">
         <v>277256</v>
@@ -4943,19 +4903,19 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B184" t="s">
+        <v>70</v>
+      </c>
+      <c r="C184" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" t="s">
         <v>74</v>
       </c>
-      <c r="C184" t="s">
-        <v>13</v>
-      </c>
-      <c r="D184" t="s">
-        <v>78</v>
-      </c>
       <c r="E184" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F184" t="n">
         <v>1005695</v>
@@ -4966,19 +4926,19 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B185" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D185" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E185" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F185" t="n">
         <v>132636</v>
@@ -4989,19 +4949,19 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B186" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C186" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D186" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E186" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F186" t="n">
         <v>224278</v>
@@ -5012,19 +4972,19 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B187" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C187" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D187" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E187" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F187" t="n">
         <v>79203</v>
@@ -5035,19 +4995,19 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B188" t="s">
+        <v>70</v>
+      </c>
+      <c r="C188" t="s">
+        <v>16</v>
+      </c>
+      <c r="D188" t="s">
         <v>74</v>
       </c>
-      <c r="C188" t="s">
-        <v>20</v>
-      </c>
-      <c r="D188" t="s">
-        <v>78</v>
-      </c>
       <c r="E188" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F188" t="n">
         <v>234038</v>
@@ -5058,19 +5018,19 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B189" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C189" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D189" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E189" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F189" t="n">
         <v>508786</v>
@@ -5081,19 +5041,19 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B190" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C190" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D190" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E190" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F190" t="n">
         <v>1259056</v>
@@ -5104,19 +5064,19 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B191" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C191" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D191" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F191" t="n">
         <v>218807</v>
@@ -5127,19 +5087,19 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B192" t="s">
+        <v>70</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
         <v>74</v>
       </c>
-      <c r="C192" t="s">
-        <v>21</v>
-      </c>
-      <c r="D192" t="s">
-        <v>78</v>
-      </c>
       <c r="E192" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F192" t="n">
         <v>2345292</v>
@@ -5150,19 +5110,19 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B193" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C193" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E193" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F193" t="n">
         <v>277225</v>
@@ -5173,19 +5133,19 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B194" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C194" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E194" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F194" t="n">
         <v>667504</v>
@@ -5196,19 +5156,19 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B195" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D195" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F195" t="n">
         <v>113209</v>
@@ -5219,19 +5179,19 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B196" t="s">
+        <v>70</v>
+      </c>
+      <c r="C196" t="s">
+        <v>18</v>
+      </c>
+      <c r="D196" t="s">
         <v>74</v>
       </c>
-      <c r="C196" t="s">
-        <v>22</v>
-      </c>
-      <c r="D196" t="s">
-        <v>78</v>
-      </c>
       <c r="E196" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F196" t="n">
         <v>859895</v>
@@ -5242,19 +5202,19 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B197" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D197" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E197" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F197" t="n">
         <v>309317</v>
@@ -5265,19 +5225,19 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B198" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C198" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D198" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E198" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F198" t="n">
         <v>622609</v>
@@ -5288,19 +5248,19 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B199" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C199" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D199" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F199" t="n">
         <v>83171</v>
@@ -5311,19 +5271,19 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B200" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D200" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C200" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E200" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F200" s="2" t="n">
         <v>1539409</v>
@@ -5334,19 +5294,19 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B201" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C201" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D201" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E201" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F201" t="n">
         <v>2113005</v>
@@ -5357,19 +5317,19 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B202" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C202" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D202" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E202" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F202" t="n">
         <v>390945</v>
@@ -5380,19 +5340,19 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B203" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C203" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D203" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E203" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F203" t="n">
         <v>506278</v>
@@ -5403,19 +5363,19 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B204" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C204" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D204" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E204" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F204" t="n">
         <v>163877</v>
@@ -5426,19 +5386,19 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B205" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C205" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D205" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E205" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F205" t="n">
         <v>3074350</v>
@@ -5449,19 +5409,19 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B206" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C206" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D206" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E206" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F206" t="n">
         <v>1257591</v>
@@ -5472,19 +5432,19 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B207" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C207" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D207" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E207" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F207" t="n">
         <v>1309945</v>
@@ -5495,19 +5455,19 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B208" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C208" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D208" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E208" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F208" t="n">
         <v>607887</v>
@@ -5518,19 +5478,19 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B209" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C209" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D209" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E209" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F209" t="n">
         <v>1706122</v>
@@ -5541,19 +5501,19 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>848383</v>
@@ -5564,19 +5524,19 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B211" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C211" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D211" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E211" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F211" t="n">
         <v>2439497</v>
@@ -5587,19 +5547,19 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B212" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C212" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D212" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E212" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F212" t="n">
         <v>64453</v>
@@ -5610,19 +5570,19 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B213" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C213" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D213" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E213" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F213" t="n">
         <v>629374</v>
@@ -5633,19 +5593,19 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B214" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C214" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D214" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E214" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F214" t="n">
         <v>40782</v>
@@ -5656,19 +5616,19 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B215" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C215" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D215" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E215" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F215" t="n">
         <v>4098166</v>
@@ -5679,19 +5639,19 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B216" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C216" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D216" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E216" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F216" t="n">
         <v>233775</v>
@@ -5702,19 +5662,19 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B217" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C217" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D217" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E217" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F217" t="n">
         <v>1800965</v>
@@ -5725,19 +5685,19 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B218" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C218" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D218" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E218" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F218" t="n">
         <v>116867</v>
@@ -5748,19 +5708,19 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B219" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C219" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D219" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E219" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F219" t="n">
         <v>2368182</v>
@@ -5771,19 +5731,19 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F220" s="2" t="n">
         <v>186324</v>
@@ -5794,19 +5754,19 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B221" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C221" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E221" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F221" t="n">
         <v>1186500</v>
@@ -5817,19 +5777,19 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B222" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C222" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D222" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E222" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F222" t="n">
         <v>774822</v>
@@ -5840,19 +5800,19 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B223" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C223" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D223" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E223" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F223" t="n">
         <v>540688</v>
@@ -5863,13 +5823,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B224" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C224" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D224"/>
       <c r="E224"/>
@@ -5882,19 +5842,19 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B225" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C225" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D225" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E225" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F225" t="n">
         <v>234120</v>
@@ -5905,19 +5865,19 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B226" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C226" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D226" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E226" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F226" t="n">
         <v>198783</v>
@@ -5928,19 +5888,19 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B227" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C227" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D227" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E227" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F227" t="n">
         <v>236530</v>
@@ -5951,13 +5911,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B228" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C228" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D228"/>
       <c r="E228"/>
@@ -5970,19 +5930,19 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C229" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D229" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F229" t="n">
         <v>1138176</v>
@@ -5993,19 +5953,19 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B230" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C230" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D230" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E230" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F230" t="n">
         <v>1441225</v>
@@ -6016,19 +5976,19 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B231" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C231" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D231" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F231" t="n">
         <v>1751066</v>
@@ -6039,13 +5999,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B232" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C232" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D232"/>
       <c r="E232"/>
@@ -6058,19 +6018,19 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B233" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C233" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D233" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E233" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F233" t="n">
         <v>429107</v>
@@ -6081,19 +6041,19 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B234" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C234" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D234" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E234" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F234" t="n">
         <v>573212</v>
@@ -6104,19 +6064,19 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B235" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C235" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D235" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F235" t="n">
         <v>915216</v>
@@ -6127,13 +6087,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B236" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C236" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D236"/>
       <c r="E236"/>
@@ -6146,19 +6106,19 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B237" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C237" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D237" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E237" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F237" t="n">
         <v>371949</v>
@@ -6169,19 +6129,19 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B238" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C238" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D238" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E238" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F238" t="n">
         <v>623803</v>
@@ -6192,19 +6152,19 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B239" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C239" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D239" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F239" t="n">
         <v>1558075</v>
@@ -6215,13 +6175,13 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
@@ -6234,19 +6194,19 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B241" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C241" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D241" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E241" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F241" t="n">
         <v>1164220</v>
@@ -6257,19 +6217,19 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B242" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C242" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E242" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F242" t="n">
         <v>926342</v>
@@ -6280,19 +6240,19 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B243" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C243" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D243" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E243" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F243" t="n">
         <v>410706</v>
@@ -6303,13 +6263,13 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B244" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C244" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D244"/>
       <c r="E244"/>
@@ -6322,19 +6282,19 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B245" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C245" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D245" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E245" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F245" t="n">
         <v>211816</v>
@@ -6345,19 +6305,19 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B246" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C246" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D246" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E246" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F246" t="n">
         <v>225454</v>
@@ -6368,19 +6328,19 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B247" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C247" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D247" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E247" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F247" t="n">
         <v>232195</v>
@@ -6391,13 +6351,13 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B248" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C248" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D248"/>
       <c r="E248"/>
@@ -6410,19 +6370,19 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B249" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C249" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D249" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E249" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F249" t="n">
         <v>944162</v>
@@ -6433,19 +6393,19 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B250" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C250" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D250" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E250" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F250" t="n">
         <v>1760575</v>
@@ -6456,19 +6416,19 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B251" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C251" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D251" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E251" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F251" t="n">
         <v>1623359</v>
@@ -6479,13 +6439,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B252" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C252" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D252"/>
       <c r="E252"/>
@@ -6498,19 +6458,19 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B253" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C253" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D253" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E253" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F253" t="n">
         <v>302569</v>
@@ -6521,19 +6481,19 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B254" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C254" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D254" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E254" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F254" t="n">
         <v>696666</v>
@@ -6544,19 +6504,19 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B255" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C255" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D255" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E255" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F255" t="n">
         <v>917202</v>
@@ -6567,13 +6527,13 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B256" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C256" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D256"/>
       <c r="E256"/>
@@ -6586,19 +6546,19 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B257" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C257" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D257" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E257" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F257" t="n">
         <v>224456</v>
@@ -6609,19 +6569,19 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B258" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C258" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D258" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E258" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F258" t="n">
         <v>698051</v>
@@ -6632,19 +6592,19 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B259" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C259" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D259" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F259" t="n">
         <v>1625894</v>
@@ -6655,13 +6615,13 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
@@ -6674,19 +6634,19 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B261" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C261" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D261" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E261" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F261" t="n">
         <v>1919750</v>
@@ -6697,19 +6657,19 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B262" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C262" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D262" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E262" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F262" t="n">
         <v>580306</v>
@@ -6720,19 +6680,19 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B263" t="s">
+        <v>88</v>
+      </c>
+      <c r="C263" t="s">
+        <v>9</v>
+      </c>
+      <c r="D263" t="s">
+        <v>91</v>
+      </c>
+      <c r="E263" t="s">
         <v>92</v>
-      </c>
-      <c r="C263" t="s">
-        <v>13</v>
-      </c>
-      <c r="D263" t="s">
-        <v>95</v>
-      </c>
-      <c r="E263" t="s">
-        <v>96</v>
       </c>
       <c r="F263" t="n">
         <v>3570</v>
@@ -6743,19 +6703,19 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B264" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C264" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D264" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E264" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F264" t="n">
         <v>324</v>
@@ -6766,19 +6726,19 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B265" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C265" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D265" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E265" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F265" t="n">
         <v>513700</v>
@@ -6789,19 +6749,19 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B266" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C266" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D266" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E266" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F266" t="n">
         <v>155672</v>
@@ -6812,19 +6772,19 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B267" t="s">
+        <v>88</v>
+      </c>
+      <c r="C267" t="s">
+        <v>16</v>
+      </c>
+      <c r="D267" t="s">
+        <v>91</v>
+      </c>
+      <c r="E267" t="s">
         <v>92</v>
-      </c>
-      <c r="C267" t="s">
-        <v>20</v>
-      </c>
-      <c r="D267" t="s">
-        <v>95</v>
-      </c>
-      <c r="E267" t="s">
-        <v>96</v>
       </c>
       <c r="F267" t="n">
         <v>783</v>
@@ -6835,19 +6795,19 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B268" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C268" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D268" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E268" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F268" t="n">
         <v>3394170</v>
@@ -6858,19 +6818,19 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B269" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C269" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D269" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E269" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F269" t="n">
         <v>934292</v>
@@ -6881,19 +6841,19 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B270" t="s">
+        <v>88</v>
+      </c>
+      <c r="C270" t="s">
+        <v>17</v>
+      </c>
+      <c r="D270" t="s">
+        <v>91</v>
+      </c>
+      <c r="E270" t="s">
         <v>92</v>
-      </c>
-      <c r="C270" t="s">
-        <v>21</v>
-      </c>
-      <c r="D270" t="s">
-        <v>95</v>
-      </c>
-      <c r="E270" t="s">
-        <v>96</v>
       </c>
       <c r="F270" t="n">
         <v>3400</v>
@@ -6904,19 +6864,19 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B271" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C271" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D271" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E271" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F271" t="n">
         <v>79</v>
@@ -6927,19 +6887,19 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B272" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C272" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D272" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E272" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F272" t="n">
         <v>1470345</v>
@@ -6950,19 +6910,19 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B273" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C273" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D273" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E273" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F273" t="n">
         <v>446494</v>
@@ -6973,19 +6933,19 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B274" t="s">
+        <v>88</v>
+      </c>
+      <c r="C274" t="s">
+        <v>18</v>
+      </c>
+      <c r="D274" t="s">
+        <v>91</v>
+      </c>
+      <c r="E274" t="s">
         <v>92</v>
-      </c>
-      <c r="C274" t="s">
-        <v>22</v>
-      </c>
-      <c r="D274" t="s">
-        <v>95</v>
-      </c>
-      <c r="E274" t="s">
-        <v>96</v>
       </c>
       <c r="F274" t="n">
         <v>978</v>
@@ -6996,19 +6956,19 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B275" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C275" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D275" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E275" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F275" t="n">
         <v>15</v>
@@ -7019,19 +6979,19 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B276" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C276" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D276" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E276" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F276" t="n">
         <v>1896963</v>
@@ -7042,19 +7002,19 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B277" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C277" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D277" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E277" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F277" t="n">
         <v>656790</v>
@@ -7065,19 +7025,19 @@
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B278" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F278" s="2" t="n">
         <v>753</v>
@@ -7088,19 +7048,19 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B279" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C279" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D279" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E279" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F279" t="n">
         <v>1106125</v>
@@ -7111,19 +7071,19 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B280" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C280" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E280" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F280" t="n">
         <v>1393931</v>
@@ -7134,19 +7094,19 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B281" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C281" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D281" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E281" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F281" t="n">
         <v>3570</v>
@@ -7157,19 +7117,19 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B282" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C282" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D282" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E282" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F282" t="n">
         <v>324</v>
@@ -7180,19 +7140,19 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B283" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C283" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D283" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E283" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F283" t="n">
         <v>297801</v>
@@ -7203,19 +7163,19 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B284" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C284" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D284" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E284" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F284" t="n">
         <v>371571</v>
@@ -7226,19 +7186,19 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B285" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C285" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D285" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E285" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F285" t="n">
         <v>783</v>
@@ -7249,19 +7209,19 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B286" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C286" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D286" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E286" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F286" t="n">
         <v>1810510</v>
@@ -7272,19 +7232,19 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B287" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C287" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D287" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E287" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F287" t="n">
         <v>2517953</v>
@@ -7295,19 +7255,19 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B288" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C288" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D288" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E288" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F288" t="n">
         <v>3400</v>
@@ -7318,19 +7278,19 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B289" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C289" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D289" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E289" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F289" t="n">
         <v>79</v>
@@ -7341,19 +7301,19 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B290" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C290" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D290" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E290" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F290" t="n">
         <v>760636</v>
@@ -7364,19 +7324,19 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B291" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C291" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D291" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E291" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F291" t="n">
         <v>1156203</v>
@@ -7387,19 +7347,19 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B292" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C292" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D292" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E292" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F292" t="n">
         <v>978</v>
@@ -7410,19 +7370,19 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B293" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C293" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D293" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E293" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F293" t="n">
         <v>15</v>
@@ -7433,19 +7393,19 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B294" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C294" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D294" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E294" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F294" t="n">
         <v>1106700</v>
@@ -7456,19 +7416,19 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B295" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C295" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D295" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E295" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F295" t="n">
         <v>1447053</v>
@@ -7479,19 +7439,19 @@
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F296" s="2" t="n">
         <v>753</v>
@@ -7502,19 +7462,19 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B297" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C297" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D297" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E297" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F297" t="n">
         <v>1073916</v>
@@ -7525,19 +7485,19 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B298" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C298" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D298" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E298" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F298" t="n">
         <v>1426140</v>
@@ -7548,19 +7508,19 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B299" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C299" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D299" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E299" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F299" t="n">
         <v>3570</v>
@@ -7571,19 +7531,19 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B300" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C300" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D300" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E300" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F300" t="n">
         <v>324</v>
@@ -7594,19 +7554,19 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B301" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C301" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D301" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E301" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F301" t="n">
         <v>269921</v>
@@ -7617,19 +7577,19 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B302" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C302" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D302" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E302" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F302" t="n">
         <v>399452</v>
@@ -7640,19 +7600,19 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B303" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C303" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D303" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E303" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F303" t="n">
         <v>783</v>
@@ -7663,19 +7623,19 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B304" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C304" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D304" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E304" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F304" t="n">
         <v>1696166</v>
@@ -7686,19 +7646,19 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B305" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C305" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D305" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E305" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F305" t="n">
         <v>2632296</v>
@@ -7709,19 +7669,19 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B306" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C306" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D306" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E306" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F306" t="n">
         <v>3400</v>
@@ -7732,19 +7692,19 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B307" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C307" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D307" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E307" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F307" t="n">
         <v>79</v>
@@ -7755,19 +7715,19 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B308" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C308" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D308" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E308" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F308" t="n">
         <v>806688</v>
@@ -7778,19 +7738,19 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B309" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C309" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D309" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E309" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F309" t="n">
         <v>1110151</v>
@@ -7801,19 +7761,19 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B310" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C310" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D310" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E310" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F310" t="n">
         <v>978</v>
@@ -7824,19 +7784,19 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B311" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C311" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D311" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E311" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F311" t="n">
         <v>15</v>
@@ -7847,19 +7807,19 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B312" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C312" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D312" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E312" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F312" t="n">
         <v>1146555</v>
@@ -7870,19 +7830,19 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B313" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C313" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D313" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E313" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F313" t="n">
         <v>1407198</v>
@@ -7893,19 +7853,19 @@
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F314" s="2" t="n">
         <v>753</v>
@@ -7916,19 +7876,19 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B315" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C315" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D315" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E315" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F315" t="n">
         <v>1042147</v>
@@ -7939,19 +7899,19 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B316" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C316" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D316" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E316" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F316" t="n">
         <v>1457909</v>
@@ -7962,19 +7922,19 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B317" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C317" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D317" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E317" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F317" t="n">
         <v>3570</v>
@@ -7985,19 +7945,19 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B318" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C318" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D318" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E318" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F318" t="n">
         <v>324</v>
@@ -8008,19 +7968,19 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B319" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C319" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D319" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E319" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F319" t="n">
         <v>268614</v>
@@ -8031,19 +7991,19 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B320" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C320" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D320" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E320" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F320" t="n">
         <v>400758</v>
@@ -8054,19 +8014,19 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B321" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C321" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D321" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E321" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F321" t="n">
         <v>783</v>
@@ -8077,19 +8037,19 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B322" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C322" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D322" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E322" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F322" t="n">
         <v>1729012</v>
@@ -8100,19 +8060,19 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B323" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C323" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D323" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E323" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F323" t="n">
         <v>2599450</v>
@@ -8123,19 +8083,19 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B324" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C324" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D324" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E324" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F324" t="n">
         <v>3400</v>
@@ -8146,19 +8106,19 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B325" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C325" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D325" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E325" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F325" t="n">
         <v>79</v>
@@ -8169,19 +8129,19 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B326" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C326" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D326" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E326" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F326" t="n">
         <v>700215</v>
@@ -8192,19 +8152,19 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B327" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C327" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D327" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E327" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F327" t="n">
         <v>1216625</v>
@@ -8215,19 +8175,19 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B328" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C328" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D328" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E328" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F328" t="n">
         <v>978</v>
@@ -8238,19 +8198,19 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B329" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C329" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D329" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E329" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F329" t="n">
         <v>15</v>
@@ -8261,19 +8221,19 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B330" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C330" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D330" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E330" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F330" t="n">
         <v>959368</v>
@@ -8284,19 +8244,19 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B331" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C331" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D331" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E331" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F331" t="n">
         <v>1594385</v>
@@ -8307,19 +8267,19 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F332" s="2" t="n">
         <v>753</v>
@@ -8330,19 +8290,19 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B333" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C333" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D333" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E333" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F333" t="n">
         <v>1369885</v>
@@ -8353,19 +8313,19 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B334" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C334" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D334" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E334" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F334" t="n">
         <v>1130171</v>
@@ -8376,19 +8336,19 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B335" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C335" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D335" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E335" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F335" t="n">
         <v>3570</v>
@@ -8399,19 +8359,19 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B336" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C336" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D336" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E336" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F336" t="n">
         <v>324</v>
@@ -8422,19 +8382,19 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B337" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C337" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D337" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E337" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F337" t="n">
         <v>336013</v>
@@ -8445,19 +8405,19 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B338" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C338" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D338" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E338" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F338" t="n">
         <v>333359</v>
@@ -8468,19 +8428,19 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B339" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C339" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D339" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E339" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F339" t="n">
         <v>783</v>
@@ -8491,19 +8451,19 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B340" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C340" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D340" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E340" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F340" t="n">
         <v>2255476</v>
@@ -8514,19 +8474,19 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B341" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C341" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D341" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E341" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F341" t="n">
         <v>2072987</v>
@@ -8537,19 +8497,19 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B342" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C342" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D342" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E342" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F342" t="n">
         <v>3400</v>
@@ -8560,19 +8520,19 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B343" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C343" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D343" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E343" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F343" t="n">
         <v>79</v>
@@ -8583,19 +8543,19 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B344" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C344" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D344" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E344" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F344" t="n">
         <v>909108</v>
@@ -8606,19 +8566,19 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B345" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C345" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D345" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E345" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F345" t="n">
         <v>1007732</v>
@@ -8629,19 +8589,19 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B346" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C346" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D346" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E346" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F346" t="n">
         <v>978</v>
@@ -8652,19 +8612,19 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B347" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C347" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D347" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E347" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F347" t="n">
         <v>15</v>
@@ -8675,19 +8635,19 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B348" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C348" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D348" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E348" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F348" t="n">
         <v>1223065</v>
@@ -8698,19 +8658,19 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B349" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C349" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D349" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E349" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F349" t="n">
         <v>1330688</v>
@@ -8721,19 +8681,19 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B350" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C350" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D350" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E350" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F350" t="n">
         <v>753</v>

--- a/output/tables/2025/tabla5_cruces_cluster.xlsx
+++ b/output/tables/2025/tabla5_cruces_cluster.xlsx
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_cat</t>
+    <t xml:space="preserve">comgen_per_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en la vivienda</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">Tres o más medidas en la vivienda</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_cat</t>
+    <t xml:space="preserve">comgen_com_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en el barrio</t>

--- a/output/tables/2025/tabla5_cruces_cluster.xlsx
+++ b/output/tables/2025/tabla5_cruces_cluster.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t xml:space="preserve">grupo_variable</t>
   </si>
@@ -278,6 +278,33 @@
     <t xml:space="preserve">Alta percepción de incivilidades</t>
   </si>
   <si>
+    <t xml:space="preserve">p_aumento_pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aumentó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se mantuvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disminuyó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No sabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_barrio</t>
+  </si>
+  <si>
     <t xml:space="preserve">info_exp_personal</t>
   </si>
   <si>
@@ -285,15 +312,6 @@
   </si>
   <si>
     <t xml:space="preserve">Se informa por experiencia personal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No sabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No responde</t>
   </si>
   <si>
     <t xml:space="preserve">info_otras_personas</t>
@@ -6643,16 +6661,16 @@
         <v>9</v>
       </c>
       <c r="D261" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E261" t="s">
         <v>89</v>
       </c>
       <c r="F261" t="n">
-        <v>1919750</v>
+        <v>1632610</v>
       </c>
       <c r="G261" t="n">
-        <v>76.67</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="262">
@@ -6666,16 +6684,16 @@
         <v>9</v>
       </c>
       <c r="D262" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E262" t="s">
         <v>90</v>
       </c>
       <c r="F262" t="n">
-        <v>580306</v>
+        <v>682382</v>
       </c>
       <c r="G262" t="n">
-        <v>23.18</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="263">
@@ -6689,16 +6707,16 @@
         <v>9</v>
       </c>
       <c r="D263" t="s">
+        <v>14</v>
+      </c>
+      <c r="E263" t="s">
         <v>91</v>
       </c>
-      <c r="E263" t="s">
-        <v>92</v>
-      </c>
       <c r="F263" t="n">
-        <v>3570</v>
+        <v>157176</v>
       </c>
       <c r="G263" t="n">
-        <v>0.14</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="264">
@@ -6712,16 +6730,16 @@
         <v>9</v>
       </c>
       <c r="D264" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E264" t="s">
         <v>93</v>
       </c>
       <c r="F264" t="n">
-        <v>324</v>
+        <v>30542</v>
       </c>
       <c r="G264" t="n">
-        <v>0.01</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="265">
@@ -6732,19 +6750,19 @@
         <v>88</v>
       </c>
       <c r="C265" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E265" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F265" t="n">
-        <v>513700</v>
+        <v>1239</v>
       </c>
       <c r="G265" t="n">
-        <v>76.65</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="266">
@@ -6761,13 +6779,13 @@
         <v>10</v>
       </c>
       <c r="E266" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F266" t="n">
-        <v>155672</v>
+        <v>556703</v>
       </c>
       <c r="G266" t="n">
-        <v>23.23</v>
+        <v>83.07</v>
       </c>
     </row>
     <row r="267">
@@ -6781,16 +6799,16 @@
         <v>16</v>
       </c>
       <c r="D267" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E267" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F267" t="n">
-        <v>783</v>
+        <v>94675</v>
       </c>
       <c r="G267" t="n">
-        <v>0.12</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="268">
@@ -6801,19 +6819,19 @@
         <v>88</v>
       </c>
       <c r="C268" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D268" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E268" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F268" t="n">
-        <v>3394170</v>
+        <v>13669</v>
       </c>
       <c r="G268" t="n">
-        <v>78.35</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="269">
@@ -6824,19 +6842,19 @@
         <v>88</v>
       </c>
       <c r="C269" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D269" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E269" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F269" t="n">
-        <v>934292</v>
+        <v>5107</v>
       </c>
       <c r="G269" t="n">
-        <v>21.57</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="270">
@@ -6850,16 +6868,16 @@
         <v>17</v>
       </c>
       <c r="D270" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="E270" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F270" t="n">
-        <v>3400</v>
+        <v>3520693</v>
       </c>
       <c r="G270" t="n">
-        <v>0.08</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="271">
@@ -6873,16 +6891,16 @@
         <v>17</v>
       </c>
       <c r="D271" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E271" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F271" t="n">
-        <v>79</v>
+        <v>721769</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="272">
@@ -6893,19 +6911,19 @@
         <v>88</v>
       </c>
       <c r="C272" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D272" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E272" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F272" t="n">
-        <v>1470345</v>
+        <v>73110</v>
       </c>
       <c r="G272" t="n">
-        <v>76.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="273">
@@ -6916,19 +6934,19 @@
         <v>88</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D273" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E273" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F273" t="n">
-        <v>446494</v>
+        <v>16305</v>
       </c>
       <c r="G273" t="n">
-        <v>23.28</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="274">
@@ -6939,19 +6957,19 @@
         <v>88</v>
       </c>
       <c r="C274" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D274" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="E274" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F274" t="n">
-        <v>978</v>
+        <v>63</v>
       </c>
       <c r="G274" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -6965,16 +6983,16 @@
         <v>18</v>
       </c>
       <c r="D275" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E275" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F275" t="n">
-        <v>15</v>
+        <v>1782326</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>92.93</v>
       </c>
     </row>
     <row r="276">
@@ -6985,19 +7003,19 @@
         <v>88</v>
       </c>
       <c r="C276" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D276" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E276" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F276" t="n">
-        <v>1896963</v>
+        <v>123221</v>
       </c>
       <c r="G276" t="n">
-        <v>74.26</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="277">
@@ -7008,42 +7026,42 @@
         <v>88</v>
       </c>
       <c r="C277" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D277" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E277" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F277" t="n">
-        <v>656790</v>
+        <v>8031</v>
       </c>
       <c r="G277" t="n">
-        <v>25.71</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B278" s="2" t="s">
+      <c r="A278" t="s">
+        <v>50</v>
+      </c>
+      <c r="B278" t="s">
         <v>88</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E278" s="2" t="s">
+      <c r="C278" t="s">
+        <v>18</v>
+      </c>
+      <c r="D278" t="s">
         <v>92</v>
       </c>
-      <c r="F278" s="2" t="n">
-        <v>753</v>
-      </c>
-      <c r="G278" s="2" t="n">
-        <v>0.03</v>
+      <c r="E278" t="s">
+        <v>93</v>
+      </c>
+      <c r="F278" t="n">
+        <v>3923</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="279">
@@ -7051,22 +7069,22 @@
         <v>50</v>
       </c>
       <c r="B279" t="s">
+        <v>88</v>
+      </c>
+      <c r="C279" t="s">
+        <v>18</v>
+      </c>
+      <c r="D279" t="s">
+        <v>60</v>
+      </c>
+      <c r="E279" t="s">
         <v>94</v>
       </c>
-      <c r="C279" t="s">
-        <v>9</v>
-      </c>
-      <c r="D279" t="s">
-        <v>39</v>
-      </c>
-      <c r="E279" t="s">
-        <v>95</v>
-      </c>
       <c r="F279" t="n">
-        <v>1106125</v>
+        <v>332</v>
       </c>
       <c r="G279" t="n">
-        <v>44.18</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="280">
@@ -7074,22 +7092,22 @@
         <v>50</v>
       </c>
       <c r="B280" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C280" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D280" t="s">
         <v>10</v>
       </c>
       <c r="E280" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F280" t="n">
-        <v>1393931</v>
+        <v>2422711</v>
       </c>
       <c r="G280" t="n">
-        <v>55.67</v>
+        <v>94.84</v>
       </c>
     </row>
     <row r="281">
@@ -7097,22 +7115,22 @@
         <v>50</v>
       </c>
       <c r="B281" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C281" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D281" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E281" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F281" t="n">
-        <v>3570</v>
+        <v>119503</v>
       </c>
       <c r="G281" t="n">
-        <v>0.14</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="282">
@@ -7120,22 +7138,22 @@
         <v>50</v>
       </c>
       <c r="B282" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C282" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D282" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E282" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F282" t="n">
-        <v>324</v>
+        <v>9524</v>
       </c>
       <c r="G282" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="283">
@@ -7143,45 +7161,45 @@
         <v>50</v>
       </c>
       <c r="B283" t="s">
+        <v>88</v>
+      </c>
+      <c r="C283" t="s">
+        <v>19</v>
+      </c>
+      <c r="D283" t="s">
+        <v>92</v>
+      </c>
+      <c r="E283" t="s">
+        <v>93</v>
+      </c>
+      <c r="F283" t="n">
+        <v>2077</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E284" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C283" t="s">
-        <v>16</v>
-      </c>
-      <c r="D283" t="s">
-        <v>39</v>
-      </c>
-      <c r="E283" t="s">
-        <v>95</v>
-      </c>
-      <c r="F283" t="n">
-        <v>297801</v>
-      </c>
-      <c r="G283" t="n">
-        <v>44.44</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="s">
-        <v>50</v>
-      </c>
-      <c r="B284" t="s">
-        <v>94</v>
-      </c>
-      <c r="C284" t="s">
-        <v>16</v>
-      </c>
-      <c r="D284" t="s">
-        <v>10</v>
-      </c>
-      <c r="E284" t="s">
-        <v>96</v>
-      </c>
-      <c r="F284" t="n">
-        <v>371571</v>
-      </c>
-      <c r="G284" t="n">
-        <v>55.45</v>
+      <c r="F284" s="2" t="n">
+        <v>691</v>
+      </c>
+      <c r="G284" s="2" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="285">
@@ -7189,22 +7207,22 @@
         <v>50</v>
       </c>
       <c r="B285" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C285" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D285" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="E285" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F285" t="n">
-        <v>783</v>
+        <v>1166484</v>
       </c>
       <c r="G285" t="n">
-        <v>0.12</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="286">
@@ -7212,22 +7230,22 @@
         <v>50</v>
       </c>
       <c r="B286" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C286" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D286" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E286" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F286" t="n">
-        <v>1810510</v>
+        <v>1060647</v>
       </c>
       <c r="G286" t="n">
-        <v>41.79</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="287">
@@ -7235,22 +7253,22 @@
         <v>50</v>
       </c>
       <c r="B287" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C287" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D287" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E287" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F287" t="n">
-        <v>2517953</v>
+        <v>215173</v>
       </c>
       <c r="G287" t="n">
-        <v>58.13</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="288">
@@ -7258,22 +7276,22 @@
         <v>50</v>
       </c>
       <c r="B288" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C288" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D288" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E288" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F288" t="n">
-        <v>3400</v>
+        <v>60006</v>
       </c>
       <c r="G288" t="n">
-        <v>0.08</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="289">
@@ -7281,22 +7299,22 @@
         <v>50</v>
       </c>
       <c r="B289" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C289" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D289" t="s">
         <v>60</v>
       </c>
       <c r="E289" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F289" t="n">
-        <v>79</v>
+        <v>1641</v>
       </c>
       <c r="G289" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="290">
@@ -7304,22 +7322,22 @@
         <v>50</v>
       </c>
       <c r="B290" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C290" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D290" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E290" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F290" t="n">
-        <v>760636</v>
+        <v>458129</v>
       </c>
       <c r="G290" t="n">
-        <v>39.66</v>
+        <v>68.36</v>
       </c>
     </row>
     <row r="291">
@@ -7327,22 +7345,22 @@
         <v>50</v>
       </c>
       <c r="B291" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C291" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D291" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E291" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F291" t="n">
-        <v>1156203</v>
+        <v>177458</v>
       </c>
       <c r="G291" t="n">
-        <v>60.29</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="292">
@@ -7350,22 +7368,22 @@
         <v>50</v>
       </c>
       <c r="B292" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C292" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D292" t="s">
+        <v>14</v>
+      </c>
+      <c r="E292" t="s">
         <v>91</v>
       </c>
-      <c r="E292" t="s">
-        <v>92</v>
-      </c>
       <c r="F292" t="n">
-        <v>978</v>
+        <v>22259</v>
       </c>
       <c r="G292" t="n">
-        <v>0.05</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="293">
@@ -7373,22 +7391,22 @@
         <v>50</v>
       </c>
       <c r="B293" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C293" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D293" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E293" t="s">
         <v>93</v>
       </c>
       <c r="F293" t="n">
-        <v>15</v>
+        <v>12267</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="294">
@@ -7396,22 +7414,22 @@
         <v>50</v>
       </c>
       <c r="B294" t="s">
+        <v>95</v>
+      </c>
+      <c r="C294" t="s">
+        <v>16</v>
+      </c>
+      <c r="D294" t="s">
+        <v>60</v>
+      </c>
+      <c r="E294" t="s">
         <v>94</v>
       </c>
-      <c r="C294" t="s">
-        <v>19</v>
-      </c>
-      <c r="D294" t="s">
-        <v>39</v>
-      </c>
-      <c r="E294" t="s">
-        <v>95</v>
-      </c>
       <c r="F294" t="n">
-        <v>1106700</v>
+        <v>41</v>
       </c>
       <c r="G294" t="n">
-        <v>43.32</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="295">
@@ -7419,45 +7437,45 @@
         <v>50</v>
       </c>
       <c r="B295" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C295" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D295" t="s">
         <v>10</v>
       </c>
       <c r="E295" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F295" t="n">
-        <v>1447053</v>
+        <v>2982670</v>
       </c>
       <c r="G295" t="n">
-        <v>56.65</v>
+        <v>68.85</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F296" s="2" t="n">
-        <v>753</v>
-      </c>
-      <c r="G296" s="2" t="n">
-        <v>0.03</v>
+      <c r="A296" t="s">
+        <v>50</v>
+      </c>
+      <c r="B296" t="s">
+        <v>95</v>
+      </c>
+      <c r="C296" t="s">
+        <v>17</v>
+      </c>
+      <c r="D296" t="s">
+        <v>12</v>
+      </c>
+      <c r="E296" t="s">
+        <v>90</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1140901</v>
+      </c>
+      <c r="G296" t="n">
+        <v>26.34</v>
       </c>
     </row>
     <row r="297">
@@ -7465,22 +7483,22 @@
         <v>50</v>
       </c>
       <c r="B297" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C297" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D297" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E297" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F297" t="n">
-        <v>1073916</v>
+        <v>149677</v>
       </c>
       <c r="G297" t="n">
-        <v>42.89</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="298">
@@ -7488,22 +7506,22 @@
         <v>50</v>
       </c>
       <c r="B298" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C298" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D298" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E298" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F298" t="n">
-        <v>1426140</v>
+        <v>57471</v>
       </c>
       <c r="G298" t="n">
-        <v>56.96</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="299">
@@ -7511,22 +7529,22 @@
         <v>50</v>
       </c>
       <c r="B299" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C299" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D299" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="E299" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F299" t="n">
-        <v>3570</v>
+        <v>1222</v>
       </c>
       <c r="G299" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="300">
@@ -7534,22 +7552,22 @@
         <v>50</v>
       </c>
       <c r="B300" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C300" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D300" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E300" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F300" t="n">
-        <v>324</v>
+        <v>1629041</v>
       </c>
       <c r="G300" t="n">
-        <v>0.01</v>
+        <v>84.94</v>
       </c>
     </row>
     <row r="301">
@@ -7557,22 +7575,22 @@
         <v>50</v>
       </c>
       <c r="B301" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C301" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D301" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E301" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F301" t="n">
-        <v>269921</v>
+        <v>253443</v>
       </c>
       <c r="G301" t="n">
-        <v>40.28</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="302">
@@ -7580,22 +7598,22 @@
         <v>50</v>
       </c>
       <c r="B302" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C302" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D302" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E302" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F302" t="n">
-        <v>399452</v>
+        <v>23440</v>
       </c>
       <c r="G302" t="n">
-        <v>59.61</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="303">
@@ -7603,22 +7621,22 @@
         <v>50</v>
       </c>
       <c r="B303" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C303" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D303" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E303" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F303" t="n">
-        <v>783</v>
+        <v>11827</v>
       </c>
       <c r="G303" t="n">
-        <v>0.12</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="304">
@@ -7626,22 +7644,22 @@
         <v>50</v>
       </c>
       <c r="B304" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C304" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D304" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E304" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F304" t="n">
-        <v>1696166</v>
+        <v>82</v>
       </c>
       <c r="G304" t="n">
-        <v>39.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -7649,22 +7667,22 @@
         <v>50</v>
       </c>
       <c r="B305" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C305" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D305" t="s">
         <v>10</v>
       </c>
       <c r="E305" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F305" t="n">
-        <v>2632296</v>
+        <v>2250229</v>
       </c>
       <c r="G305" t="n">
-        <v>60.76</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="306">
@@ -7672,22 +7690,22 @@
         <v>50</v>
       </c>
       <c r="B306" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C306" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D306" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F306" t="n">
-        <v>3400</v>
+        <v>265149</v>
       </c>
       <c r="G306" t="n">
-        <v>0.08</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="307">
@@ -7695,22 +7713,22 @@
         <v>50</v>
       </c>
       <c r="B307" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C307" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D307" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E307" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F307" t="n">
-        <v>79</v>
+        <v>19025</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="308">
@@ -7718,45 +7736,45 @@
         <v>50</v>
       </c>
       <c r="B308" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C308" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D308" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E308" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F308" t="n">
-        <v>806688</v>
+        <v>18378</v>
       </c>
       <c r="G308" t="n">
-        <v>42.06</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="s">
-        <v>50</v>
-      </c>
-      <c r="B309" t="s">
-        <v>97</v>
-      </c>
-      <c r="C309" t="s">
-        <v>18</v>
-      </c>
-      <c r="D309" t="s">
-        <v>10</v>
-      </c>
-      <c r="E309" t="s">
-        <v>99</v>
-      </c>
-      <c r="F309" t="n">
-        <v>1110151</v>
-      </c>
-      <c r="G309" t="n">
-        <v>57.89</v>
+      <c r="A309" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>1725</v>
+      </c>
+      <c r="G309" s="2" t="n">
+        <v>0.07</v>
       </c>
     </row>
     <row r="310">
@@ -7764,22 +7782,22 @@
         <v>50</v>
       </c>
       <c r="B310" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C310" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D310" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="E310" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F310" t="n">
-        <v>978</v>
+        <v>507545</v>
       </c>
       <c r="G310" t="n">
-        <v>0.05</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="311">
@@ -7787,22 +7805,22 @@
         <v>50</v>
       </c>
       <c r="B311" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C311" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D311" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F311" t="n">
-        <v>15</v>
+        <v>1566121</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="312">
@@ -7810,22 +7828,22 @@
         <v>50</v>
       </c>
       <c r="B312" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C312" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D312" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E312" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F312" t="n">
-        <v>1146555</v>
+        <v>381283</v>
       </c>
       <c r="G312" t="n">
-        <v>44.88</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="313">
@@ -7833,45 +7851,45 @@
         <v>50</v>
       </c>
       <c r="B313" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C313" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D313" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E313" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F313" t="n">
-        <v>1407198</v>
+        <v>46495</v>
       </c>
       <c r="G313" t="n">
-        <v>55.09</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F314" s="2" t="n">
-        <v>753</v>
-      </c>
-      <c r="G314" s="2" t="n">
-        <v>0.03</v>
+      <c r="A314" t="s">
+        <v>50</v>
+      </c>
+      <c r="B314" t="s">
+        <v>96</v>
+      </c>
+      <c r="C314" t="s">
+        <v>9</v>
+      </c>
+      <c r="D314" t="s">
+        <v>60</v>
+      </c>
+      <c r="E314" t="s">
+        <v>94</v>
+      </c>
+      <c r="F314" t="n">
+        <v>2506</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="315">
@@ -7879,22 +7897,22 @@
         <v>50</v>
       </c>
       <c r="B315" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C315" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D315" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E315" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F315" t="n">
-        <v>1042147</v>
+        <v>267873</v>
       </c>
       <c r="G315" t="n">
-        <v>41.62</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="316">
@@ -7902,22 +7920,22 @@
         <v>50</v>
       </c>
       <c r="B316" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C316" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D316" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E316" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F316" t="n">
-        <v>1457909</v>
+        <v>345878</v>
       </c>
       <c r="G316" t="n">
-        <v>58.22</v>
+        <v>51.61</v>
       </c>
     </row>
     <row r="317">
@@ -7925,22 +7943,22 @@
         <v>50</v>
       </c>
       <c r="B317" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C317" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D317" t="s">
+        <v>14</v>
+      </c>
+      <c r="E317" t="s">
         <v>91</v>
       </c>
-      <c r="E317" t="s">
-        <v>92</v>
-      </c>
       <c r="F317" t="n">
-        <v>3570</v>
+        <v>48094</v>
       </c>
       <c r="G317" t="n">
-        <v>0.14</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="318">
@@ -7948,22 +7966,22 @@
         <v>50</v>
       </c>
       <c r="B318" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C318" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D318" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E318" t="s">
         <v>93</v>
       </c>
       <c r="F318" t="n">
-        <v>324</v>
+        <v>8107</v>
       </c>
       <c r="G318" t="n">
-        <v>0.01</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="319">
@@ -7971,22 +7989,22 @@
         <v>50</v>
       </c>
       <c r="B319" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C319" t="s">
         <v>16</v>
       </c>
       <c r="D319" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E319" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F319" t="n">
-        <v>268614</v>
+        <v>203</v>
       </c>
       <c r="G319" t="n">
-        <v>40.08</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="320">
@@ -7994,22 +8012,22 @@
         <v>50</v>
       </c>
       <c r="B320" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C320" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D320" t="s">
         <v>10</v>
       </c>
       <c r="E320" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F320" t="n">
-        <v>400758</v>
+        <v>1903588</v>
       </c>
       <c r="G320" t="n">
-        <v>59.8</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="321">
@@ -8017,22 +8035,22 @@
         <v>50</v>
       </c>
       <c r="B321" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C321" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D321" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E321" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F321" t="n">
-        <v>783</v>
+        <v>2024911</v>
       </c>
       <c r="G321" t="n">
-        <v>0.12</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="322">
@@ -8040,22 +8058,22 @@
         <v>50</v>
       </c>
       <c r="B322" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C322" t="s">
         <v>17</v>
       </c>
       <c r="D322" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E322" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F322" t="n">
-        <v>1729012</v>
+        <v>337690</v>
       </c>
       <c r="G322" t="n">
-        <v>39.91</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="323">
@@ -8063,22 +8081,22 @@
         <v>50</v>
       </c>
       <c r="B323" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C323" t="s">
         <v>17</v>
       </c>
       <c r="D323" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E323" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F323" t="n">
-        <v>2599450</v>
+        <v>62684</v>
       </c>
       <c r="G323" t="n">
-        <v>60.01</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="324">
@@ -8086,22 +8104,22 @@
         <v>50</v>
       </c>
       <c r="B324" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C324" t="s">
         <v>17</v>
       </c>
       <c r="D324" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="E324" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F324" t="n">
-        <v>3400</v>
+        <v>3068</v>
       </c>
       <c r="G324" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="325">
@@ -8109,22 +8127,22 @@
         <v>50</v>
       </c>
       <c r="B325" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C325" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D325" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E325" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F325" t="n">
-        <v>79</v>
+        <v>1180745</v>
       </c>
       <c r="G325" t="n">
-        <v>0</v>
+        <v>61.57</v>
       </c>
     </row>
     <row r="326">
@@ -8132,22 +8150,22 @@
         <v>50</v>
       </c>
       <c r="B326" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C326" t="s">
         <v>18</v>
       </c>
       <c r="D326" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E326" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F326" t="n">
-        <v>700215</v>
+        <v>653913</v>
       </c>
       <c r="G326" t="n">
-        <v>36.51</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="327">
@@ -8155,22 +8173,22 @@
         <v>50</v>
       </c>
       <c r="B327" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C327" t="s">
         <v>18</v>
       </c>
       <c r="D327" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E327" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F327" t="n">
-        <v>1216625</v>
+        <v>65568</v>
       </c>
       <c r="G327" t="n">
-        <v>63.44</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="328">
@@ -8178,22 +8196,22 @@
         <v>50</v>
       </c>
       <c r="B328" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C328" t="s">
         <v>18</v>
       </c>
       <c r="D328" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E328" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F328" t="n">
-        <v>978</v>
+        <v>16356</v>
       </c>
       <c r="G328" t="n">
-        <v>0.05</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="329">
@@ -8201,7 +8219,7 @@
         <v>50</v>
       </c>
       <c r="B329" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C329" t="s">
         <v>18</v>
@@ -8210,13 +8228,13 @@
         <v>60</v>
       </c>
       <c r="E329" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F329" t="n">
-        <v>15</v>
+        <v>1250</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="330">
@@ -8224,22 +8242,22 @@
         <v>50</v>
       </c>
       <c r="B330" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C330" t="s">
         <v>19</v>
       </c>
       <c r="D330" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E330" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F330" t="n">
-        <v>959368</v>
+        <v>1841528</v>
       </c>
       <c r="G330" t="n">
-        <v>37.56</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="331">
@@ -8247,45 +8265,45 @@
         <v>50</v>
       </c>
       <c r="B331" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C331" t="s">
         <v>19</v>
       </c>
       <c r="D331" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E331" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F331" t="n">
-        <v>1594385</v>
+        <v>638029</v>
       </c>
       <c r="G331" t="n">
-        <v>62.41</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C332" s="2" t="s">
+      <c r="A332" t="s">
+        <v>50</v>
+      </c>
+      <c r="B332" t="s">
+        <v>96</v>
+      </c>
+      <c r="C332" t="s">
         <v>19</v>
       </c>
-      <c r="D332" s="2" t="s">
+      <c r="D332" t="s">
+        <v>14</v>
+      </c>
+      <c r="E332" t="s">
         <v>91</v>
       </c>
-      <c r="E332" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F332" s="2" t="n">
-        <v>753</v>
-      </c>
-      <c r="G332" s="2" t="n">
-        <v>0.03</v>
+      <c r="F332" t="n">
+        <v>54578</v>
+      </c>
+      <c r="G332" t="n">
+        <v>2.14</v>
       </c>
     </row>
     <row r="333">
@@ -8293,45 +8311,45 @@
         <v>50</v>
       </c>
       <c r="B333" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C333" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D333" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E333" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F333" t="n">
-        <v>1369885</v>
+        <v>19815</v>
       </c>
       <c r="G333" t="n">
-        <v>54.71</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="s">
-        <v>50</v>
-      </c>
-      <c r="B334" t="s">
-        <v>103</v>
-      </c>
-      <c r="C334" t="s">
-        <v>9</v>
-      </c>
-      <c r="D334" t="s">
-        <v>10</v>
-      </c>
-      <c r="E334" t="s">
-        <v>105</v>
-      </c>
-      <c r="F334" t="n">
-        <v>1130171</v>
-      </c>
-      <c r="G334" t="n">
-        <v>45.14</v>
+      <c r="A334" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F334" s="2" t="n">
+        <v>556</v>
+      </c>
+      <c r="G334" s="2" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="335">
@@ -8339,22 +8357,22 @@
         <v>50</v>
       </c>
       <c r="B335" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C335" t="s">
         <v>9</v>
       </c>
       <c r="D335" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="E335" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F335" t="n">
-        <v>3570</v>
+        <v>1919750</v>
       </c>
       <c r="G335" t="n">
-        <v>0.14</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="336">
@@ -8362,22 +8380,22 @@
         <v>50</v>
       </c>
       <c r="B336" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C336" t="s">
         <v>9</v>
       </c>
       <c r="D336" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E336" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F336" t="n">
-        <v>324</v>
+        <v>580306</v>
       </c>
       <c r="G336" t="n">
-        <v>0.01</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="337">
@@ -8385,22 +8403,22 @@
         <v>50</v>
       </c>
       <c r="B337" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C337" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D337" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E337" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F337" t="n">
-        <v>336013</v>
+        <v>3570</v>
       </c>
       <c r="G337" t="n">
-        <v>50.14</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="338">
@@ -8408,22 +8426,22 @@
         <v>50</v>
       </c>
       <c r="B338" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C338" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D338" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E338" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F338" t="n">
-        <v>333359</v>
+        <v>324</v>
       </c>
       <c r="G338" t="n">
-        <v>49.74</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="339">
@@ -8431,22 +8449,22 @@
         <v>50</v>
       </c>
       <c r="B339" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C339" t="s">
         <v>16</v>
       </c>
       <c r="D339" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="E339" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F339" t="n">
-        <v>783</v>
+        <v>513700</v>
       </c>
       <c r="G339" t="n">
-        <v>0.12</v>
+        <v>76.65</v>
       </c>
     </row>
     <row r="340">
@@ -8454,22 +8472,22 @@
         <v>50</v>
       </c>
       <c r="B340" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C340" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D340" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E340" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F340" t="n">
-        <v>2255476</v>
+        <v>155672</v>
       </c>
       <c r="G340" t="n">
-        <v>52.07</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="341">
@@ -8477,22 +8495,22 @@
         <v>50</v>
       </c>
       <c r="B341" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C341" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D341" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E341" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F341" t="n">
-        <v>2072987</v>
+        <v>783</v>
       </c>
       <c r="G341" t="n">
-        <v>47.85</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="342">
@@ -8500,22 +8518,22 @@
         <v>50</v>
       </c>
       <c r="B342" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C342" t="s">
         <v>17</v>
       </c>
       <c r="D342" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="E342" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F342" t="n">
-        <v>3400</v>
+        <v>3394170</v>
       </c>
       <c r="G342" t="n">
-        <v>0.08</v>
+        <v>78.35</v>
       </c>
     </row>
     <row r="343">
@@ -8523,22 +8541,22 @@
         <v>50</v>
       </c>
       <c r="B343" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C343" t="s">
         <v>17</v>
       </c>
       <c r="D343" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E343" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F343" t="n">
-        <v>79</v>
+        <v>934292</v>
       </c>
       <c r="G343" t="n">
-        <v>0</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="344">
@@ -8546,22 +8564,22 @@
         <v>50</v>
       </c>
       <c r="B344" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C344" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D344" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E344" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F344" t="n">
-        <v>909108</v>
+        <v>3400</v>
       </c>
       <c r="G344" t="n">
-        <v>47.4</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="345">
@@ -8569,22 +8587,22 @@
         <v>50</v>
       </c>
       <c r="B345" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C345" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D345" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E345" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F345" t="n">
-        <v>1007732</v>
+        <v>79</v>
       </c>
       <c r="G345" t="n">
-        <v>52.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -8592,22 +8610,22 @@
         <v>50</v>
       </c>
       <c r="B346" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C346" t="s">
         <v>18</v>
       </c>
       <c r="D346" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="E346" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F346" t="n">
-        <v>978</v>
+        <v>1470345</v>
       </c>
       <c r="G346" t="n">
-        <v>0.05</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="347">
@@ -8615,22 +8633,22 @@
         <v>50</v>
       </c>
       <c r="B347" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C347" t="s">
         <v>18</v>
       </c>
       <c r="D347" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E347" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F347" t="n">
-        <v>15</v>
+        <v>446494</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="348">
@@ -8638,22 +8656,22 @@
         <v>50</v>
       </c>
       <c r="B348" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C348" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D348" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E348" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F348" t="n">
-        <v>1223065</v>
+        <v>978</v>
       </c>
       <c r="G348" t="n">
-        <v>47.88</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="349">
@@ -8661,22 +8679,22 @@
         <v>50</v>
       </c>
       <c r="B349" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C349" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D349" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E349" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F349" t="n">
-        <v>1330688</v>
+        <v>15</v>
       </c>
       <c r="G349" t="n">
-        <v>52.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -8684,21 +8702,1723 @@
         <v>50</v>
       </c>
       <c r="B350" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C350" t="s">
         <v>19</v>
       </c>
       <c r="D350" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="E350" t="s">
+        <v>98</v>
+      </c>
+      <c r="F350" t="n">
+        <v>1896963</v>
+      </c>
+      <c r="G350" t="n">
+        <v>74.26</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>50</v>
+      </c>
+      <c r="B351" t="s">
+        <v>97</v>
+      </c>
+      <c r="C351" t="s">
+        <v>19</v>
+      </c>
+      <c r="D351" t="s">
+        <v>10</v>
+      </c>
+      <c r="E351" t="s">
+        <v>99</v>
+      </c>
+      <c r="F351" t="n">
+        <v>656790</v>
+      </c>
+      <c r="G351" t="n">
+        <v>25.71</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D352" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F350" t="n">
+      <c r="E352" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F352" s="2" t="n">
         <v>753</v>
       </c>
-      <c r="G350" t="n">
+      <c r="G352" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>50</v>
+      </c>
+      <c r="B353" t="s">
+        <v>100</v>
+      </c>
+      <c r="C353" t="s">
+        <v>9</v>
+      </c>
+      <c r="D353" t="s">
+        <v>39</v>
+      </c>
+      <c r="E353" t="s">
+        <v>101</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1106125</v>
+      </c>
+      <c r="G353" t="n">
+        <v>44.18</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>50</v>
+      </c>
+      <c r="B354" t="s">
+        <v>100</v>
+      </c>
+      <c r="C354" t="s">
+        <v>9</v>
+      </c>
+      <c r="D354" t="s">
+        <v>10</v>
+      </c>
+      <c r="E354" t="s">
+        <v>102</v>
+      </c>
+      <c r="F354" t="n">
+        <v>1393931</v>
+      </c>
+      <c r="G354" t="n">
+        <v>55.67</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>50</v>
+      </c>
+      <c r="B355" t="s">
+        <v>100</v>
+      </c>
+      <c r="C355" t="s">
+        <v>9</v>
+      </c>
+      <c r="D355" t="s">
+        <v>92</v>
+      </c>
+      <c r="E355" t="s">
+        <v>93</v>
+      </c>
+      <c r="F355" t="n">
+        <v>3570</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>50</v>
+      </c>
+      <c r="B356" t="s">
+        <v>100</v>
+      </c>
+      <c r="C356" t="s">
+        <v>9</v>
+      </c>
+      <c r="D356" t="s">
+        <v>60</v>
+      </c>
+      <c r="E356" t="s">
+        <v>94</v>
+      </c>
+      <c r="F356" t="n">
+        <v>324</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>50</v>
+      </c>
+      <c r="B357" t="s">
+        <v>100</v>
+      </c>
+      <c r="C357" t="s">
+        <v>16</v>
+      </c>
+      <c r="D357" t="s">
+        <v>39</v>
+      </c>
+      <c r="E357" t="s">
+        <v>101</v>
+      </c>
+      <c r="F357" t="n">
+        <v>297801</v>
+      </c>
+      <c r="G357" t="n">
+        <v>44.44</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>50</v>
+      </c>
+      <c r="B358" t="s">
+        <v>100</v>
+      </c>
+      <c r="C358" t="s">
+        <v>16</v>
+      </c>
+      <c r="D358" t="s">
+        <v>10</v>
+      </c>
+      <c r="E358" t="s">
+        <v>102</v>
+      </c>
+      <c r="F358" t="n">
+        <v>371571</v>
+      </c>
+      <c r="G358" t="n">
+        <v>55.45</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>50</v>
+      </c>
+      <c r="B359" t="s">
+        <v>100</v>
+      </c>
+      <c r="C359" t="s">
+        <v>16</v>
+      </c>
+      <c r="D359" t="s">
+        <v>92</v>
+      </c>
+      <c r="E359" t="s">
+        <v>93</v>
+      </c>
+      <c r="F359" t="n">
+        <v>783</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>50</v>
+      </c>
+      <c r="B360" t="s">
+        <v>100</v>
+      </c>
+      <c r="C360" t="s">
+        <v>17</v>
+      </c>
+      <c r="D360" t="s">
+        <v>39</v>
+      </c>
+      <c r="E360" t="s">
+        <v>101</v>
+      </c>
+      <c r="F360" t="n">
+        <v>1810510</v>
+      </c>
+      <c r="G360" t="n">
+        <v>41.79</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>50</v>
+      </c>
+      <c r="B361" t="s">
+        <v>100</v>
+      </c>
+      <c r="C361" t="s">
+        <v>17</v>
+      </c>
+      <c r="D361" t="s">
+        <v>10</v>
+      </c>
+      <c r="E361" t="s">
+        <v>102</v>
+      </c>
+      <c r="F361" t="n">
+        <v>2517953</v>
+      </c>
+      <c r="G361" t="n">
+        <v>58.13</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>50</v>
+      </c>
+      <c r="B362" t="s">
+        <v>100</v>
+      </c>
+      <c r="C362" t="s">
+        <v>17</v>
+      </c>
+      <c r="D362" t="s">
+        <v>92</v>
+      </c>
+      <c r="E362" t="s">
+        <v>93</v>
+      </c>
+      <c r="F362" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>50</v>
+      </c>
+      <c r="B363" t="s">
+        <v>100</v>
+      </c>
+      <c r="C363" t="s">
+        <v>17</v>
+      </c>
+      <c r="D363" t="s">
+        <v>60</v>
+      </c>
+      <c r="E363" t="s">
+        <v>94</v>
+      </c>
+      <c r="F363" t="n">
+        <v>79</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>50</v>
+      </c>
+      <c r="B364" t="s">
+        <v>100</v>
+      </c>
+      <c r="C364" t="s">
+        <v>18</v>
+      </c>
+      <c r="D364" t="s">
+        <v>39</v>
+      </c>
+      <c r="E364" t="s">
+        <v>101</v>
+      </c>
+      <c r="F364" t="n">
+        <v>760636</v>
+      </c>
+      <c r="G364" t="n">
+        <v>39.66</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>50</v>
+      </c>
+      <c r="B365" t="s">
+        <v>100</v>
+      </c>
+      <c r="C365" t="s">
+        <v>18</v>
+      </c>
+      <c r="D365" t="s">
+        <v>10</v>
+      </c>
+      <c r="E365" t="s">
+        <v>102</v>
+      </c>
+      <c r="F365" t="n">
+        <v>1156203</v>
+      </c>
+      <c r="G365" t="n">
+        <v>60.29</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>50</v>
+      </c>
+      <c r="B366" t="s">
+        <v>100</v>
+      </c>
+      <c r="C366" t="s">
+        <v>18</v>
+      </c>
+      <c r="D366" t="s">
+        <v>92</v>
+      </c>
+      <c r="E366" t="s">
+        <v>93</v>
+      </c>
+      <c r="F366" t="n">
+        <v>978</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>50</v>
+      </c>
+      <c r="B367" t="s">
+        <v>100</v>
+      </c>
+      <c r="C367" t="s">
+        <v>18</v>
+      </c>
+      <c r="D367" t="s">
+        <v>60</v>
+      </c>
+      <c r="E367" t="s">
+        <v>94</v>
+      </c>
+      <c r="F367" t="n">
+        <v>15</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>50</v>
+      </c>
+      <c r="B368" t="s">
+        <v>100</v>
+      </c>
+      <c r="C368" t="s">
+        <v>19</v>
+      </c>
+      <c r="D368" t="s">
+        <v>39</v>
+      </c>
+      <c r="E368" t="s">
+        <v>101</v>
+      </c>
+      <c r="F368" t="n">
+        <v>1106700</v>
+      </c>
+      <c r="G368" t="n">
+        <v>43.32</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>50</v>
+      </c>
+      <c r="B369" t="s">
+        <v>100</v>
+      </c>
+      <c r="C369" t="s">
+        <v>19</v>
+      </c>
+      <c r="D369" t="s">
+        <v>10</v>
+      </c>
+      <c r="E369" t="s">
+        <v>102</v>
+      </c>
+      <c r="F369" t="n">
+        <v>1447053</v>
+      </c>
+      <c r="G369" t="n">
+        <v>56.65</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="G370" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>50</v>
+      </c>
+      <c r="B371" t="s">
+        <v>103</v>
+      </c>
+      <c r="C371" t="s">
+        <v>9</v>
+      </c>
+      <c r="D371" t="s">
+        <v>39</v>
+      </c>
+      <c r="E371" t="s">
+        <v>104</v>
+      </c>
+      <c r="F371" t="n">
+        <v>1073916</v>
+      </c>
+      <c r="G371" t="n">
+        <v>42.89</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>50</v>
+      </c>
+      <c r="B372" t="s">
+        <v>103</v>
+      </c>
+      <c r="C372" t="s">
+        <v>9</v>
+      </c>
+      <c r="D372" t="s">
+        <v>10</v>
+      </c>
+      <c r="E372" t="s">
+        <v>105</v>
+      </c>
+      <c r="F372" t="n">
+        <v>1426140</v>
+      </c>
+      <c r="G372" t="n">
+        <v>56.96</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>50</v>
+      </c>
+      <c r="B373" t="s">
+        <v>103</v>
+      </c>
+      <c r="C373" t="s">
+        <v>9</v>
+      </c>
+      <c r="D373" t="s">
+        <v>92</v>
+      </c>
+      <c r="E373" t="s">
+        <v>93</v>
+      </c>
+      <c r="F373" t="n">
+        <v>3570</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>50</v>
+      </c>
+      <c r="B374" t="s">
+        <v>103</v>
+      </c>
+      <c r="C374" t="s">
+        <v>9</v>
+      </c>
+      <c r="D374" t="s">
+        <v>60</v>
+      </c>
+      <c r="E374" t="s">
+        <v>94</v>
+      </c>
+      <c r="F374" t="n">
+        <v>324</v>
+      </c>
+      <c r="G374" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>50</v>
+      </c>
+      <c r="B375" t="s">
+        <v>103</v>
+      </c>
+      <c r="C375" t="s">
+        <v>16</v>
+      </c>
+      <c r="D375" t="s">
+        <v>39</v>
+      </c>
+      <c r="E375" t="s">
+        <v>104</v>
+      </c>
+      <c r="F375" t="n">
+        <v>269921</v>
+      </c>
+      <c r="G375" t="n">
+        <v>40.28</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>50</v>
+      </c>
+      <c r="B376" t="s">
+        <v>103</v>
+      </c>
+      <c r="C376" t="s">
+        <v>16</v>
+      </c>
+      <c r="D376" t="s">
+        <v>10</v>
+      </c>
+      <c r="E376" t="s">
+        <v>105</v>
+      </c>
+      <c r="F376" t="n">
+        <v>399452</v>
+      </c>
+      <c r="G376" t="n">
+        <v>59.61</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>50</v>
+      </c>
+      <c r="B377" t="s">
+        <v>103</v>
+      </c>
+      <c r="C377" t="s">
+        <v>16</v>
+      </c>
+      <c r="D377" t="s">
+        <v>92</v>
+      </c>
+      <c r="E377" t="s">
+        <v>93</v>
+      </c>
+      <c r="F377" t="n">
+        <v>783</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>50</v>
+      </c>
+      <c r="B378" t="s">
+        <v>103</v>
+      </c>
+      <c r="C378" t="s">
+        <v>17</v>
+      </c>
+      <c r="D378" t="s">
+        <v>39</v>
+      </c>
+      <c r="E378" t="s">
+        <v>104</v>
+      </c>
+      <c r="F378" t="n">
+        <v>1696166</v>
+      </c>
+      <c r="G378" t="n">
+        <v>39.15</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>50</v>
+      </c>
+      <c r="B379" t="s">
+        <v>103</v>
+      </c>
+      <c r="C379" t="s">
+        <v>17</v>
+      </c>
+      <c r="D379" t="s">
+        <v>10</v>
+      </c>
+      <c r="E379" t="s">
+        <v>105</v>
+      </c>
+      <c r="F379" t="n">
+        <v>2632296</v>
+      </c>
+      <c r="G379" t="n">
+        <v>60.76</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>50</v>
+      </c>
+      <c r="B380" t="s">
+        <v>103</v>
+      </c>
+      <c r="C380" t="s">
+        <v>17</v>
+      </c>
+      <c r="D380" t="s">
+        <v>92</v>
+      </c>
+      <c r="E380" t="s">
+        <v>93</v>
+      </c>
+      <c r="F380" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G380" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>50</v>
+      </c>
+      <c r="B381" t="s">
+        <v>103</v>
+      </c>
+      <c r="C381" t="s">
+        <v>17</v>
+      </c>
+      <c r="D381" t="s">
+        <v>60</v>
+      </c>
+      <c r="E381" t="s">
+        <v>94</v>
+      </c>
+      <c r="F381" t="n">
+        <v>79</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s">
+        <v>50</v>
+      </c>
+      <c r="B382" t="s">
+        <v>103</v>
+      </c>
+      <c r="C382" t="s">
+        <v>18</v>
+      </c>
+      <c r="D382" t="s">
+        <v>39</v>
+      </c>
+      <c r="E382" t="s">
+        <v>104</v>
+      </c>
+      <c r="F382" t="n">
+        <v>806688</v>
+      </c>
+      <c r="G382" t="n">
+        <v>42.06</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s">
+        <v>50</v>
+      </c>
+      <c r="B383" t="s">
+        <v>103</v>
+      </c>
+      <c r="C383" t="s">
+        <v>18</v>
+      </c>
+      <c r="D383" t="s">
+        <v>10</v>
+      </c>
+      <c r="E383" t="s">
+        <v>105</v>
+      </c>
+      <c r="F383" t="n">
+        <v>1110151</v>
+      </c>
+      <c r="G383" t="n">
+        <v>57.89</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s">
+        <v>50</v>
+      </c>
+      <c r="B384" t="s">
+        <v>103</v>
+      </c>
+      <c r="C384" t="s">
+        <v>18</v>
+      </c>
+      <c r="D384" t="s">
+        <v>92</v>
+      </c>
+      <c r="E384" t="s">
+        <v>93</v>
+      </c>
+      <c r="F384" t="n">
+        <v>978</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s">
+        <v>50</v>
+      </c>
+      <c r="B385" t="s">
+        <v>103</v>
+      </c>
+      <c r="C385" t="s">
+        <v>18</v>
+      </c>
+      <c r="D385" t="s">
+        <v>60</v>
+      </c>
+      <c r="E385" t="s">
+        <v>94</v>
+      </c>
+      <c r="F385" t="n">
+        <v>15</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s">
+        <v>50</v>
+      </c>
+      <c r="B386" t="s">
+        <v>103</v>
+      </c>
+      <c r="C386" t="s">
+        <v>19</v>
+      </c>
+      <c r="D386" t="s">
+        <v>39</v>
+      </c>
+      <c r="E386" t="s">
+        <v>104</v>
+      </c>
+      <c r="F386" t="n">
+        <v>1146555</v>
+      </c>
+      <c r="G386" t="n">
+        <v>44.88</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s">
+        <v>50</v>
+      </c>
+      <c r="B387" t="s">
+        <v>103</v>
+      </c>
+      <c r="C387" t="s">
+        <v>19</v>
+      </c>
+      <c r="D387" t="s">
+        <v>10</v>
+      </c>
+      <c r="E387" t="s">
+        <v>105</v>
+      </c>
+      <c r="F387" t="n">
+        <v>1407198</v>
+      </c>
+      <c r="G387" t="n">
+        <v>55.09</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="G388" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s">
+        <v>50</v>
+      </c>
+      <c r="B389" t="s">
+        <v>106</v>
+      </c>
+      <c r="C389" t="s">
+        <v>9</v>
+      </c>
+      <c r="D389" t="s">
+        <v>39</v>
+      </c>
+      <c r="E389" t="s">
+        <v>107</v>
+      </c>
+      <c r="F389" t="n">
+        <v>1042147</v>
+      </c>
+      <c r="G389" t="n">
+        <v>41.62</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s">
+        <v>50</v>
+      </c>
+      <c r="B390" t="s">
+        <v>106</v>
+      </c>
+      <c r="C390" t="s">
+        <v>9</v>
+      </c>
+      <c r="D390" t="s">
+        <v>10</v>
+      </c>
+      <c r="E390" t="s">
+        <v>108</v>
+      </c>
+      <c r="F390" t="n">
+        <v>1457909</v>
+      </c>
+      <c r="G390" t="n">
+        <v>58.22</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s">
+        <v>50</v>
+      </c>
+      <c r="B391" t="s">
+        <v>106</v>
+      </c>
+      <c r="C391" t="s">
+        <v>9</v>
+      </c>
+      <c r="D391" t="s">
+        <v>92</v>
+      </c>
+      <c r="E391" t="s">
+        <v>93</v>
+      </c>
+      <c r="F391" t="n">
+        <v>3570</v>
+      </c>
+      <c r="G391" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s">
+        <v>50</v>
+      </c>
+      <c r="B392" t="s">
+        <v>106</v>
+      </c>
+      <c r="C392" t="s">
+        <v>9</v>
+      </c>
+      <c r="D392" t="s">
+        <v>60</v>
+      </c>
+      <c r="E392" t="s">
+        <v>94</v>
+      </c>
+      <c r="F392" t="n">
+        <v>324</v>
+      </c>
+      <c r="G392" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s">
+        <v>50</v>
+      </c>
+      <c r="B393" t="s">
+        <v>106</v>
+      </c>
+      <c r="C393" t="s">
+        <v>16</v>
+      </c>
+      <c r="D393" t="s">
+        <v>39</v>
+      </c>
+      <c r="E393" t="s">
+        <v>107</v>
+      </c>
+      <c r="F393" t="n">
+        <v>268614</v>
+      </c>
+      <c r="G393" t="n">
+        <v>40.08</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s">
+        <v>50</v>
+      </c>
+      <c r="B394" t="s">
+        <v>106</v>
+      </c>
+      <c r="C394" t="s">
+        <v>16</v>
+      </c>
+      <c r="D394" t="s">
+        <v>10</v>
+      </c>
+      <c r="E394" t="s">
+        <v>108</v>
+      </c>
+      <c r="F394" t="n">
+        <v>400758</v>
+      </c>
+      <c r="G394" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s">
+        <v>50</v>
+      </c>
+      <c r="B395" t="s">
+        <v>106</v>
+      </c>
+      <c r="C395" t="s">
+        <v>16</v>
+      </c>
+      <c r="D395" t="s">
+        <v>92</v>
+      </c>
+      <c r="E395" t="s">
+        <v>93</v>
+      </c>
+      <c r="F395" t="n">
+        <v>783</v>
+      </c>
+      <c r="G395" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>50</v>
+      </c>
+      <c r="B396" t="s">
+        <v>106</v>
+      </c>
+      <c r="C396" t="s">
+        <v>17</v>
+      </c>
+      <c r="D396" t="s">
+        <v>39</v>
+      </c>
+      <c r="E396" t="s">
+        <v>107</v>
+      </c>
+      <c r="F396" t="n">
+        <v>1729012</v>
+      </c>
+      <c r="G396" t="n">
+        <v>39.91</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>50</v>
+      </c>
+      <c r="B397" t="s">
+        <v>106</v>
+      </c>
+      <c r="C397" t="s">
+        <v>17</v>
+      </c>
+      <c r="D397" t="s">
+        <v>10</v>
+      </c>
+      <c r="E397" t="s">
+        <v>108</v>
+      </c>
+      <c r="F397" t="n">
+        <v>2599450</v>
+      </c>
+      <c r="G397" t="n">
+        <v>60.01</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>50</v>
+      </c>
+      <c r="B398" t="s">
+        <v>106</v>
+      </c>
+      <c r="C398" t="s">
+        <v>17</v>
+      </c>
+      <c r="D398" t="s">
+        <v>92</v>
+      </c>
+      <c r="E398" t="s">
+        <v>93</v>
+      </c>
+      <c r="F398" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>50</v>
+      </c>
+      <c r="B399" t="s">
+        <v>106</v>
+      </c>
+      <c r="C399" t="s">
+        <v>17</v>
+      </c>
+      <c r="D399" t="s">
+        <v>60</v>
+      </c>
+      <c r="E399" t="s">
+        <v>94</v>
+      </c>
+      <c r="F399" t="n">
+        <v>79</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>50</v>
+      </c>
+      <c r="B400" t="s">
+        <v>106</v>
+      </c>
+      <c r="C400" t="s">
+        <v>18</v>
+      </c>
+      <c r="D400" t="s">
+        <v>39</v>
+      </c>
+      <c r="E400" t="s">
+        <v>107</v>
+      </c>
+      <c r="F400" t="n">
+        <v>700215</v>
+      </c>
+      <c r="G400" t="n">
+        <v>36.51</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>50</v>
+      </c>
+      <c r="B401" t="s">
+        <v>106</v>
+      </c>
+      <c r="C401" t="s">
+        <v>18</v>
+      </c>
+      <c r="D401" t="s">
+        <v>10</v>
+      </c>
+      <c r="E401" t="s">
+        <v>108</v>
+      </c>
+      <c r="F401" t="n">
+        <v>1216625</v>
+      </c>
+      <c r="G401" t="n">
+        <v>63.44</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>50</v>
+      </c>
+      <c r="B402" t="s">
+        <v>106</v>
+      </c>
+      <c r="C402" t="s">
+        <v>18</v>
+      </c>
+      <c r="D402" t="s">
+        <v>92</v>
+      </c>
+      <c r="E402" t="s">
+        <v>93</v>
+      </c>
+      <c r="F402" t="n">
+        <v>978</v>
+      </c>
+      <c r="G402" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>50</v>
+      </c>
+      <c r="B403" t="s">
+        <v>106</v>
+      </c>
+      <c r="C403" t="s">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>60</v>
+      </c>
+      <c r="E403" t="s">
+        <v>94</v>
+      </c>
+      <c r="F403" t="n">
+        <v>15</v>
+      </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>50</v>
+      </c>
+      <c r="B404" t="s">
+        <v>106</v>
+      </c>
+      <c r="C404" t="s">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>39</v>
+      </c>
+      <c r="E404" t="s">
+        <v>107</v>
+      </c>
+      <c r="F404" t="n">
+        <v>959368</v>
+      </c>
+      <c r="G404" t="n">
+        <v>37.56</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>50</v>
+      </c>
+      <c r="B405" t="s">
+        <v>106</v>
+      </c>
+      <c r="C405" t="s">
+        <v>19</v>
+      </c>
+      <c r="D405" t="s">
+        <v>10</v>
+      </c>
+      <c r="E405" t="s">
+        <v>108</v>
+      </c>
+      <c r="F405" t="n">
+        <v>1594385</v>
+      </c>
+      <c r="G405" t="n">
+        <v>62.41</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E406" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="G406" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>50</v>
+      </c>
+      <c r="B407" t="s">
+        <v>109</v>
+      </c>
+      <c r="C407" t="s">
+        <v>9</v>
+      </c>
+      <c r="D407" t="s">
+        <v>39</v>
+      </c>
+      <c r="E407" t="s">
+        <v>110</v>
+      </c>
+      <c r="F407" t="n">
+        <v>1369885</v>
+      </c>
+      <c r="G407" t="n">
+        <v>54.71</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>50</v>
+      </c>
+      <c r="B408" t="s">
+        <v>109</v>
+      </c>
+      <c r="C408" t="s">
+        <v>9</v>
+      </c>
+      <c r="D408" t="s">
+        <v>10</v>
+      </c>
+      <c r="E408" t="s">
+        <v>111</v>
+      </c>
+      <c r="F408" t="n">
+        <v>1130171</v>
+      </c>
+      <c r="G408" t="n">
+        <v>45.14</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>50</v>
+      </c>
+      <c r="B409" t="s">
+        <v>109</v>
+      </c>
+      <c r="C409" t="s">
+        <v>9</v>
+      </c>
+      <c r="D409" t="s">
+        <v>92</v>
+      </c>
+      <c r="E409" t="s">
+        <v>93</v>
+      </c>
+      <c r="F409" t="n">
+        <v>3570</v>
+      </c>
+      <c r="G409" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>50</v>
+      </c>
+      <c r="B410" t="s">
+        <v>109</v>
+      </c>
+      <c r="C410" t="s">
+        <v>9</v>
+      </c>
+      <c r="D410" t="s">
+        <v>60</v>
+      </c>
+      <c r="E410" t="s">
+        <v>94</v>
+      </c>
+      <c r="F410" t="n">
+        <v>324</v>
+      </c>
+      <c r="G410" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>50</v>
+      </c>
+      <c r="B411" t="s">
+        <v>109</v>
+      </c>
+      <c r="C411" t="s">
+        <v>16</v>
+      </c>
+      <c r="D411" t="s">
+        <v>39</v>
+      </c>
+      <c r="E411" t="s">
+        <v>110</v>
+      </c>
+      <c r="F411" t="n">
+        <v>336013</v>
+      </c>
+      <c r="G411" t="n">
+        <v>50.14</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>50</v>
+      </c>
+      <c r="B412" t="s">
+        <v>109</v>
+      </c>
+      <c r="C412" t="s">
+        <v>16</v>
+      </c>
+      <c r="D412" t="s">
+        <v>10</v>
+      </c>
+      <c r="E412" t="s">
+        <v>111</v>
+      </c>
+      <c r="F412" t="n">
+        <v>333359</v>
+      </c>
+      <c r="G412" t="n">
+        <v>49.74</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>50</v>
+      </c>
+      <c r="B413" t="s">
+        <v>109</v>
+      </c>
+      <c r="C413" t="s">
+        <v>16</v>
+      </c>
+      <c r="D413" t="s">
+        <v>92</v>
+      </c>
+      <c r="E413" t="s">
+        <v>93</v>
+      </c>
+      <c r="F413" t="n">
+        <v>783</v>
+      </c>
+      <c r="G413" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>50</v>
+      </c>
+      <c r="B414" t="s">
+        <v>109</v>
+      </c>
+      <c r="C414" t="s">
+        <v>17</v>
+      </c>
+      <c r="D414" t="s">
+        <v>39</v>
+      </c>
+      <c r="E414" t="s">
+        <v>110</v>
+      </c>
+      <c r="F414" t="n">
+        <v>2255476</v>
+      </c>
+      <c r="G414" t="n">
+        <v>52.07</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>50</v>
+      </c>
+      <c r="B415" t="s">
+        <v>109</v>
+      </c>
+      <c r="C415" t="s">
+        <v>17</v>
+      </c>
+      <c r="D415" t="s">
+        <v>10</v>
+      </c>
+      <c r="E415" t="s">
+        <v>111</v>
+      </c>
+      <c r="F415" t="n">
+        <v>2072987</v>
+      </c>
+      <c r="G415" t="n">
+        <v>47.85</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>50</v>
+      </c>
+      <c r="B416" t="s">
+        <v>109</v>
+      </c>
+      <c r="C416" t="s">
+        <v>17</v>
+      </c>
+      <c r="D416" t="s">
+        <v>92</v>
+      </c>
+      <c r="E416" t="s">
+        <v>93</v>
+      </c>
+      <c r="F416" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G416" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>50</v>
+      </c>
+      <c r="B417" t="s">
+        <v>109</v>
+      </c>
+      <c r="C417" t="s">
+        <v>17</v>
+      </c>
+      <c r="D417" t="s">
+        <v>60</v>
+      </c>
+      <c r="E417" t="s">
+        <v>94</v>
+      </c>
+      <c r="F417" t="n">
+        <v>79</v>
+      </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>50</v>
+      </c>
+      <c r="B418" t="s">
+        <v>109</v>
+      </c>
+      <c r="C418" t="s">
+        <v>18</v>
+      </c>
+      <c r="D418" t="s">
+        <v>39</v>
+      </c>
+      <c r="E418" t="s">
+        <v>110</v>
+      </c>
+      <c r="F418" t="n">
+        <v>909108</v>
+      </c>
+      <c r="G418" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>50</v>
+      </c>
+      <c r="B419" t="s">
+        <v>109</v>
+      </c>
+      <c r="C419" t="s">
+        <v>18</v>
+      </c>
+      <c r="D419" t="s">
+        <v>10</v>
+      </c>
+      <c r="E419" t="s">
+        <v>111</v>
+      </c>
+      <c r="F419" t="n">
+        <v>1007732</v>
+      </c>
+      <c r="G419" t="n">
+        <v>52.55</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>50</v>
+      </c>
+      <c r="B420" t="s">
+        <v>109</v>
+      </c>
+      <c r="C420" t="s">
+        <v>18</v>
+      </c>
+      <c r="D420" t="s">
+        <v>92</v>
+      </c>
+      <c r="E420" t="s">
+        <v>93</v>
+      </c>
+      <c r="F420" t="n">
+        <v>978</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>50</v>
+      </c>
+      <c r="B421" t="s">
+        <v>109</v>
+      </c>
+      <c r="C421" t="s">
+        <v>18</v>
+      </c>
+      <c r="D421" t="s">
+        <v>60</v>
+      </c>
+      <c r="E421" t="s">
+        <v>94</v>
+      </c>
+      <c r="F421" t="n">
+        <v>15</v>
+      </c>
+      <c r="G421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>50</v>
+      </c>
+      <c r="B422" t="s">
+        <v>109</v>
+      </c>
+      <c r="C422" t="s">
+        <v>19</v>
+      </c>
+      <c r="D422" t="s">
+        <v>39</v>
+      </c>
+      <c r="E422" t="s">
+        <v>110</v>
+      </c>
+      <c r="F422" t="n">
+        <v>1223065</v>
+      </c>
+      <c r="G422" t="n">
+        <v>47.88</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>50</v>
+      </c>
+      <c r="B423" t="s">
+        <v>109</v>
+      </c>
+      <c r="C423" t="s">
+        <v>19</v>
+      </c>
+      <c r="D423" t="s">
+        <v>10</v>
+      </c>
+      <c r="E423" t="s">
+        <v>111</v>
+      </c>
+      <c r="F423" t="n">
+        <v>1330688</v>
+      </c>
+      <c r="G423" t="n">
+        <v>52.09</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>50</v>
+      </c>
+      <c r="B424" t="s">
+        <v>109</v>
+      </c>
+      <c r="C424" t="s">
+        <v>19</v>
+      </c>
+      <c r="D424" t="s">
+        <v>92</v>
+      </c>
+      <c r="E424" t="s">
+        <v>93</v>
+      </c>
+      <c r="F424" t="n">
+        <v>753</v>
+      </c>
+      <c r="G424" t="n">
         <v>0.03</v>
       </c>
     </row>
